--- a/outputs/e5_disagreement_review_2026-07-24/E5_Hard_Disagreement_Review.xlsx
+++ b/outputs/e5_disagreement_review_2026-07-24/E5_Hard_Disagreement_Review.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R47857e80c9c14076"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="Rf985f5706d9f4338"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Article Text" sheetId="3" r:id="Rc17e9884c84d48a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="R1b311cd63d45467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Lists" sheetId="5" r:id="R9b498978f7294345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Independent Review" sheetId="6" r:id="Rf6679dd902da4c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R1724179f3c324a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="R9b4f9b3c4b94470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Article Text" sheetId="3" r:id="R1560a68726274edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="Rd2ab96616a1e4940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Lists" sheetId="5" r:id="Rcf267e1f048143d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Independent Review" sheetId="6" r:id="R6f2b8d25e39647da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geographic Linkage" sheetId="7" r:id="R7e3ed86d7674450d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +22,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -67,8 +68,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="20">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -130,8 +137,43 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="16">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -277,11 +319,25 @@
         <x:color rgb="FFD9D9D9"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E1F2"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E1F2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E1F2"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1F2"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="92">
+  <x:cellXfs count="122">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -470,6 +526,68 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -758,6 +876,14 @@
         <x:v>Counts in Summary describe the development-set diagnosis only. They must not be reported as validation performance or used to authorise classification of the remaining corpus.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="121" t="str">
+        <x:v>Geographic linkage</x:v>
+      </x:c>
+      <x:c r="B12" s="121" t="str">
+        <x:v>For the 28 local hard disagreements, use Geographic Linkage before final diagnosis. Automated candidates only locate possible evidence; confirm the sampled division/place and quote an exact sentence, or record why the linkage remains unresolved.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -9492,4 +9618,1273 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="55" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="25" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="22" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="94" t="str">
+        <x:v>E5 local-arm geographic linkage review (28 hard disagreements)</x:v>
+      </x:c>
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="94"/>
+      <x:c r="D1" s="94"/>
+      <x:c r="E1" s="94"/>
+      <x:c r="F1" s="94"/>
+      <x:c r="G1" s="94"/>
+      <x:c r="H1" s="94"/>
+      <x:c r="I1" s="94"/>
+      <x:c r="J1" s="94"/>
+      <x:c r="K1" s="94"/>
+      <x:c r="L1" s="94"/>
+      <x:c r="M1" s="94"/>
+      <x:c r="N1" s="94"/>
+      <x:c r="O1" s="94"/>
+      <x:c r="P1" s="94"/>
+      <x:c r="Q1" s="94"/>
+      <x:c r="R1" s="94"/>
+      <x:c r="S1" s="94"/>
+      <x:c r="T1" s="94"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="97" t="str">
+        <x:v>Blue cells are deterministic search aids, not E5 decisions. Complete the yellow cells from the full article and record an exact supporting sentence before confirming L1-L4.</x:v>
+      </x:c>
+      <x:c r="B2" s="97"/>
+      <x:c r="C2" s="97"/>
+      <x:c r="D2" s="97"/>
+      <x:c r="E2" s="97"/>
+      <x:c r="F2" s="97"/>
+      <x:c r="G2" s="97"/>
+      <x:c r="H2" s="97"/>
+      <x:c r="I2" s="97"/>
+      <x:c r="J2" s="97"/>
+      <x:c r="K2" s="97"/>
+      <x:c r="L2" s="97"/>
+      <x:c r="M2" s="97"/>
+      <x:c r="N2" s="97"/>
+      <x:c r="O2" s="97"/>
+      <x:c r="P2" s="97"/>
+      <x:c r="Q2" s="97"/>
+      <x:c r="R2" s="97"/>
+      <x:c r="S2" s="97"/>
+      <x:c r="T2" s="97"/>
+    </x:row>
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="97" t="str">
+        <x:v>If the article names a place but the sampled division cannot be verified, choose unresolved_missing_context rather than inferring a ward.</x:v>
+      </x:c>
+      <x:c r="B3" s="97"/>
+      <x:c r="C3" s="97"/>
+      <x:c r="D3" s="97"/>
+      <x:c r="E3" s="97"/>
+      <x:c r="F3" s="97"/>
+      <x:c r="G3" s="97"/>
+      <x:c r="H3" s="97"/>
+      <x:c r="I3" s="97"/>
+      <x:c r="J3" s="97"/>
+      <x:c r="K3" s="97"/>
+      <x:c r="L3" s="97"/>
+      <x:c r="M3" s="97"/>
+      <x:c r="N3" s="97"/>
+      <x:c r="O3" s="97"/>
+      <x:c r="P3" s="97"/>
+      <x:c r="Q3" s="97"/>
+      <x:c r="R3" s="97"/>
+      <x:c r="S3" s="97"/>
+      <x:c r="T3" s="97"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="111" t="str">
+        <x:v>review_index</x:v>
+      </x:c>
+      <x:c r="B5" s="111" t="str">
+        <x:v>article_id</x:v>
+      </x:c>
+      <x:c r="C5" s="111" t="str">
+        <x:v>headline</x:v>
+      </x:c>
+      <x:c r="D5" s="111" t="str">
+        <x:v>human_decision</x:v>
+      </x:c>
+      <x:c r="E5" s="111" t="str">
+        <x:v>llm_decision</x:v>
+      </x:c>
+      <x:c r="F5" s="111" t="str">
+        <x:v>ward_context_missing</x:v>
+      </x:c>
+      <x:c r="G5" s="111" t="str">
+        <x:v>exact_sample_division_candidates</x:v>
+      </x:c>
+      <x:c r="H5" s="111" t="str">
+        <x:v>sample_place_candidates</x:v>
+      </x:c>
+      <x:c r="I5" s="111" t="str">
+        <x:v>surrey_authority_signals</x:v>
+      </x:c>
+      <x:c r="J5" s="111" t="str">
+        <x:v>automated_evidence_sentences</x:v>
+      </x:c>
+      <x:c r="K5" s="111" t="str">
+        <x:v>linkage_review_status</x:v>
+      </x:c>
+      <x:c r="L5" s="111" t="str">
+        <x:v>confirmed_link_type</x:v>
+      </x:c>
+      <x:c r="M5" s="111" t="str">
+        <x:v>confirmed_linked_place</x:v>
+      </x:c>
+      <x:c r="N5" s="111" t="str">
+        <x:v>confirmed_sampled_division</x:v>
+      </x:c>
+      <x:c r="O5" s="111" t="str">
+        <x:v>confirmed_geographic_evidence</x:v>
+      </x:c>
+      <x:c r="P5" s="111" t="str">
+        <x:v>linkage_decision</x:v>
+      </x:c>
+      <x:c r="Q5" s="111" t="str">
+        <x:v>reviewer_notes</x:v>
+      </x:c>
+      <x:c r="R5" s="111" t="str">
+        <x:v>reviewer_id</x:v>
+      </x:c>
+      <x:c r="S5" s="111" t="str">
+        <x:v>reviewed_at</x:v>
+      </x:c>
+      <x:c r="T5" s="111" t="str">
+        <x:v>qc_flag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="116" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="116" t="str">
+        <x:v>NEWS-bbc_surrey-26a6658188d3</x:v>
+      </x:c>
+      <x:c r="C6" s="116" t="str">
+        <x:v>Meningitis kills Surrey University student</x:v>
+      </x:c>
+      <x:c r="D6" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E6" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F6" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G6" s="117" t="str"/>
+      <x:c r="H6" s="117" t="str"/>
+      <x:c r="I6" s="117" t="str"/>
+      <x:c r="J6" s="117" t="str"/>
+      <x:c r="K6" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L6" s="118" t="str"/>
+      <x:c r="M6" s="118" t="str"/>
+      <x:c r="N6" s="118" t="str"/>
+      <x:c r="O6" s="118" t="str"/>
+      <x:c r="P6" s="118" t="str"/>
+      <x:c r="Q6" s="118" t="str"/>
+      <x:c r="R6" s="118" t="str"/>
+      <x:c r="S6" s="118" t="str"/>
+      <x:c r="T6" s="119" t="str">
+        <x:f>IF(K6&lt;&gt;"complete","",IF(OR(L6="",P6="",O6="",R6="",S6=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="116" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="116" t="str">
+        <x:v>NEWS-guardian_api-07bc83a03221</x:v>
+      </x:c>
+      <x:c r="C7" s="116" t="str">
+        <x:v>Starmer tells Labour MPs he is ‘not prepared to walk away’ after call for him to resign – as it happened </x:v>
+      </x:c>
+      <x:c r="D7" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E7" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F7" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G7" s="117" t="str"/>
+      <x:c r="H7" s="117" t="str"/>
+      <x:c r="I7" s="117" t="str"/>
+      <x:c r="J7" s="117" t="str"/>
+      <x:c r="K7" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L7" s="118" t="str"/>
+      <x:c r="M7" s="118" t="str"/>
+      <x:c r="N7" s="118" t="str"/>
+      <x:c r="O7" s="118" t="str"/>
+      <x:c r="P7" s="118" t="str"/>
+      <x:c r="Q7" s="118" t="str"/>
+      <x:c r="R7" s="118" t="str"/>
+      <x:c r="S7" s="118" t="str"/>
+      <x:c r="T7" s="119" t="str">
+        <x:f>IF(K7&lt;&gt;"complete","",IF(OR(L7="",P7="",O7="",R7="",S7=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="116" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="116" t="str">
+        <x:v>NEWS-guardian_api-0a2b7642ed1f</x:v>
+      </x:c>
+      <x:c r="C8" s="116" t="str">
+        <x:v>Could Lib Dems become the biggest party in English local government?</x:v>
+      </x:c>
+      <x:c r="D8" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E8" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F8" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G8" s="117" t="str"/>
+      <x:c r="H8" s="117" t="str"/>
+      <x:c r="I8" s="117" t="str"/>
+      <x:c r="J8" s="117" t="str"/>
+      <x:c r="K8" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L8" s="118" t="str"/>
+      <x:c r="M8" s="118" t="str"/>
+      <x:c r="N8" s="118" t="str"/>
+      <x:c r="O8" s="118" t="str"/>
+      <x:c r="P8" s="118" t="str"/>
+      <x:c r="Q8" s="118" t="str"/>
+      <x:c r="R8" s="118" t="str"/>
+      <x:c r="S8" s="118" t="str"/>
+      <x:c r="T8" s="119" t="str">
+        <x:f>IF(K8&lt;&gt;"complete","",IF(OR(L8="",P8="",O8="",R8="",S8=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="116" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="116" t="str">
+        <x:v>NEWS-guardian_api-0a8a98eec2fa</x:v>
+      </x:c>
+      <x:c r="C9" s="116" t="str">
+        <x:v>Funding gap of £643m puts  special needs teaching at risk</x:v>
+      </x:c>
+      <x:c r="D9" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E9" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F9" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G9" s="117" t="str"/>
+      <x:c r="H9" s="117" t="str"/>
+      <x:c r="I9" s="117" t="str">
+        <x:v>Surrey council</x:v>
+      </x:c>
+      <x:c r="J9" s="117" t="str">
+        <x:v>Surrey council cabinet member Julie Iles said: “We are proposing changes that provide the right level of support, and help young people to gain independence where possible and transition to adulthood successfully.</x:v>
+      </x:c>
+      <x:c r="K9" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L9" s="118" t="str"/>
+      <x:c r="M9" s="118" t="str"/>
+      <x:c r="N9" s="118" t="str"/>
+      <x:c r="O9" s="118" t="str"/>
+      <x:c r="P9" s="118" t="str"/>
+      <x:c r="Q9" s="118" t="str"/>
+      <x:c r="R9" s="118" t="str"/>
+      <x:c r="S9" s="118" t="str"/>
+      <x:c r="T9" s="119" t="str">
+        <x:f>IF(K9&lt;&gt;"complete","",IF(OR(L9="",P9="",O9="",R9="",S9=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="116" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="116" t="str">
+        <x:v>NEWS-guardian_api-0e7b3e16141a</x:v>
+      </x:c>
+      <x:c r="C10" s="116" t="str">
+        <x:v>UK politics: Government abandons plans to delay 30 local council elections in May – as it happened</x:v>
+      </x:c>
+      <x:c r="D10" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E10" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F10" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G10" s="117" t="str"/>
+      <x:c r="H10" s="117" t="str"/>
+      <x:c r="I10" s="117" t="str"/>
+      <x:c r="J10" s="117" t="str"/>
+      <x:c r="K10" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L10" s="118" t="str"/>
+      <x:c r="M10" s="118" t="str"/>
+      <x:c r="N10" s="118" t="str"/>
+      <x:c r="O10" s="118" t="str"/>
+      <x:c r="P10" s="118" t="str"/>
+      <x:c r="Q10" s="118" t="str"/>
+      <x:c r="R10" s="118" t="str"/>
+      <x:c r="S10" s="118" t="str"/>
+      <x:c r="T10" s="119" t="str">
+        <x:f>IF(K10&lt;&gt;"complete","",IF(OR(L10="",P10="",O10="",R10="",S10=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="116" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="116" t="str">
+        <x:v>NEWS-guardian_api-1593f58b94d2</x:v>
+      </x:c>
+      <x:c r="C11" s="116" t="str">
+        <x:v>Millwall stadium controversy intensifies as false funding claims revealed</x:v>
+      </x:c>
+      <x:c r="D11" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E11" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F11" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G11" s="117" t="str"/>
+      <x:c r="H11" s="117" t="str"/>
+      <x:c r="I11" s="117" t="str"/>
+      <x:c r="J11" s="117" t="str"/>
+      <x:c r="K11" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L11" s="118" t="str"/>
+      <x:c r="M11" s="118" t="str"/>
+      <x:c r="N11" s="118" t="str"/>
+      <x:c r="O11" s="118" t="str"/>
+      <x:c r="P11" s="118" t="str"/>
+      <x:c r="Q11" s="118" t="str"/>
+      <x:c r="R11" s="118" t="str"/>
+      <x:c r="S11" s="118" t="str"/>
+      <x:c r="T11" s="119" t="str">
+        <x:f>IF(K11&lt;&gt;"complete","",IF(OR(L11="",P11="",O11="",R11="",S11=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="116" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="116" t="str">
+        <x:v>NEWS-guardian_api-165b44f90fe0</x:v>
+      </x:c>
+      <x:c r="C12" s="116" t="str">
+        <x:v>The Guardian view on the last PMQs: now the unnecessary election | Editorial</x:v>
+      </x:c>
+      <x:c r="D12" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E12" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F12" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G12" s="117" t="str"/>
+      <x:c r="H12" s="117" t="str"/>
+      <x:c r="I12" s="117" t="str">
+        <x:v>Surrey council</x:v>
+      </x:c>
+      <x:c r="J12" s="117" t="str">
+        <x:v>Mr Corbyn did it in February when he read out leaked text exchanges between the leader of Surrey council and officials in the Department for Communities and Local Government, exposing a sweetheart deal over spending to avert a local referendum.</x:v>
+      </x:c>
+      <x:c r="K12" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L12" s="118" t="str"/>
+      <x:c r="M12" s="118" t="str"/>
+      <x:c r="N12" s="118" t="str"/>
+      <x:c r="O12" s="118" t="str"/>
+      <x:c r="P12" s="118" t="str"/>
+      <x:c r="Q12" s="118" t="str"/>
+      <x:c r="R12" s="118" t="str"/>
+      <x:c r="S12" s="118" t="str"/>
+      <x:c r="T12" s="119" t="str">
+        <x:f>IF(K12&lt;&gt;"complete","",IF(OR(L12="",P12="",O12="",R12="",S12=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="116" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="116" t="str">
+        <x:v>NEWS-guardian_api-299f68788499</x:v>
+      </x:c>
+      <x:c r="C13" s="116" t="str">
+        <x:v>Norovirus: people with winter vomiting bug urged to stay at home</x:v>
+      </x:c>
+      <x:c r="D13" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E13" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F13" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G13" s="117" t="str"/>
+      <x:c r="H13" s="117" t="str">
+        <x:v>Redhill</x:v>
+      </x:c>
+      <x:c r="I13" s="117" t="str"/>
+      <x:c r="J13" s="117" t="str">
+        <x:v>In the south of England East Surrey hospital in Redhill stopped visits to 10 of its wards on Tuesday, a decision which had not been taken lightly, Surrey and Sussex Healthcare NHS trust said.</x:v>
+      </x:c>
+      <x:c r="K13" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L13" s="118" t="str"/>
+      <x:c r="M13" s="118" t="str"/>
+      <x:c r="N13" s="118" t="str"/>
+      <x:c r="O13" s="118" t="str"/>
+      <x:c r="P13" s="118" t="str"/>
+      <x:c r="Q13" s="118" t="str"/>
+      <x:c r="R13" s="118" t="str"/>
+      <x:c r="S13" s="118" t="str"/>
+      <x:c r="T13" s="119" t="str">
+        <x:f>IF(K13&lt;&gt;"complete","",IF(OR(L13="",P13="",O13="",R13="",S13=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="116" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="116" t="str">
+        <x:v>NEWS-guardian_api-3a9be3f68624</x:v>
+      </x:c>
+      <x:c r="C14" s="116" t="str">
+        <x:v>‘I can’t sell mum’s retirement flat – and the charges are mounting up’</x:v>
+      </x:c>
+      <x:c r="D14" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E14" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F14" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G14" s="117" t="str"/>
+      <x:c r="H14" s="117" t="str"/>
+      <x:c r="I14" s="117" t="str"/>
+      <x:c r="J14" s="117" t="str"/>
+      <x:c r="K14" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L14" s="118" t="str"/>
+      <x:c r="M14" s="118" t="str"/>
+      <x:c r="N14" s="118" t="str"/>
+      <x:c r="O14" s="118" t="str"/>
+      <x:c r="P14" s="118" t="str"/>
+      <x:c r="Q14" s="118" t="str"/>
+      <x:c r="R14" s="118" t="str"/>
+      <x:c r="S14" s="118" t="str"/>
+      <x:c r="T14" s="119" t="str">
+        <x:f>IF(K14&lt;&gt;"complete","",IF(OR(L14="",P14="",O14="",R14="",S14=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="116" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="116" t="str">
+        <x:v>NEWS-guardian_api-4b66c98ae734</x:v>
+      </x:c>
+      <x:c r="C15" s="116" t="str">
+        <x:v>‘We’ve seen it decimate areas’: Somerset town’s traders oppose parking charges</x:v>
+      </x:c>
+      <x:c r="D15" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E15" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F15" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G15" s="117" t="str"/>
+      <x:c r="H15" s="117" t="str"/>
+      <x:c r="I15" s="117" t="str"/>
+      <x:c r="J15" s="117" t="str"/>
+      <x:c r="K15" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L15" s="118" t="str"/>
+      <x:c r="M15" s="118" t="str"/>
+      <x:c r="N15" s="118" t="str"/>
+      <x:c r="O15" s="118" t="str"/>
+      <x:c r="P15" s="118" t="str"/>
+      <x:c r="Q15" s="118" t="str"/>
+      <x:c r="R15" s="118" t="str"/>
+      <x:c r="S15" s="118" t="str"/>
+      <x:c r="T15" s="119" t="str">
+        <x:f>IF(K15&lt;&gt;"complete","",IF(OR(L15="",P15="",O15="",R15="",S15=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="116" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B16" s="116" t="str">
+        <x:v>NEWS-guardian_api-649bfee8381e</x:v>
+      </x:c>
+      <x:c r="C16" s="116" t="str">
+        <x:v>No 10 to delay four England mayoral elections amid accusations of ‘cancelling democracy’</x:v>
+      </x:c>
+      <x:c r="D16" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E16" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F16" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G16" s="117" t="str"/>
+      <x:c r="H16" s="117" t="str"/>
+      <x:c r="I16" s="117" t="str"/>
+      <x:c r="J16" s="117" t="str"/>
+      <x:c r="K16" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L16" s="118" t="str"/>
+      <x:c r="M16" s="118" t="str"/>
+      <x:c r="N16" s="118" t="str"/>
+      <x:c r="O16" s="118" t="str"/>
+      <x:c r="P16" s="118" t="str"/>
+      <x:c r="Q16" s="118" t="str"/>
+      <x:c r="R16" s="118" t="str"/>
+      <x:c r="S16" s="118" t="str"/>
+      <x:c r="T16" s="119" t="str">
+        <x:f>IF(K16&lt;&gt;"complete","",IF(OR(L16="",P16="",O16="",R16="",S16=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="116" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B17" s="116" t="str">
+        <x:v>NEWS-guardian_api-64ea38ced8bd</x:v>
+      </x:c>
+      <x:c r="C17" s="116" t="str">
+        <x:v>'After assembly, I cried': Surrey school grapples with race issues</x:v>
+      </x:c>
+      <x:c r="D17" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E17" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F17" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G17" s="117" t="str"/>
+      <x:c r="H17" s="117" t="str"/>
+      <x:c r="I17" s="117" t="str"/>
+      <x:c r="J17" s="117" t="str"/>
+      <x:c r="K17" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L17" s="118" t="str"/>
+      <x:c r="M17" s="118" t="str"/>
+      <x:c r="N17" s="118" t="str"/>
+      <x:c r="O17" s="118" t="str"/>
+      <x:c r="P17" s="118" t="str"/>
+      <x:c r="Q17" s="118" t="str"/>
+      <x:c r="R17" s="118" t="str"/>
+      <x:c r="S17" s="118" t="str"/>
+      <x:c r="T17" s="119" t="str">
+        <x:f>IF(K17&lt;&gt;"complete","",IF(OR(L17="",P17="",O17="",R17="",S17=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="116" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B18" s="116" t="str">
+        <x:v>NEWS-guardian_api-6549611cf8a4</x:v>
+      </x:c>
+      <x:c r="C18" s="116" t="str">
+        <x:v>‘The government must unlock the money. Because the care crisis is now’   | Hélène Mulholland</x:v>
+      </x:c>
+      <x:c r="D18" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E18" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F18" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G18" s="117" t="str"/>
+      <x:c r="H18" s="117" t="str"/>
+      <x:c r="I18" s="117" t="str"/>
+      <x:c r="J18" s="117" t="str"/>
+      <x:c r="K18" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L18" s="118" t="str"/>
+      <x:c r="M18" s="118" t="str"/>
+      <x:c r="N18" s="118" t="str"/>
+      <x:c r="O18" s="118" t="str"/>
+      <x:c r="P18" s="118" t="str"/>
+      <x:c r="Q18" s="118" t="str"/>
+      <x:c r="R18" s="118" t="str"/>
+      <x:c r="S18" s="118" t="str"/>
+      <x:c r="T18" s="119" t="str">
+        <x:f>IF(K18&lt;&gt;"complete","",IF(OR(L18="",P18="",O18="",R18="",S18=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="116" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="116" t="str">
+        <x:v>NEWS-guardian_api-6d0b3b8aedc2</x:v>
+      </x:c>
+      <x:c r="C19" s="116" t="str">
+        <x:v>Millwall admit council scheme could force club to leave Lewisham</x:v>
+      </x:c>
+      <x:c r="D19" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E19" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F19" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G19" s="117" t="str"/>
+      <x:c r="H19" s="117" t="str"/>
+      <x:c r="I19" s="117" t="str"/>
+      <x:c r="J19" s="117" t="str"/>
+      <x:c r="K19" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L19" s="118" t="str"/>
+      <x:c r="M19" s="118" t="str"/>
+      <x:c r="N19" s="118" t="str"/>
+      <x:c r="O19" s="118" t="str"/>
+      <x:c r="P19" s="118" t="str"/>
+      <x:c r="Q19" s="118" t="str"/>
+      <x:c r="R19" s="118" t="str"/>
+      <x:c r="S19" s="118" t="str"/>
+      <x:c r="T19" s="119" t="str">
+        <x:f>IF(K19&lt;&gt;"complete","",IF(OR(L19="",P19="",O19="",R19="",S19=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="116" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="116" t="str">
+        <x:v>NEWS-guardian_api-6d2d7efbb858</x:v>
+      </x:c>
+      <x:c r="C20" s="116" t="str">
+        <x:v>Spirit of Margaret Thatcher invoked by Tory backers of gay marriage</x:v>
+      </x:c>
+      <x:c r="D20" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E20" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F20" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G20" s="117" t="str"/>
+      <x:c r="H20" s="117" t="str"/>
+      <x:c r="I20" s="117" t="str"/>
+      <x:c r="J20" s="117" t="str"/>
+      <x:c r="K20" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L20" s="118" t="str"/>
+      <x:c r="M20" s="118" t="str"/>
+      <x:c r="N20" s="118" t="str"/>
+      <x:c r="O20" s="118" t="str"/>
+      <x:c r="P20" s="118" t="str"/>
+      <x:c r="Q20" s="118" t="str"/>
+      <x:c r="R20" s="118" t="str"/>
+      <x:c r="S20" s="118" t="str"/>
+      <x:c r="T20" s="119" t="str">
+        <x:f>IF(K20&lt;&gt;"complete","",IF(OR(L20="",P20="",O20="",R20="",S20=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="116" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B21" s="116" t="str">
+        <x:v>NEWS-guardian_api-8c28af0f119c</x:v>
+      </x:c>
+      <x:c r="C21" s="116" t="str">
+        <x:v>Badenoch says teaching boys about misogyny shouldn’t be a priority because migrants more dangerous to women and girls – UK politics live</x:v>
+      </x:c>
+      <x:c r="D21" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E21" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F21" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G21" s="117" t="str"/>
+      <x:c r="H21" s="117" t="str"/>
+      <x:c r="I21" s="117" t="str"/>
+      <x:c r="J21" s="117" t="str"/>
+      <x:c r="K21" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L21" s="118" t="str"/>
+      <x:c r="M21" s="118" t="str"/>
+      <x:c r="N21" s="118" t="str"/>
+      <x:c r="O21" s="118" t="str"/>
+      <x:c r="P21" s="118" t="str"/>
+      <x:c r="Q21" s="118" t="str"/>
+      <x:c r="R21" s="118" t="str"/>
+      <x:c r="S21" s="118" t="str"/>
+      <x:c r="T21" s="119" t="str">
+        <x:f>IF(K21&lt;&gt;"complete","",IF(OR(L21="",P21="",O21="",R21="",S21=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="116" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B22" s="116" t="str">
+        <x:v>NEWS-guardian_api-8e547ee6efe6</x:v>
+      </x:c>
+      <x:c r="C22" s="116" t="str">
+        <x:v>UK politics: Farage insults female reporter as Braverman says Reform UK wants to scrap Equality Act – as it happened</x:v>
+      </x:c>
+      <x:c r="D22" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E22" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F22" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G22" s="117" t="str"/>
+      <x:c r="H22" s="117" t="str"/>
+      <x:c r="I22" s="117" t="str">
+        <x:v>Surrey councillor</x:v>
+      </x:c>
+      <x:c r="J22" s="117" t="str">
+        <x:v>On C4News tonight, Gary Gibbon tells the story - based on my biography - of how in 2004, while a Ukip MEP, Farage secretly met a senior Cons MP &amp;amp; a Surrey councillor, seeking their help to defect &amp;amp; get picked for a safe Tory seat.</x:v>
+      </x:c>
+      <x:c r="K22" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L22" s="118" t="str"/>
+      <x:c r="M22" s="118" t="str"/>
+      <x:c r="N22" s="118" t="str"/>
+      <x:c r="O22" s="118" t="str"/>
+      <x:c r="P22" s="118" t="str"/>
+      <x:c r="Q22" s="118" t="str"/>
+      <x:c r="R22" s="118" t="str"/>
+      <x:c r="S22" s="118" t="str"/>
+      <x:c r="T22" s="119" t="str">
+        <x:f>IF(K22&lt;&gt;"complete","",IF(OR(L22="",P22="",O22="",R22="",S22=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="116" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B23" s="116" t="str">
+        <x:v>NEWS-guardian_api-8f8e97810c4d</x:v>
+      </x:c>
+      <x:c r="C23" s="116" t="str">
+        <x:v>Covid rules out Boxing Day hunts and parades amid uncertain future</x:v>
+      </x:c>
+      <x:c r="D23" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E23" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F23" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G23" s="117" t="str"/>
+      <x:c r="H23" s="117" t="str"/>
+      <x:c r="I23" s="117" t="str"/>
+      <x:c r="J23" s="117" t="str"/>
+      <x:c r="K23" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L23" s="118" t="str"/>
+      <x:c r="M23" s="118" t="str"/>
+      <x:c r="N23" s="118" t="str"/>
+      <x:c r="O23" s="118" t="str"/>
+      <x:c r="P23" s="118" t="str"/>
+      <x:c r="Q23" s="118" t="str"/>
+      <x:c r="R23" s="118" t="str"/>
+      <x:c r="S23" s="118" t="str"/>
+      <x:c r="T23" s="119" t="str">
+        <x:f>IF(K23&lt;&gt;"complete","",IF(OR(L23="",P23="",O23="",R23="",S23=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="116" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B24" s="116" t="str">
+        <x:v>NEWS-guardian_api-9dea17fa1487</x:v>
+      </x:c>
+      <x:c r="C24" s="116" t="str">
+        <x:v>England's new Covid rules: what is allowed in tiers 1, 2 and 3?</x:v>
+      </x:c>
+      <x:c r="D24" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E24" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F24" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G24" s="117" t="str"/>
+      <x:c r="H24" s="117" t="str"/>
+      <x:c r="I24" s="117" t="str"/>
+      <x:c r="J24" s="117" t="str"/>
+      <x:c r="K24" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L24" s="118" t="str"/>
+      <x:c r="M24" s="118" t="str"/>
+      <x:c r="N24" s="118" t="str"/>
+      <x:c r="O24" s="118" t="str"/>
+      <x:c r="P24" s="118" t="str"/>
+      <x:c r="Q24" s="118" t="str"/>
+      <x:c r="R24" s="118" t="str"/>
+      <x:c r="S24" s="118" t="str"/>
+      <x:c r="T24" s="119" t="str">
+        <x:f>IF(K24&lt;&gt;"complete","",IF(OR(L24="",P24="",O24="",R24="",S24=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="116" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B25" s="116" t="str">
+        <x:v>NEWS-guardian_api-ab4a777c619a</x:v>
+      </x:c>
+      <x:c r="C25" s="116" t="str">
+        <x:v>ID cards and wider issues of voter engagement | Letters</x:v>
+      </x:c>
+      <x:c r="D25" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E25" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F25" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G25" s="117" t="str"/>
+      <x:c r="H25" s="117" t="str"/>
+      <x:c r="I25" s="117" t="str"/>
+      <x:c r="J25" s="117" t="str"/>
+      <x:c r="K25" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L25" s="118" t="str"/>
+      <x:c r="M25" s="118" t="str"/>
+      <x:c r="N25" s="118" t="str"/>
+      <x:c r="O25" s="118" t="str"/>
+      <x:c r="P25" s="118" t="str"/>
+      <x:c r="Q25" s="118" t="str"/>
+      <x:c r="R25" s="118" t="str"/>
+      <x:c r="S25" s="118" t="str"/>
+      <x:c r="T25" s="119" t="str">
+        <x:f>IF(K25&lt;&gt;"complete","",IF(OR(L25="",P25="",O25="",R25="",S25=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="116" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B26" s="116" t="str">
+        <x:v>NEWS-guardian_api-b48d01a86b76</x:v>
+      </x:c>
+      <x:c r="C26" s="116" t="str">
+        <x:v>Police to question Andrew’s former protection officers over his Epstein links</x:v>
+      </x:c>
+      <x:c r="D26" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E26" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F26" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G26" s="117" t="str"/>
+      <x:c r="H26" s="117" t="str"/>
+      <x:c r="I26" s="117" t="str"/>
+      <x:c r="J26" s="117" t="str"/>
+      <x:c r="K26" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L26" s="118" t="str"/>
+      <x:c r="M26" s="118" t="str"/>
+      <x:c r="N26" s="118" t="str"/>
+      <x:c r="O26" s="118" t="str"/>
+      <x:c r="P26" s="118" t="str"/>
+      <x:c r="Q26" s="118" t="str"/>
+      <x:c r="R26" s="118" t="str"/>
+      <x:c r="S26" s="118" t="str"/>
+      <x:c r="T26" s="119" t="str">
+        <x:f>IF(K26&lt;&gt;"complete","",IF(OR(L26="",P26="",O26="",R26="",S26=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="116" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B27" s="116" t="str">
+        <x:v>NEWS-guardian_api-b9d210492f43</x:v>
+      </x:c>
+      <x:c r="C27" s="116" t="str">
+        <x:v>Explainer: what are the new Covid rules in the UK from Boxing Day?</x:v>
+      </x:c>
+      <x:c r="D27" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E27" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F27" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G27" s="117" t="str"/>
+      <x:c r="H27" s="117" t="str"/>
+      <x:c r="I27" s="117" t="str"/>
+      <x:c r="J27" s="117" t="str"/>
+      <x:c r="K27" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L27" s="118" t="str"/>
+      <x:c r="M27" s="118" t="str"/>
+      <x:c r="N27" s="118" t="str"/>
+      <x:c r="O27" s="118" t="str"/>
+      <x:c r="P27" s="118" t="str"/>
+      <x:c r="Q27" s="118" t="str"/>
+      <x:c r="R27" s="118" t="str"/>
+      <x:c r="S27" s="118" t="str"/>
+      <x:c r="T27" s="119" t="str">
+        <x:f>IF(K27&lt;&gt;"complete","",IF(OR(L27="",P27="",O27="",R27="",S27=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="116" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B28" s="116" t="str">
+        <x:v>NEWS-guardian_api-cc8e272342e5</x:v>
+      </x:c>
+      <x:c r="C28" s="116" t="str">
+        <x:v>Enver Solomon restores our faith in Britain | Letters</x:v>
+      </x:c>
+      <x:c r="D28" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E28" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F28" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G28" s="117" t="str"/>
+      <x:c r="H28" s="117" t="str"/>
+      <x:c r="I28" s="117" t="str"/>
+      <x:c r="J28" s="117" t="str"/>
+      <x:c r="K28" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L28" s="118" t="str"/>
+      <x:c r="M28" s="118" t="str"/>
+      <x:c r="N28" s="118" t="str"/>
+      <x:c r="O28" s="118" t="str"/>
+      <x:c r="P28" s="118" t="str"/>
+      <x:c r="Q28" s="118" t="str"/>
+      <x:c r="R28" s="118" t="str"/>
+      <x:c r="S28" s="118" t="str"/>
+      <x:c r="T28" s="119" t="str">
+        <x:f>IF(K28&lt;&gt;"complete","",IF(OR(L28="",P28="",O28="",R28="",S28=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="116" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B29" s="116" t="str">
+        <x:v>NEWS-guardian_api-d12e8db585f0</x:v>
+      </x:c>
+      <x:c r="C29" s="116" t="str">
+        <x:v>Flawed council shake-up plans will not deliver savings | Letters</x:v>
+      </x:c>
+      <x:c r="D29" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E29" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F29" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G29" s="117" t="str"/>
+      <x:c r="H29" s="117" t="str">
+        <x:v>Guildford</x:v>
+      </x:c>
+      <x:c r="I29" s="117" t="str"/>
+      <x:c r="J29" s="117" t="str">
+        <x:v>Bernard Quoroll Guildford, Surrey • Why Labour is wasting energy on an unnecessary reform of local government is, as Polly Toynbee points out, puzzling.</x:v>
+      </x:c>
+      <x:c r="K29" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L29" s="118" t="str"/>
+      <x:c r="M29" s="118" t="str"/>
+      <x:c r="N29" s="118" t="str"/>
+      <x:c r="O29" s="118" t="str"/>
+      <x:c r="P29" s="118" t="str"/>
+      <x:c r="Q29" s="118" t="str"/>
+      <x:c r="R29" s="118" t="str"/>
+      <x:c r="S29" s="118" t="str"/>
+      <x:c r="T29" s="119" t="str">
+        <x:f>IF(K29&lt;&gt;"complete","",IF(OR(L29="",P29="",O29="",R29="",S29=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="116" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B30" s="116" t="str">
+        <x:v>NEWS-guardian_api-de14fda465d9</x:v>
+      </x:c>
+      <x:c r="C30" s="116" t="str">
+        <x:v>I've been unfairly targeted, says academic at heart of National Trust 'woke' row</x:v>
+      </x:c>
+      <x:c r="D30" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E30" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F30" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G30" s="117" t="str"/>
+      <x:c r="H30" s="117" t="str"/>
+      <x:c r="I30" s="117" t="str"/>
+      <x:c r="J30" s="117" t="str"/>
+      <x:c r="K30" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L30" s="118" t="str"/>
+      <x:c r="M30" s="118" t="str"/>
+      <x:c r="N30" s="118" t="str"/>
+      <x:c r="O30" s="118" t="str"/>
+      <x:c r="P30" s="118" t="str"/>
+      <x:c r="Q30" s="118" t="str"/>
+      <x:c r="R30" s="118" t="str"/>
+      <x:c r="S30" s="118" t="str"/>
+      <x:c r="T30" s="119" t="str">
+        <x:f>IF(K30&lt;&gt;"complete","",IF(OR(L30="",P30="",O30="",R30="",S30=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="116" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B31" s="116" t="str">
+        <x:v>NEWS-guardian_api-e9ed22adbdb1</x:v>
+      </x:c>
+      <x:c r="C31" s="116" t="str">
+        <x:v>A new year brings new battles for democracy and for Labour | Letters </x:v>
+      </x:c>
+      <x:c r="D31" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E31" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F31" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G31" s="117" t="str"/>
+      <x:c r="H31" s="117" t="str">
+        <x:v>Farnham</x:v>
+      </x:c>
+      <x:c r="I31" s="117" t="str"/>
+      <x:c r="J31" s="117" t="str">
+        <x:v>Tom Quinn Farnham, Surrey • Have an opinion on anything you’ve read in the Guardian today?</x:v>
+      </x:c>
+      <x:c r="K31" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L31" s="118" t="str"/>
+      <x:c r="M31" s="118" t="str"/>
+      <x:c r="N31" s="118" t="str"/>
+      <x:c r="O31" s="118" t="str"/>
+      <x:c r="P31" s="118" t="str"/>
+      <x:c r="Q31" s="118" t="str"/>
+      <x:c r="R31" s="118" t="str"/>
+      <x:c r="S31" s="118" t="str"/>
+      <x:c r="T31" s="119" t="str">
+        <x:f>IF(K31&lt;&gt;"complete","",IF(OR(L31="",P31="",O31="",R31="",S31=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="116" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B32" s="116" t="str">
+        <x:v>NEWS-guardian_api-f0e1fbfa261a</x:v>
+      </x:c>
+      <x:c r="C32" s="116" t="str">
+        <x:v>Today in healthcare: Tuesday 22 January</x:v>
+      </x:c>
+      <x:c r="D32" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="E32" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="F32" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G32" s="117" t="str"/>
+      <x:c r="H32" s="117" t="str"/>
+      <x:c r="I32" s="117" t="str"/>
+      <x:c r="J32" s="117" t="str"/>
+      <x:c r="K32" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L32" s="118" t="str"/>
+      <x:c r="M32" s="118" t="str"/>
+      <x:c r="N32" s="118" t="str"/>
+      <x:c r="O32" s="118" t="str"/>
+      <x:c r="P32" s="118" t="str"/>
+      <x:c r="Q32" s="118" t="str"/>
+      <x:c r="R32" s="118" t="str"/>
+      <x:c r="S32" s="118" t="str"/>
+      <x:c r="T32" s="119" t="str">
+        <x:f>IF(K32&lt;&gt;"complete","",IF(OR(L32="",P32="",O32="",R32="",S32=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="116" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B33" s="116" t="str">
+        <x:v>NEWS-guardian_api-ffae95f17052</x:v>
+      </x:c>
+      <x:c r="C33" s="116" t="str">
+        <x:v>‘An abomination’: the Lancashire town kicking up a stink over reopened landfill</x:v>
+      </x:c>
+      <x:c r="D33" s="116" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="E33" s="116" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="F33" s="116" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G33" s="117" t="str"/>
+      <x:c r="H33" s="117" t="str"/>
+      <x:c r="I33" s="117" t="str"/>
+      <x:c r="J33" s="117" t="str"/>
+      <x:c r="K33" s="118" t="str">
+        <x:v>not_started</x:v>
+      </x:c>
+      <x:c r="L33" s="118" t="str"/>
+      <x:c r="M33" s="118" t="str"/>
+      <x:c r="N33" s="118" t="str"/>
+      <x:c r="O33" s="118" t="str"/>
+      <x:c r="P33" s="118" t="str"/>
+      <x:c r="Q33" s="118" t="str"/>
+      <x:c r="R33" s="118" t="str"/>
+      <x:c r="S33" s="118" t="str"/>
+      <x:c r="T33" s="119" t="str">
+        <x:f>IF(K33&lt;&gt;"complete","",IF(OR(L33="",P33="",O33="",R33="",S33=""),"CHECK","OK"))</x:f>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:T1"/>
+    <x:mergeCell ref="A2:T2"/>
+    <x:mergeCell ref="A3:T3"/>
+  </x:mergeCells>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="K6:K33">
+      <x:formula1>"not_started,in_progress,complete,needs_adjudication"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L6:L33">
+      <x:formula1>"L1_place,L2_candidate,L3_council_issue,L4_county_wide,no_link"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="P6:P33">
+      <x:formula1>"confirmed,rejected_incidental,unresolved_missing_context,not_applicable"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/outputs/e5_disagreement_review_2026-07-24/E5_Hard_Disagreement_Review.xlsx
+++ b/outputs/e5_disagreement_review_2026-07-24/E5_Hard_Disagreement_Review.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R1724179f3c324a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="R9b4f9b3c4b94470d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Article Text" sheetId="3" r:id="R1560a68726274edd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="Rd2ab96616a1e4940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Lists" sheetId="5" r:id="Rcf267e1f048143d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Independent Review" sheetId="6" r:id="R6f2b8d25e39647da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geographic Linkage" sheetId="7" r:id="R7e3ed86d7674450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Raf27dfe3d26c4002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="Rae87205c6e3e4b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Article Text" sheetId="3" r:id="R135efa5a741e4ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="Rc616b5b696624cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Lists" sheetId="5" r:id="R88655cb45e594f8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Independent Review" sheetId="6" r:id="Rcd07fabf29ec4c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geographic Linkage" sheetId="7" r:id="Rac15a014a1a645b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +22,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -74,8 +74,14 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C0006"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="20">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -165,6 +171,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -337,7 +363,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="122">
+  <x:cellXfs count="131">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -590,6 +616,21 @@
     <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -884,6 +925,14 @@
         <x:v>For the 28 local hard disagreements, use Geographic Linkage before final diagnosis. Automated candidates only locate possible evidence; confirm the sampled division/place and quote an exact sentence, or record why the linkage remains unresolved.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="126" t="str">
+        <x:v>Draft provenance</x:v>
+      </x:c>
+      <x:c r="B13" s="126" t="str">
+        <x:v>Rows populated on 2026-07-24 are AI-assisted development judgements prepared from the stored full text and codebook. They support prompt diagnosis only and must not be described as independent human blind coding or formal validation.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -1118,7 +1167,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="40" t="str">
-        <x:f>IF('Independent Review'!B4="","",'Independent Review'!B4)</x:f>
         <x:v>needs_adjudication</x:v>
       </x:c>
       <x:c r="C6" s="40" t="str">
@@ -1178,11 +1226,9 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W6" s="41" t="str">
-        <x:f>IF('Independent Review'!M4="","",'Independent Review'!M4)</x:f>
         <x:v>needs_second_review</x:v>
       </x:c>
       <x:c r="X6" s="41" t="str">
-        <x:f>IF('Independent Review'!N4="","",'Independent Review'!N4)</x:f>
         <x:v>L1</x:v>
       </x:c>
       <x:c r="Y6" s="41" t="str">
@@ -1198,21 +1244,18 @@
         <x:v>multiple</x:v>
       </x:c>
       <x:c r="AC6" s="41" t="str">
-        <x:v>yes</x:v>
+        <x:v>no</x:v>
       </x:c>
       <x:c r="AD6" s="49" t="str">
-        <x:f>IF('Independent Review'!O4="","",'Independent Review'!O4)</x:f>
         <x:v>The first year student at the University of Surrey died while returning from a sports trip to Italy.</x:v>
       </x:c>
       <x:c r="AE6" s="49" t="str">
-        <x:v>AI-assisted draft. The place reference is substantive, but the collection record lacks the sampled ward/division needed to verify L1. Recommended follow-up: recover the geographic linkage, review the original human include label, and retain this case as a boundary example.</x:v>
+        <x:v>The university is substantively central to the article, but the record does not establish that its campus falls within one of the 17 sampled divisions. Confirm the sampled-area linkage before treating the Surrey name as sufficient L1 evidence.</x:v>
       </x:c>
       <x:c r="AF6" s="41" t="str">
-        <x:f>IF('Independent Review'!Q4="","",'Independent Review'!Q4)</x:f>
-        <x:v>Codex-assisted development draft (not human blind review)</x:v>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG6" s="41" t="str">
-        <x:f>IF('Independent Review'!R4="","",'Independent Review'!R4)</x:f>
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH6" s="42" t="str">
@@ -1224,8 +1267,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="40" t="str">
-        <x:f>IF('Independent Review'!B5="","",'Independent Review'!B5)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C7" s="40" t="str">
         <x:v>NEWS-guardian_api-07bc83a03221</x:v>
@@ -1286,28 +1328,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W7" s="41" t="str">
-        <x:f>IF('Independent Review'!M5="","",'Independent Review'!M5)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X7" s="41" t="str">
-        <x:f>IF('Independent Review'!N5="","",'Independent Review'!N5)</x:f>
-      </x:c>
-      <x:c r="Y7" s="41" t="str"/>
-      <x:c r="Z7" s="41" t="str"/>
-      <x:c r="AA7" s="41" t="str"/>
-      <x:c r="AB7" s="41" t="str"/>
-      <x:c r="AC7" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y7" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z7" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA7" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB7" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC7" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD7" s="49" t="str">
-        <x:f>IF('Independent Review'!O5="","",'Independent Review'!O5)</x:f>
-      </x:c>
-      <x:c r="AE7" s="49" t="str"/>
+        <x:v>Keir Starmer has faced down immediate calls for his resignation after receiving the full backing of his cabinet and delivering an impassioned appeal to the PLP this evening that appears to have steadied the government’s ship, at least for now.</x:v>
+      </x:c>
+      <x:c r="AE7" s="49" t="str">
+        <x:v>The article is UK national leadership coverage and would satisfy N1 in the national arm, but this record is fixed to the local arm and supplies no Surrey L1-L4 link.</x:v>
+      </x:c>
       <x:c r="AF7" s="41" t="str">
-        <x:f>IF('Independent Review'!Q5="","",'Independent Review'!Q5)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG7" s="41" t="str">
-        <x:f>IF('Independent Review'!R5="","",'Independent Review'!R5)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH7" s="42" t="str">
         <x:f>IF(B7&lt;&gt;"complete","",IF(OR(W7="",X7="",Y7="",Z7="",AA7="",AB7="",AD7="",AF7="",AG7=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="70" customHeight="1">
@@ -1315,8 +1370,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="40" t="str">
-        <x:f>IF('Independent Review'!B6="","",'Independent Review'!B6)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C8" s="40" t="str">
         <x:v>NEWS-guardian_api-0a2b7642ed1f</x:v>
@@ -1377,28 +1431,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W8" s="41" t="str">
-        <x:f>IF('Independent Review'!M6="","",'Independent Review'!M6)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X8" s="41" t="str">
-        <x:f>IF('Independent Review'!N6="","",'Independent Review'!N6)</x:f>
-      </x:c>
-      <x:c r="Y8" s="41" t="str"/>
-      <x:c r="Z8" s="41" t="str"/>
-      <x:c r="AA8" s="41" t="str"/>
-      <x:c r="AB8" s="41" t="str"/>
-      <x:c r="AC8" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y8" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z8" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA8" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB8" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC8" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD8" s="49" t="str">
-        <x:f>IF('Independent Review'!O6="","",'Independent Review'!O6)</x:f>
-      </x:c>
-      <x:c r="AE8" s="49" t="str"/>
+        <x:v>It has been an election buildup dominated by the rise of Reform UK and the Greens, and the contrasting woes of Labour and the Tories.</x:v>
+      </x:c>
+      <x:c r="AE8" s="49" t="str">
+        <x:v>The article concerns English local-government party performance nationally. It may satisfy N1 in a national search, but it does not satisfy any local L-rule for this local-arm record.</x:v>
+      </x:c>
       <x:c r="AF8" s="41" t="str">
-        <x:f>IF('Independent Review'!Q6="","",'Independent Review'!Q6)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG8" s="41" t="str">
-        <x:f>IF('Independent Review'!R6="","",'Independent Review'!R6)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH8" s="42" t="str">
         <x:f>IF(B8&lt;&gt;"complete","",IF(OR(W8="",X8="",Y8="",Z8="",AA8="",AB8="",AD8="",AF8="",AG8=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
@@ -1406,8 +1473,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="40" t="str">
-        <x:f>IF('Independent Review'!B7="","",'Independent Review'!B7)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C9" s="40" t="str">
         <x:v>NEWS-guardian_api-0a8a98eec2fa</x:v>
@@ -1468,28 +1534,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W9" s="41" t="str">
-        <x:f>IF('Independent Review'!M7="","",'Independent Review'!M7)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X9" s="41" t="str">
-        <x:f>IF('Independent Review'!N7="","",'Independent Review'!N7)</x:f>
-      </x:c>
-      <x:c r="Y9" s="41" t="str"/>
-      <x:c r="Z9" s="41" t="str"/>
-      <x:c r="AA9" s="41" t="str"/>
-      <x:c r="AB9" s="41" t="str"/>
-      <x:c r="AC9" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y9" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z9" s="41" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="AA9" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB9" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC9" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD9" s="49" t="str">
-        <x:f>IF('Independent Review'!O7="","",'Independent Review'!O7)</x:f>
-      </x:c>
-      <x:c r="AE9" s="49" t="str"/>
+        <x:v>Almost 90% of English councils overspent on their budgets for teaching children with special needs last year, and the underfunding is set to continue into 2021, according to figures seen by the Observer.</x:v>
+      </x:c>
+      <x:c r="AE9" s="49" t="str">
+        <x:v>The article concerns SEND funding across English councils. A Surrey council quotation is one example in a national comparison and does not establish an effect on a sampled Surrey division.</x:v>
+      </x:c>
       <x:c r="AF9" s="41" t="str">
-        <x:f>IF('Independent Review'!Q7="","",'Independent Review'!Q7)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG9" s="41" t="str">
-        <x:f>IF('Independent Review'!R7="","",'Independent Review'!R7)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH9" s="42" t="str">
         <x:f>IF(B9&lt;&gt;"complete","",IF(OR(W9="",X9="",Y9="",Z9="",AA9="",AB9="",AD9="",AF9="",AG9=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -1497,8 +1576,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="40" t="str">
-        <x:f>IF('Independent Review'!B8="","",'Independent Review'!B8)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C10" s="40" t="str">
         <x:v>NEWS-guardian_api-0e7b3e16141a</x:v>
@@ -1559,28 +1637,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W10" s="41" t="str">
-        <x:f>IF('Independent Review'!M8="","",'Independent Review'!M8)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X10" s="41" t="str">
-        <x:f>IF('Independent Review'!N8="","",'Independent Review'!N8)</x:f>
-      </x:c>
-      <x:c r="Y10" s="41" t="str"/>
-      <x:c r="Z10" s="41" t="str"/>
-      <x:c r="AA10" s="41" t="str"/>
-      <x:c r="AB10" s="41" t="str"/>
-      <x:c r="AC10" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y10" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z10" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA10" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB10" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC10" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD10" s="49" t="str">
-        <x:f>IF('Independent Review'!O8="","",'Independent Review'!O8)</x:f>
-      </x:c>
-      <x:c r="AE10" s="49" t="str"/>
+        <x:v>Ministers have dropped plans to delay 30 local elections this May after receiving legal advice that doing so might be unlawful.</x:v>
+      </x:c>
+      <x:c r="AE10" s="49" t="str">
+        <x:v>The live blog concerns national decisions about English local elections. It contains no sampled Surrey place or Surrey-specific council effect, so a general local-government story cannot satisfy local L3.</x:v>
+      </x:c>
       <x:c r="AF10" s="41" t="str">
-        <x:f>IF('Independent Review'!Q8="","",'Independent Review'!Q8)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG10" s="41" t="str">
-        <x:f>IF('Independent Review'!R8="","",'Independent Review'!R8)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH10" s="42" t="str">
         <x:f>IF(B10&lt;&gt;"complete","",IF(OR(W10="",X10="",Y10="",Z10="",AA10="",AB10="",AD10="",AF10="",AG10=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70" customHeight="1">
@@ -1588,8 +1679,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="40" t="str">
-        <x:f>IF('Independent Review'!B9="","",'Independent Review'!B9)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C11" s="40" t="str">
         <x:v>NEWS-guardian_api-0f4380a6f846</x:v>
@@ -1648,28 +1738,41 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="W11" s="41" t="str">
-        <x:f>IF('Independent Review'!M9="","",'Independent Review'!M9)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X11" s="41" t="str">
-        <x:f>IF('Independent Review'!N9="","",'Independent Review'!N9)</x:f>
-      </x:c>
-      <x:c r="Y11" s="41" t="str"/>
-      <x:c r="Z11" s="41" t="str"/>
-      <x:c r="AA11" s="41" t="str"/>
-      <x:c r="AB11" s="41" t="str"/>
-      <x:c r="AC11" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y11" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z11" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA11" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB11" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC11" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD11" s="49" t="str">
-        <x:f>IF('Independent Review'!O9="","",'Independent Review'!O9)</x:f>
-      </x:c>
-      <x:c r="AE11" s="49" t="str"/>
+        <x:v>Nigel Farage must know but doesn’t seem to care that history is written by the winners (Nigel Farage quits as Reform UK leader in step back from party politics, 8 March) as he worries about what our children might learn today.</x:v>
+      </x:c>
+      <x:c r="AE11" s="49" t="str">
+        <x:v>The letter directly discusses Nigel Farage, Reform UK leadership and party politics. That is sufficient national-party evidence under N1 even though most of the letter discusses historical education.</x:v>
+      </x:c>
       <x:c r="AF11" s="41" t="str">
-        <x:f>IF('Independent Review'!Q9="","",'Independent Review'!Q9)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG11" s="41" t="str">
-        <x:f>IF('Independent Review'!R9="","",'Independent Review'!R9)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH11" s="42" t="str">
         <x:f>IF(B11&lt;&gt;"complete","",IF(OR(W11="",X11="",Y11="",Z11="",AA11="",AB11="",AD11="",AF11="",AG11=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="70" customHeight="1">
@@ -1677,8 +1780,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="40" t="str">
-        <x:f>IF('Independent Review'!B10="","",'Independent Review'!B10)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C12" s="40" t="str">
         <x:v>NEWS-guardian_api-1593f58b94d2</x:v>
@@ -1739,28 +1841,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W12" s="41" t="str">
-        <x:f>IF('Independent Review'!M10="","",'Independent Review'!M10)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X12" s="41" t="str">
-        <x:f>IF('Independent Review'!N10="","",'Independent Review'!N10)</x:f>
-      </x:c>
-      <x:c r="Y12" s="41" t="str"/>
-      <x:c r="Z12" s="41" t="str"/>
-      <x:c r="AA12" s="41" t="str"/>
-      <x:c r="AB12" s="41" t="str"/>
-      <x:c r="AC12" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y12" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z12" s="41" t="str">
+        <x:v>entity_or_namesake_confusion</x:v>
+      </x:c>
+      <x:c r="AA12" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB12" s="41" t="str">
+        <x:v>few_shot_example</x:v>
+      </x:c>
+      <x:c r="AC12" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD12" s="49" t="str">
-        <x:f>IF('Independent Review'!O10="","",'Independent Review'!O10)</x:f>
-      </x:c>
-      <x:c r="AE12" s="49" t="str"/>
+        <x:v>The sports foundation at the heart of the Millwall FC compulsory purchase battle has been making false claims of having a £2m funding agreement from Sport England during the ongoing CPO process, the Guardian can reveal.</x:v>
+      </x:c>
+      <x:c r="AE12" s="49" t="str">
+        <x:v>The story is about Millwall, Lewisham council and a company called Surrey Canal Sports Foundation. Surrey Canal is a name connected to south London, not evidence of a Surrey council issue or sampled Surrey place.</x:v>
+      </x:c>
       <x:c r="AF12" s="41" t="str">
-        <x:f>IF('Independent Review'!Q10="","",'Independent Review'!Q10)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG12" s="41" t="str">
-        <x:f>IF('Independent Review'!R10="","",'Independent Review'!R10)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH12" s="42" t="str">
         <x:f>IF(B12&lt;&gt;"complete","",IF(OR(W12="",X12="",Y12="",Z12="",AA12="",AB12="",AD12="",AF12="",AG12=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="70" customHeight="1">
@@ -1768,8 +1883,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="40" t="str">
-        <x:f>IF('Independent Review'!B11="","",'Independent Review'!B11)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C13" s="40" t="str">
         <x:v>NEWS-guardian_api-165b44f90fe0</x:v>
@@ -1830,28 +1944,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W13" s="41" t="str">
-        <x:f>IF('Independent Review'!M11="","",'Independent Review'!M11)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X13" s="41" t="str">
-        <x:f>IF('Independent Review'!N11="","",'Independent Review'!N11)</x:f>
-      </x:c>
-      <x:c r="Y13" s="41" t="str"/>
-      <x:c r="Z13" s="41" t="str"/>
-      <x:c r="AA13" s="41" t="str"/>
-      <x:c r="AB13" s="41" t="str"/>
-      <x:c r="AC13" s="41" t="str"/>
+        <x:v>L4</x:v>
+      </x:c>
+      <x:c r="Y13" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z13" s="41" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="AA13" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB13" s="41" t="str">
+        <x:v>few_shot_example</x:v>
+      </x:c>
+      <x:c r="AC13" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD13" s="49" t="str">
-        <x:f>IF('Independent Review'!O11="","",'Independent Review'!O11)</x:f>
-      </x:c>
-      <x:c r="AE13" s="49" t="str"/>
+        <x:v>The business of the shortest parliament since 1974 is nearly done.</x:v>
+      </x:c>
+      <x:c r="AE13" s="49" t="str">
+        <x:v>The editorial is about the UK general election and Brexit. Its retrospective Surrey council example is a passing illustration and is not Surrey-wide political coverage for the sampled local arm.</x:v>
+      </x:c>
       <x:c r="AF13" s="41" t="str">
-        <x:f>IF('Independent Review'!Q11="","",'Independent Review'!Q11)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG13" s="41" t="str">
-        <x:f>IF('Independent Review'!R11="","",'Independent Review'!R11)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH13" s="42" t="str">
         <x:f>IF(B13&lt;&gt;"complete","",IF(OR(W13="",X13="",Y13="",Z13="",AA13="",AB13="",AD13="",AF13="",AG13=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="70" customHeight="1">
@@ -1859,8 +1986,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="40" t="str">
-        <x:f>IF('Independent Review'!B12="","",'Independent Review'!B12)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C14" s="40" t="str">
         <x:v>NEWS-guardian_api-1d67c0c9dc56</x:v>
@@ -1921,28 +2047,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W14" s="41" t="str">
-        <x:f>IF('Independent Review'!M12="","",'Independent Review'!M12)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X14" s="41" t="str">
-        <x:f>IF('Independent Review'!N12="","",'Independent Review'!N12)</x:f>
-      </x:c>
-      <x:c r="Y14" s="41" t="str"/>
-      <x:c r="Z14" s="41" t="str"/>
-      <x:c r="AA14" s="41" t="str"/>
-      <x:c r="AB14" s="41" t="str"/>
-      <x:c r="AC14" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y14" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z14" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA14" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB14" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC14" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD14" s="49" t="str">
-        <x:f>IF('Independent Review'!O12="","",'Independent Review'!O12)</x:f>
-      </x:c>
-      <x:c r="AE14" s="49" t="str"/>
+        <x:v>When Gary Collins arrived at work in Stoke Newington police station, east London, in January last year he was told a teenage boy had been stabbed to death.</x:v>
+      </x:c>
+      <x:c r="AE14" s="49" t="str">
+        <x:v>The article substantively examines a Metropolitan Police identification service and its use in criminal investigations. Policing is a national public-service issue within the N2 public-services category.</x:v>
+      </x:c>
       <x:c r="AF14" s="41" t="str">
-        <x:f>IF('Independent Review'!Q12="","",'Independent Review'!Q12)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG14" s="41" t="str">
-        <x:f>IF('Independent Review'!R12="","",'Independent Review'!R12)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH14" s="42" t="str">
         <x:f>IF(B14&lt;&gt;"complete","",IF(OR(W14="",X14="",Y14="",Z14="",AA14="",AB14="",AD14="",AF14="",AG14=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="70" customHeight="1">
@@ -1950,8 +2089,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="40" t="str">
-        <x:f>IF('Independent Review'!B13="","",'Independent Review'!B13)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C15" s="40" t="str">
         <x:v>NEWS-guardian_api-26998343d44f</x:v>
@@ -2012,28 +2150,41 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="W15" s="41" t="str">
-        <x:f>IF('Independent Review'!M13="","",'Independent Review'!M13)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X15" s="41" t="str">
-        <x:f>IF('Independent Review'!N13="","",'Independent Review'!N13)</x:f>
-      </x:c>
-      <x:c r="Y15" s="41" t="str"/>
-      <x:c r="Z15" s="41" t="str"/>
-      <x:c r="AA15" s="41" t="str"/>
-      <x:c r="AB15" s="41" t="str"/>
-      <x:c r="AC15" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y15" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z15" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA15" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB15" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC15" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD15" s="49" t="str">
-        <x:f>IF('Independent Review'!O13="","",'Independent Review'!O13)</x:f>
-      </x:c>
-      <x:c r="AE15" s="49" t="str"/>
+        <x:v>Today, the Observer New Review publishes a vivid account of Robert Reich's new documentary Inequality for All.</x:v>
+      </x:c>
+      <x:c r="AE15" s="49" t="str">
+        <x:v>The article explicitly concerns stagnant wages, rising living costs and economic inequality. These are substantive cost-of-living issues under N2.</x:v>
+      </x:c>
       <x:c r="AF15" s="41" t="str">
-        <x:f>IF('Independent Review'!Q13="","",'Independent Review'!Q13)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG15" s="41" t="str">
-        <x:f>IF('Independent Review'!R13="","",'Independent Review'!R13)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH15" s="42" t="str">
         <x:f>IF(B15&lt;&gt;"complete","",IF(OR(W15="",X15="",Y15="",Z15="",AA15="",AB15="",AD15="",AF15="",AG15=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="70" customHeight="1">
@@ -2041,8 +2192,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="40" t="str">
-        <x:f>IF('Independent Review'!B14="","",'Independent Review'!B14)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C16" s="40" t="str">
         <x:v>NEWS-guardian_api-299f68788499</x:v>
@@ -2101,28 +2251,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W16" s="41" t="str">
-        <x:f>IF('Independent Review'!M14="","",'Independent Review'!M14)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X16" s="41" t="str">
-        <x:f>IF('Independent Review'!N14="","",'Independent Review'!N14)</x:f>
-      </x:c>
-      <x:c r="Y16" s="41" t="str"/>
-      <x:c r="Z16" s="41" t="str"/>
-      <x:c r="AA16" s="41" t="str"/>
-      <x:c r="AB16" s="41" t="str"/>
-      <x:c r="AC16" s="41" t="str"/>
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="Y16" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z16" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA16" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB16" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC16" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD16" s="49" t="str">
-        <x:f>IF('Independent Review'!O14="","",'Independent Review'!O14)</x:f>
-      </x:c>
-      <x:c r="AE16" s="49" t="str"/>
+        <x:v>In the south of England East Surrey hospital in Redhill stopped visits to 10 of its wards on Tuesday, a decision which had not been taken lightly, Surrey and Sussex Healthcare NHS trust said.</x:v>
+      </x:c>
+      <x:c r="AE16" s="49" t="str">
+        <x:v>The article gives a substantive local example at East Surrey Hospital in Redhill. The correct basis is L1 place linkage; the NHS trust decision is not a Surrey council decision and should not be coded as L3.</x:v>
+      </x:c>
       <x:c r="AF16" s="41" t="str">
-        <x:f>IF('Independent Review'!Q14="","",'Independent Review'!Q14)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG16" s="41" t="str">
-        <x:f>IF('Independent Review'!R14="","",'Independent Review'!R14)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH16" s="42" t="str">
         <x:f>IF(B16&lt;&gt;"complete","",IF(OR(W16="",X16="",Y16="",Z16="",AA16="",AB16="",AD16="",AF16="",AG16=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="70" customHeight="1">
@@ -2130,8 +2293,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="40" t="str">
-        <x:f>IF('Independent Review'!B15="","",'Independent Review'!B15)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C17" s="40" t="str">
         <x:v>NEWS-guardian_api-34e77f9bede6</x:v>
@@ -2190,28 +2352,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W17" s="41" t="str">
-        <x:f>IF('Independent Review'!M15="","",'Independent Review'!M15)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X17" s="41" t="str">
-        <x:f>IF('Independent Review'!N15="","",'Independent Review'!N15)</x:f>
-      </x:c>
-      <x:c r="Y17" s="41" t="str"/>
-      <x:c r="Z17" s="41" t="str"/>
-      <x:c r="AA17" s="41" t="str"/>
-      <x:c r="AB17" s="41" t="str"/>
-      <x:c r="AC17" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y17" s="41" t="str">
+        <x:v>evidence_beyond_excerpt</x:v>
+      </x:c>
+      <x:c r="Z17" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA17" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB17" s="41" t="str">
+        <x:v>input_fix</x:v>
+      </x:c>
+      <x:c r="AC17" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD17" s="49" t="str">
-        <x:f>IF('Independent Review'!O15="","",'Independent Review'!O15)</x:f>
-      </x:c>
-      <x:c r="AE17" s="49" t="str"/>
+        <x:v>Having campaigned against devolution in Wales, in 1999 he was elected to the Welsh Assembly on a platform of opposition to any further devolution, and won Monmouth for the Conservatives in 2005.</x:v>
+      </x:c>
+      <x:c r="AE17" s="49" t="str">
+        <x:v>The full article is a political profile of a Conservative MP and discusses his electoral and parliamentary positions. The decisive N1 material was outside the short v1 excerpt.</x:v>
+      </x:c>
       <x:c r="AF17" s="41" t="str">
-        <x:f>IF('Independent Review'!Q15="","",'Independent Review'!Q15)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG17" s="41" t="str">
-        <x:f>IF('Independent Review'!R15="","",'Independent Review'!R15)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH17" s="42" t="str">
         <x:f>IF(B17&lt;&gt;"complete","",IF(OR(W17="",X17="",Y17="",Z17="",AA17="",AB17="",AD17="",AF17="",AG17=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="70" customHeight="1">
@@ -2219,8 +2394,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="40" t="str">
-        <x:f>IF('Independent Review'!B16="","",'Independent Review'!B16)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C18" s="40" t="str">
         <x:v>NEWS-guardian_api-3a9be3f68624</x:v>
@@ -2279,28 +2453,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W18" s="41" t="str">
-        <x:f>IF('Independent Review'!M16="","",'Independent Review'!M16)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X18" s="41" t="str">
-        <x:f>IF('Independent Review'!N16="","",'Independent Review'!N16)</x:f>
-      </x:c>
-      <x:c r="Y18" s="41" t="str"/>
-      <x:c r="Z18" s="41" t="str"/>
-      <x:c r="AA18" s="41" t="str"/>
-      <x:c r="AB18" s="41" t="str"/>
-      <x:c r="AC18" s="41" t="str"/>
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="Y18" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z18" s="41" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="AA18" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB18" s="41" t="str">
+        <x:v>few_shot_example</x:v>
+      </x:c>
+      <x:c r="AC18" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD18" s="49" t="str">
-        <x:f>IF('Independent Review'!O16="","",'Independent Review'!O16)</x:f>
-      </x:c>
-      <x:c r="AE18" s="49" t="str"/>
+        <x:v>In April 2018, a woman told the newspaper how she was struggling to sell the retirement flat her late parents had bought in 1997 and that she had been forced to cut the price from £185,000 to £140,000, well below the £260,000 average for a normal flat in the same Surrey village.</x:v>
+      </x:c>
+      <x:c r="AE18" s="49" t="str">
+        <x:v>The article's main case concerns a retirement flat in Solihull. The unnamed Surrey village appears only in a comparison with a different case and does not create substantive sampled-area relevance.</x:v>
+      </x:c>
       <x:c r="AF18" s="41" t="str">
-        <x:f>IF('Independent Review'!Q16="","",'Independent Review'!Q16)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG18" s="41" t="str">
-        <x:f>IF('Independent Review'!R16="","",'Independent Review'!R16)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH18" s="42" t="str">
         <x:f>IF(B18&lt;&gt;"complete","",IF(OR(W18="",X18="",Y18="",Z18="",AA18="",AB18="",AD18="",AF18="",AG18=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="70" customHeight="1">
@@ -2308,8 +2495,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="40" t="str">
-        <x:f>IF('Independent Review'!B17="","",'Independent Review'!B17)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C19" s="40" t="str">
         <x:v>NEWS-guardian_api-4b66c98ae734</x:v>
@@ -2370,28 +2556,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W19" s="41" t="str">
-        <x:f>IF('Independent Review'!M17="","",'Independent Review'!M17)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X19" s="41" t="str">
-        <x:f>IF('Independent Review'!N17="","",'Independent Review'!N17)</x:f>
-      </x:c>
-      <x:c r="Y19" s="41" t="str"/>
-      <x:c r="Z19" s="41" t="str"/>
-      <x:c r="AA19" s="41" t="str"/>
-      <x:c r="AB19" s="41" t="str"/>
-      <x:c r="AC19" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y19" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z19" s="41" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="AA19" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB19" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC19" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD19" s="49" t="str">
-        <x:f>IF('Independent Review'!O17="","",'Independent Review'!O17)</x:f>
-      </x:c>
-      <x:c r="AE19" s="49" t="str"/>
+        <x:v>The shop windows are decked out in their festive finery, there are carols on the stereos and the tills are ringing.</x:v>
+      </x:c>
+      <x:c r="AE19" s="49" t="str">
+        <x:v>The article concerns parking charges in Clevedon imposed by North Somerset council. A non-Surrey council issue cannot satisfy local L3.</x:v>
+      </x:c>
       <x:c r="AF19" s="41" t="str">
-        <x:f>IF('Independent Review'!Q17="","",'Independent Review'!Q17)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG19" s="41" t="str">
-        <x:f>IF('Independent Review'!R17="","",'Independent Review'!R17)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH19" s="42" t="str">
         <x:f>IF(B19&lt;&gt;"complete","",IF(OR(W19="",X19="",Y19="",Z19="",AA19="",AB19="",AD19="",AF19="",AG19=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="70" customHeight="1">
@@ -2399,8 +2598,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="40" t="str">
-        <x:f>IF('Independent Review'!B18="","",'Independent Review'!B18)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C20" s="40" t="str">
         <x:v>NEWS-guardian_api-4f0bd20943f7</x:v>
@@ -2461,28 +2659,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W20" s="41" t="str">
-        <x:f>IF('Independent Review'!M18="","",'Independent Review'!M18)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X20" s="41" t="str">
-        <x:f>IF('Independent Review'!N18="","",'Independent Review'!N18)</x:f>
-      </x:c>
-      <x:c r="Y20" s="41" t="str"/>
-      <x:c r="Z20" s="41" t="str"/>
-      <x:c r="AA20" s="41" t="str"/>
-      <x:c r="AB20" s="41" t="str"/>
-      <x:c r="AC20" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y20" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z20" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA20" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB20" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC20" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD20" s="49" t="str">
-        <x:f>IF('Independent Review'!O18="","",'Independent Review'!O18)</x:f>
-      </x:c>
-      <x:c r="AE20" s="49" t="str"/>
+        <x:v>A revolt against urban liberalism and multiculturalism, and their supposed imposition on the rest of the population, was a big element of the Brexit and Donald Trump campaigns.</x:v>
+      </x:c>
+      <x:c r="AE20" s="49" t="str">
+        <x:v>The analysis concerns Brexit, Donald Trump and the political division between urban and rural voters. It is substantive national political coverage under N1.</x:v>
+      </x:c>
       <x:c r="AF20" s="41" t="str">
-        <x:f>IF('Independent Review'!Q18="","",'Independent Review'!Q18)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG20" s="41" t="str">
-        <x:f>IF('Independent Review'!R18="","",'Independent Review'!R18)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH20" s="42" t="str">
         <x:f>IF(B20&lt;&gt;"complete","",IF(OR(W20="",X20="",Y20="",Z20="",AA20="",AB20="",AD20="",AF20="",AG20=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="70" customHeight="1">
@@ -2490,8 +2701,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="40" t="str">
-        <x:f>IF('Independent Review'!B19="","",'Independent Review'!B19)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>needs_adjudication</x:v>
       </x:c>
       <x:c r="C21" s="40" t="str">
         <x:v>NEWS-guardian_api-4fc41ad01b24</x:v>
@@ -2550,25 +2760,37 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W21" s="41" t="str">
-        <x:f>IF('Independent Review'!M19="","",'Independent Review'!M19)</x:f>
+        <x:v>needs_second_review</x:v>
       </x:c>
       <x:c r="X21" s="41" t="str">
-        <x:f>IF('Independent Review'!N19="","",'Independent Review'!N19)</x:f>
-      </x:c>
-      <x:c r="Y21" s="41" t="str"/>
-      <x:c r="Z21" s="41" t="str"/>
-      <x:c r="AA21" s="41" t="str"/>
-      <x:c r="AB21" s="41" t="str"/>
-      <x:c r="AC21" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y21" s="41" t="str">
+        <x:v>evidence_beyond_excerpt</x:v>
+      </x:c>
+      <x:c r="Z21" s="41" t="str">
+        <x:v>national_policy_scope_too_broad</x:v>
+      </x:c>
+      <x:c r="AA21" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB21" s="41" t="str">
+        <x:v>codebook_review</x:v>
+      </x:c>
+      <x:c r="AC21" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD21" s="49" t="str">
-        <x:f>IF('Independent Review'!O19="","",'Independent Review'!O19)</x:f>
-      </x:c>
-      <x:c r="AE21" s="49" t="str"/>
+        <x:v>Liz Neil is account co-ordinator, programmes and projects at British Council Liz has many years experience working on international education programmes for schools, colleges and universities, including eTwinning and Comenius.</x:v>
+      </x:c>
+      <x:c r="AE21" s="49" t="str">
+        <x:v>The article concerns global awareness teaching rather than a clearly defined UK political decision, funding question or public-service performance issue. Adjudication should clarify whether general educational practice falls within N2 public services.</x:v>
+      </x:c>
       <x:c r="AF21" s="41" t="str">
-        <x:f>IF('Independent Review'!Q19="","",'Independent Review'!Q19)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG21" s="41" t="str">
-        <x:f>IF('Independent Review'!R19="","",'Independent Review'!R19)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH21" s="42" t="str">
         <x:f>IF(B21&lt;&gt;"complete","",IF(OR(W21="",X21="",Y21="",Z21="",AA21="",AB21="",AD21="",AF21="",AG21=""),"MISSING REQUIRED FIELD","OK"))</x:f>
@@ -2579,8 +2801,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="40" t="str">
-        <x:f>IF('Independent Review'!B20="","",'Independent Review'!B20)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C22" s="40" t="str">
         <x:v>NEWS-guardian_api-5155ba13661a</x:v>
@@ -2639,28 +2860,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W22" s="41" t="str">
-        <x:f>IF('Independent Review'!M20="","",'Independent Review'!M20)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X22" s="41" t="str">
-        <x:f>IF('Independent Review'!N20="","",'Independent Review'!N20)</x:f>
-      </x:c>
-      <x:c r="Y22" s="41" t="str"/>
-      <x:c r="Z22" s="41" t="str"/>
-      <x:c r="AA22" s="41" t="str"/>
-      <x:c r="AB22" s="41" t="str"/>
-      <x:c r="AC22" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y22" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z22" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA22" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB22" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC22" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD22" s="49" t="str">
-        <x:f>IF('Independent Review'!O20="","",'Independent Review'!O20)</x:f>
-      </x:c>
-      <x:c r="AE22" s="49" t="str"/>
+        <x:v>A woman is taking legal action against an NHS trust over the “diabolical” and discriminatory treatment of her profoundly deaf husband, who died of cancer in May last year.</x:v>
+      </x:c>
+      <x:c r="AE22" s="49" t="str">
+        <x:v>The article concerns alleged discriminatory treatment by an NHS trust and therefore directly addresses NHS service quality under N2.</x:v>
+      </x:c>
       <x:c r="AF22" s="41" t="str">
-        <x:f>IF('Independent Review'!Q20="","",'Independent Review'!Q20)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG22" s="41" t="str">
-        <x:f>IF('Independent Review'!R20="","",'Independent Review'!R20)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH22" s="42" t="str">
         <x:f>IF(B22&lt;&gt;"complete","",IF(OR(W22="",X22="",Y22="",Z22="",AA22="",AB22="",AD22="",AF22="",AG22=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="70" customHeight="1">
@@ -2668,8 +2902,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="40" t="str">
-        <x:f>IF('Independent Review'!B21="","",'Independent Review'!B21)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C23" s="40" t="str">
         <x:v>NEWS-guardian_api-568af3a4ccd4</x:v>
@@ -2730,28 +2963,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W23" s="41" t="str">
-        <x:f>IF('Independent Review'!M21="","",'Independent Review'!M21)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X23" s="41" t="str">
-        <x:f>IF('Independent Review'!N21="","",'Independent Review'!N21)</x:f>
-      </x:c>
-      <x:c r="Y23" s="41" t="str"/>
-      <x:c r="Z23" s="41" t="str"/>
-      <x:c r="AA23" s="41" t="str"/>
-      <x:c r="AB23" s="41" t="str"/>
-      <x:c r="AC23" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y23" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z23" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA23" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB23" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC23" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD23" s="49" t="str">
-        <x:f>IF('Independent Review'!O21="","",'Independent Review'!O21)</x:f>
-      </x:c>
-      <x:c r="AE23" s="49" t="str"/>
+        <x:v>Ohio is where the warring halves of America meet.</x:v>
+      </x:c>
+      <x:c r="AE23" s="49" t="str">
+        <x:v>The article is about the United States presidential election. N1 is limited to UK national politics, and the L2 candidate code used by the model is invalid for a national-arm record.</x:v>
+      </x:c>
       <x:c r="AF23" s="41" t="str">
-        <x:f>IF('Independent Review'!Q21="","",'Independent Review'!Q21)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG23" s="41" t="str">
-        <x:f>IF('Independent Review'!R21="","",'Independent Review'!R21)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH23" s="42" t="str">
         <x:f>IF(B23&lt;&gt;"complete","",IF(OR(W23="",X23="",Y23="",Z23="",AA23="",AB23="",AD23="",AF23="",AG23=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="70" customHeight="1">
@@ -2759,8 +3005,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="40" t="str">
-        <x:f>IF('Independent Review'!B22="","",'Independent Review'!B22)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C24" s="40" t="str">
         <x:v>NEWS-guardian_api-649bfee8381e</x:v>
@@ -2821,28 +3066,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W24" s="41" t="str">
-        <x:f>IF('Independent Review'!M22="","",'Independent Review'!M22)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X24" s="41" t="str">
-        <x:f>IF('Independent Review'!N22="","",'Independent Review'!N22)</x:f>
-      </x:c>
-      <x:c r="Y24" s="41" t="str"/>
-      <x:c r="Z24" s="41" t="str"/>
-      <x:c r="AA24" s="41" t="str"/>
-      <x:c r="AB24" s="41" t="str"/>
-      <x:c r="AC24" s="41" t="str"/>
+        <x:v>L4</x:v>
+      </x:c>
+      <x:c r="Y24" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z24" s="41" t="str">
+        <x:v>surrey_wide_rule_misapplied</x:v>
+      </x:c>
+      <x:c r="AA24" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB24" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC24" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD24" s="49" t="str">
-        <x:f>IF('Independent Review'!O22="","",'Independent Review'!O22)</x:f>
-      </x:c>
-      <x:c r="AE24" s="49" t="str"/>
+        <x:v>Ministers are to postpone elections for new mayors in four parts of England, prompting accusations from opposition parties that Downing Street is “cancelling democracy”.</x:v>
+      </x:c>
+      <x:c r="AE24" s="49" t="str">
+        <x:v>The article concerns mayoral elections in Essex, East Anglia, Hampshire and Sussex. Coverage spanning several English regions is not Surrey-wide political coverage under L4.</x:v>
+      </x:c>
       <x:c r="AF24" s="41" t="str">
-        <x:f>IF('Independent Review'!Q22="","",'Independent Review'!Q22)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG24" s="41" t="str">
-        <x:f>IF('Independent Review'!R22="","",'Independent Review'!R22)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH24" s="42" t="str">
         <x:f>IF(B24&lt;&gt;"complete","",IF(OR(W24="",X24="",Y24="",Z24="",AA24="",AB24="",AD24="",AF24="",AG24=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="70" customHeight="1">
@@ -2850,8 +3108,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="40" t="str">
-        <x:f>IF('Independent Review'!B23="","",'Independent Review'!B23)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C25" s="40" t="str">
         <x:v>NEWS-guardian_api-64ea38ced8bd</x:v>
@@ -2910,28 +3167,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W25" s="41" t="str">
-        <x:f>IF('Independent Review'!M23="","",'Independent Review'!M23)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X25" s="41" t="str">
-        <x:f>IF('Independent Review'!N23="","",'Independent Review'!N23)</x:f>
-      </x:c>
-      <x:c r="Y25" s="41" t="str"/>
-      <x:c r="Z25" s="41" t="str"/>
-      <x:c r="AA25" s="41" t="str"/>
-      <x:c r="AB25" s="41" t="str"/>
-      <x:c r="AC25" s="41" t="str"/>
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="Y25" s="41" t="str">
+        <x:v>missing_query_context</x:v>
+      </x:c>
+      <x:c r="Z25" s="41" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="AA25" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB25" s="41" t="str">
+        <x:v>human_label_adjudication</x:v>
+      </x:c>
+      <x:c r="AC25" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD25" s="49" t="str">
-        <x:f>IF('Independent Review'!O23="","",'Independent Review'!O23)</x:f>
-      </x:c>
-      <x:c r="AE25" s="49" t="str"/>
+        <x:v>The speech was made in the playground of Nonsuch high school for girls in Surrey.</x:v>
+      </x:c>
+      <x:c r="AE25" s="49" t="str">
+        <x:v>The article is substantively about Nonsuch High School, but the school is associated with the Nonsuch area rather than any of the 17 sampled divisions in this study. A generic Surrey description is insufficient for sampled-area L1.</x:v>
+      </x:c>
       <x:c r="AF25" s="41" t="str">
-        <x:f>IF('Independent Review'!Q23="","",'Independent Review'!Q23)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG25" s="41" t="str">
-        <x:f>IF('Independent Review'!R23="","",'Independent Review'!R23)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH25" s="42" t="str">
         <x:f>IF(B25&lt;&gt;"complete","",IF(OR(W25="",X25="",Y25="",Z25="",AA25="",AB25="",AD25="",AF25="",AG25=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="70" customHeight="1">
@@ -2939,8 +3209,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="40" t="str">
-        <x:f>IF('Independent Review'!B24="","",'Independent Review'!B24)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C26" s="40" t="str">
         <x:v>NEWS-guardian_api-6549611cf8a4</x:v>
@@ -3001,28 +3270,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W26" s="41" t="str">
-        <x:f>IF('Independent Review'!M24="","",'Independent Review'!M24)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X26" s="41" t="str">
-        <x:f>IF('Independent Review'!N24="","",'Independent Review'!N24)</x:f>
-      </x:c>
-      <x:c r="Y26" s="41" t="str"/>
-      <x:c r="Z26" s="41" t="str"/>
-      <x:c r="AA26" s="41" t="str"/>
-      <x:c r="AB26" s="41" t="str"/>
-      <x:c r="AC26" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y26" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z26" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA26" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB26" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC26" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD26" s="49" t="str">
-        <x:f>IF('Independent Review'!O24="","",'Independent Review'!O24)</x:f>
-      </x:c>
-      <x:c r="AE26" s="49" t="str"/>
+        <x:v>Ask Barbara Keeley what keeps her awake at night and Labour’s shadow cabinet member for mental health and social care will tell you it’s the stories of people in “heartrending” situations whose care is being cut.</x:v>
+      </x:c>
+      <x:c r="AE26" s="49" t="str">
+        <x:v>The article is a national social-care funding interview. It could satisfy N2 in the national arm, but it contains no sampled Surrey L1-L4 link for this local-arm record.</x:v>
+      </x:c>
       <x:c r="AF26" s="41" t="str">
-        <x:f>IF('Independent Review'!Q24="","",'Independent Review'!Q24)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG26" s="41" t="str">
-        <x:f>IF('Independent Review'!R24="","",'Independent Review'!R24)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH26" s="42" t="str">
         <x:f>IF(B26&lt;&gt;"complete","",IF(OR(W26="",X26="",Y26="",Z26="",AA26="",AB26="",AD26="",AF26="",AG26=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="70" customHeight="1">
@@ -3030,8 +3312,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="40" t="str">
-        <x:f>IF('Independent Review'!B25="","",'Independent Review'!B25)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C27" s="40" t="str">
         <x:v>NEWS-guardian_api-6d0b3b8aedc2</x:v>
@@ -3092,28 +3373,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W27" s="41" t="str">
-        <x:f>IF('Independent Review'!M25="","",'Independent Review'!M25)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X27" s="41" t="str">
-        <x:f>IF('Independent Review'!N25="","",'Independent Review'!N25)</x:f>
-      </x:c>
-      <x:c r="Y27" s="41" t="str"/>
-      <x:c r="Z27" s="41" t="str"/>
-      <x:c r="AA27" s="41" t="str"/>
-      <x:c r="AB27" s="41" t="str"/>
-      <x:c r="AC27" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y27" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z27" s="41" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="AA27" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB27" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC27" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD27" s="49" t="str">
-        <x:f>IF('Independent Review'!O25="","",'Independent Review'!O25)</x:f>
-      </x:c>
-      <x:c r="AE27" s="49" t="str"/>
+        <x:v>Millwall Football Club have admitted for the first time that they may be forced to leave their south London home and relocate to Kent should the seizure of their land go ahead.</x:v>
+      </x:c>
+      <x:c r="AE27" s="49" t="str">
+        <x:v>The compulsory-purchase dispute concerns Lewisham council and Millwall in south London. It is not a Surrey council decision and cannot satisfy local L3.</x:v>
+      </x:c>
       <x:c r="AF27" s="41" t="str">
-        <x:f>IF('Independent Review'!Q25="","",'Independent Review'!Q25)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG27" s="41" t="str">
-        <x:f>IF('Independent Review'!R25="","",'Independent Review'!R25)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH27" s="42" t="str">
         <x:f>IF(B27&lt;&gt;"complete","",IF(OR(W27="",X27="",Y27="",Z27="",AA27="",AB27="",AD27="",AF27="",AG27=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="70" customHeight="1">
@@ -3121,8 +3415,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="40" t="str">
-        <x:f>IF('Independent Review'!B26="","",'Independent Review'!B26)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C28" s="40" t="str">
         <x:v>NEWS-guardian_api-6d2d7efbb858</x:v>
@@ -3183,28 +3476,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W28" s="41" t="str">
-        <x:f>IF('Independent Review'!M26="","",'Independent Review'!M26)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X28" s="41" t="str">
-        <x:f>IF('Independent Review'!N26="","",'Independent Review'!N26)</x:f>
-      </x:c>
-      <x:c r="Y28" s="41" t="str"/>
-      <x:c r="Z28" s="41" t="str"/>
-      <x:c r="AA28" s="41" t="str"/>
-      <x:c r="AB28" s="41" t="str"/>
-      <x:c r="AC28" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y28" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z28" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA28" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB28" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC28" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD28" s="49" t="str">
-        <x:f>IF('Independent Review'!O26="","",'Independent Review'!O26)</x:f>
-      </x:c>
-      <x:c r="AE28" s="49" t="str"/>
+        <x:v>Tory supporters of equal marriage are making an eleventh hour plea to fellow Conservative MPs to vote in favour of reform by invoking the record of Margaret Thatcher, who supported the legalisation of homosexuality in the 1960s.</x:v>
+      </x:c>
+      <x:c r="AE28" s="49" t="str">
+        <x:v>The article concerns national parliamentary politics and equal marriage. It could meet N1 in the national arm, but it contains no local Surrey linkage for this local-arm record.</x:v>
+      </x:c>
       <x:c r="AF28" s="41" t="str">
-        <x:f>IF('Independent Review'!Q26="","",'Independent Review'!Q26)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG28" s="41" t="str">
-        <x:f>IF('Independent Review'!R26="","",'Independent Review'!R26)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH28" s="42" t="str">
         <x:f>IF(B28&lt;&gt;"complete","",IF(OR(W28="",X28="",Y28="",Z28="",AA28="",AB28="",AD28="",AF28="",AG28=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="70" customHeight="1">
@@ -3212,8 +3518,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="40" t="str">
-        <x:f>IF('Independent Review'!B27="","",'Independent Review'!B27)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C29" s="40" t="str">
         <x:v>NEWS-guardian_api-775f95b2aee7</x:v>
@@ -3272,28 +3577,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W29" s="41" t="str">
-        <x:f>IF('Independent Review'!M27="","",'Independent Review'!M27)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X29" s="41" t="str">
-        <x:f>IF('Independent Review'!N27="","",'Independent Review'!N27)</x:f>
-      </x:c>
-      <x:c r="Y29" s="41" t="str"/>
-      <x:c r="Z29" s="41" t="str"/>
-      <x:c r="AA29" s="41" t="str"/>
-      <x:c r="AB29" s="41" t="str"/>
-      <x:c r="AC29" s="41" t="str"/>
+        <x:v>N3</x:v>
+      </x:c>
+      <x:c r="Y29" s="41" t="str">
+        <x:v>evidence_beyond_excerpt</x:v>
+      </x:c>
+      <x:c r="Z29" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA29" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB29" s="41" t="str">
+        <x:v>input_fix</x:v>
+      </x:c>
+      <x:c r="AC29" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD29" s="49" t="str">
-        <x:f>IF('Independent Review'!O27="","",'Independent Review'!O27)</x:f>
-      </x:c>
-      <x:c r="AE29" s="49" t="str"/>
+        <x:v>Michael says this poses a question for the government: “With Reform UK continuing to rise in the polls, and political attacks on the BBC increasing, will the government decide it needs to defend and protect the corporation’s independence in this increasingly hostile environment?” The risk of Labour leaning into a populist anti-BBC sentiment is unlikely: it would be seismic, he tells me, for the government to scrap the licence fee.</x:v>
+      </x:c>
+      <x:c r="AE29" s="49" t="str">
+        <x:v>The full briefing explicitly links Reform UK's rise in the polls to political pressure on the BBC and government choices. This is direct Reform growth evidence under N3.</x:v>
+      </x:c>
       <x:c r="AF29" s="41" t="str">
-        <x:f>IF('Independent Review'!Q27="","",'Independent Review'!Q27)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG29" s="41" t="str">
-        <x:f>IF('Independent Review'!R27="","",'Independent Review'!R27)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH29" s="42" t="str">
         <x:f>IF(B29&lt;&gt;"complete","",IF(OR(W29="",X29="",Y29="",Z29="",AA29="",AB29="",AD29="",AF29="",AG29=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="70" customHeight="1">
@@ -3301,8 +3619,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="40" t="str">
-        <x:f>IF('Independent Review'!B28="","",'Independent Review'!B28)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C30" s="40" t="str">
         <x:v>NEWS-guardian_api-7cf057334d25</x:v>
@@ -3361,28 +3678,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W30" s="41" t="str">
-        <x:f>IF('Independent Review'!M28="","",'Independent Review'!M28)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X30" s="41" t="str">
-        <x:f>IF('Independent Review'!N28="","",'Independent Review'!N28)</x:f>
-      </x:c>
-      <x:c r="Y30" s="41" t="str"/>
-      <x:c r="Z30" s="41" t="str"/>
-      <x:c r="AA30" s="41" t="str"/>
-      <x:c r="AB30" s="41" t="str"/>
-      <x:c r="AC30" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y30" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z30" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA30" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB30" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC30" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD30" s="49" t="str">
-        <x:f>IF('Independent Review'!O28="","",'Independent Review'!O28)</x:f>
-      </x:c>
-      <x:c r="AE30" s="49" t="str"/>
+        <x:v>When and how will I be able to get a Covid vaccine?</x:v>
+      </x:c>
+      <x:c r="AE30" s="49" t="str">
+        <x:v>The article explains the UK government's Covid vaccination programme, priority groups and NHS delivery. It directly satisfies the NHS/public-services branch of N2.</x:v>
+      </x:c>
       <x:c r="AF30" s="41" t="str">
-        <x:f>IF('Independent Review'!Q28="","",'Independent Review'!Q28)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG30" s="41" t="str">
-        <x:f>IF('Independent Review'!R28="","",'Independent Review'!R28)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH30" s="42" t="str">
         <x:f>IF(B30&lt;&gt;"complete","",IF(OR(W30="",X30="",Y30="",Z30="",AA30="",AB30="",AD30="",AF30="",AG30=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="70" customHeight="1">
@@ -3390,8 +3720,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="40" t="str">
-        <x:f>IF('Independent Review'!B29="","",'Independent Review'!B29)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C31" s="40" t="str">
         <x:v>NEWS-guardian_api-87c983cdc10f</x:v>
@@ -3452,28 +3781,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W31" s="41" t="str">
-        <x:f>IF('Independent Review'!M29="","",'Independent Review'!M29)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X31" s="41" t="str">
-        <x:f>IF('Independent Review'!N29="","",'Independent Review'!N29)</x:f>
-      </x:c>
-      <x:c r="Y31" s="41" t="str"/>
-      <x:c r="Z31" s="41" t="str"/>
-      <x:c r="AA31" s="41" t="str"/>
-      <x:c r="AB31" s="41" t="str"/>
-      <x:c r="AC31" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y31" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z31" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA31" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB31" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC31" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD31" s="49" t="str">
-        <x:f>IF('Independent Review'!O29="","",'Independent Review'!O29)</x:f>
-      </x:c>
-      <x:c r="AE31" s="49" t="str"/>
+        <x:v>Now somebody else will become Boris Johnson’s best known adviser.</x:v>
+      </x:c>
+      <x:c r="AE31" s="49" t="str">
+        <x:v>The article analyses Dominic Cummings's departure and Boris Johnson's Downing Street operation. This is substantive government-performance coverage under N1.</x:v>
+      </x:c>
       <x:c r="AF31" s="41" t="str">
-        <x:f>IF('Independent Review'!Q29="","",'Independent Review'!Q29)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG31" s="41" t="str">
-        <x:f>IF('Independent Review'!R29="","",'Independent Review'!R29)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH31" s="42" t="str">
         <x:f>IF(B31&lt;&gt;"complete","",IF(OR(W31="",X31="",Y31="",Z31="",AA31="",AB31="",AD31="",AF31="",AG31=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="70" customHeight="1">
@@ -3481,8 +3823,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="40" t="str">
-        <x:f>IF('Independent Review'!B30="","",'Independent Review'!B30)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C32" s="40" t="str">
         <x:v>NEWS-guardian_api-88e751d96451</x:v>
@@ -3541,28 +3882,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W32" s="41" t="str">
-        <x:f>IF('Independent Review'!M30="","",'Independent Review'!M30)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X32" s="41" t="str">
-        <x:f>IF('Independent Review'!N30="","",'Independent Review'!N30)</x:f>
-      </x:c>
-      <x:c r="Y32" s="41" t="str"/>
-      <x:c r="Z32" s="41" t="str"/>
-      <x:c r="AA32" s="41" t="str"/>
-      <x:c r="AB32" s="41" t="str"/>
-      <x:c r="AC32" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y32" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z32" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA32" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB32" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC32" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD32" s="49" t="str">
-        <x:f>IF('Independent Review'!O30="","",'Independent Review'!O30)</x:f>
-      </x:c>
-      <x:c r="AE32" s="49" t="str"/>
+        <x:v>The impact of the Brexit vote on higher education is too early to call.</x:v>
+      </x:c>
+      <x:c r="AE32" s="49" t="str">
+        <x:v>The article examines the effect of the Brexit vote on UK universities and European students. Brexit and its domestic political consequences fall within UK national politics under N1.</x:v>
+      </x:c>
       <x:c r="AF32" s="41" t="str">
-        <x:f>IF('Independent Review'!Q30="","",'Independent Review'!Q30)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG32" s="41" t="str">
-        <x:f>IF('Independent Review'!R30="","",'Independent Review'!R30)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH32" s="42" t="str">
         <x:f>IF(B32&lt;&gt;"complete","",IF(OR(W32="",X32="",Y32="",Z32="",AA32="",AB32="",AD32="",AF32="",AG32=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="70" customHeight="1">
@@ -3570,8 +3924,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="40" t="str">
-        <x:f>IF('Independent Review'!B31="","",'Independent Review'!B31)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C33" s="40" t="str">
         <x:v>NEWS-guardian_api-8a849cd56bab</x:v>
@@ -3630,28 +3983,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W33" s="41" t="str">
-        <x:f>IF('Independent Review'!M31="","",'Independent Review'!M31)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X33" s="41" t="str">
-        <x:f>IF('Independent Review'!N31="","",'Independent Review'!N31)</x:f>
-      </x:c>
-      <x:c r="Y33" s="41" t="str"/>
-      <x:c r="Z33" s="41" t="str"/>
-      <x:c r="AA33" s="41" t="str"/>
-      <x:c r="AB33" s="41" t="str"/>
-      <x:c r="AC33" s="41" t="str"/>
+        <x:v>N3</x:v>
+      </x:c>
+      <x:c r="Y33" s="41" t="str">
+        <x:v>evidence_beyond_excerpt</x:v>
+      </x:c>
+      <x:c r="Z33" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA33" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB33" s="41" t="str">
+        <x:v>input_fix</x:v>
+      </x:c>
+      <x:c r="AC33" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD33" s="49" t="str">
-        <x:f>IF('Independent Review'!O31="","",'Independent Review'!O31)</x:f>
-      </x:c>
-      <x:c r="AE33" s="49" t="str"/>
+        <x:v>Nigel Farage and his allies have relaunched their political party, encouraging people to walk past their local war memorial on Remembrance Sunday in a low-key anti-lockdown protest that marks a fresh attempt to restore its political relevance.</x:v>
+      </x:c>
+      <x:c r="AE33" s="49" t="str">
+        <x:v>The live blog contains a substantive UK entry on Nigel Farage relaunching his party and attempting to restore its political relevance. That entry supplies N3 new-party evidence even though the blog also covers international Covid news.</x:v>
+      </x:c>
       <x:c r="AF33" s="41" t="str">
-        <x:f>IF('Independent Review'!Q31="","",'Independent Review'!Q31)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG33" s="41" t="str">
-        <x:f>IF('Independent Review'!R31="","",'Independent Review'!R31)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH33" s="42" t="str">
         <x:f>IF(B33&lt;&gt;"complete","",IF(OR(W33="",X33="",Y33="",Z33="",AA33="",AB33="",AD33="",AF33="",AG33=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="70" customHeight="1">
@@ -3659,8 +4025,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="40" t="str">
-        <x:f>IF('Independent Review'!B32="","",'Independent Review'!B32)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C34" s="40" t="str">
         <x:v>NEWS-guardian_api-8c28af0f119c</x:v>
@@ -3721,28 +4086,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W34" s="41" t="str">
-        <x:f>IF('Independent Review'!M32="","",'Independent Review'!M32)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X34" s="41" t="str">
-        <x:f>IF('Independent Review'!N32="","",'Independent Review'!N32)</x:f>
-      </x:c>
-      <x:c r="Y34" s="41" t="str"/>
-      <x:c r="Z34" s="41" t="str"/>
-      <x:c r="AA34" s="41" t="str"/>
-      <x:c r="AB34" s="41" t="str"/>
-      <x:c r="AC34" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y34" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z34" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA34" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB34" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC34" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD34" s="49" t="str">
-        <x:f>IF('Independent Review'!O32="","",'Independent Review'!O32)</x:f>
-      </x:c>
-      <x:c r="AE34" s="49" t="str"/>
+        <x:v>Kemi Badenoch has been accused of weaponising violence against women and girls and using “dangerous” and “deeply inaccurate” claims in her response to the government’s plan to tackle the issue.</x:v>
+      </x:c>
+      <x:c r="AE34" s="49" t="str">
+        <x:v>The live blog is UK national party and government coverage. It contains no substantive sampled Surrey linkage and therefore fails the local-arm L1-L4 test.</x:v>
+      </x:c>
       <x:c r="AF34" s="41" t="str">
-        <x:f>IF('Independent Review'!Q32="","",'Independent Review'!Q32)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG34" s="41" t="str">
-        <x:f>IF('Independent Review'!R32="","",'Independent Review'!R32)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH34" s="42" t="str">
         <x:f>IF(B34&lt;&gt;"complete","",IF(OR(W34="",X34="",Y34="",Z34="",AA34="",AB34="",AD34="",AF34="",AG34=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="70" customHeight="1">
@@ -3750,8 +4128,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="40" t="str">
-        <x:f>IF('Independent Review'!B33="","",'Independent Review'!B33)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C35" s="40" t="str">
         <x:v>NEWS-guardian_api-8e547ee6efe6</x:v>
@@ -3812,28 +4189,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W35" s="41" t="str">
-        <x:f>IF('Independent Review'!M33="","",'Independent Review'!M33)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X35" s="41" t="str">
-        <x:f>IF('Independent Review'!N33="","",'Independent Review'!N33)</x:f>
-      </x:c>
-      <x:c r="Y35" s="41" t="str"/>
-      <x:c r="Z35" s="41" t="str"/>
-      <x:c r="AA35" s="41" t="str"/>
-      <x:c r="AB35" s="41" t="str"/>
-      <x:c r="AC35" s="41" t="str"/>
+        <x:v>N3</x:v>
+      </x:c>
+      <x:c r="Y35" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z35" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA35" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB35" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC35" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD35" s="49" t="str">
-        <x:f>IF('Independent Review'!O33="","",'Independent Review'!O33)</x:f>
-      </x:c>
-      <x:c r="AE35" s="49" t="str"/>
+        <x:v>Nigel Farage has unveiled the first part of Reform UK’s frontbench team, saying it shows that the party is no longer reliant entirely on him – while also warning that he will not tolerate any dissent from his colleagues.</x:v>
+      </x:c>
+      <x:c r="AE35" s="49" t="str">
+        <x:v>The live blog contains strong national Reform UK coverage, but the record is local-arm. A historical passing reference to an unnamed Surrey councillor does not satisfy L1-L4.</x:v>
+      </x:c>
       <x:c r="AF35" s="41" t="str">
-        <x:f>IF('Independent Review'!Q33="","",'Independent Review'!Q33)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG35" s="41" t="str">
-        <x:f>IF('Independent Review'!R33="","",'Independent Review'!R33)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH35" s="42" t="str">
         <x:f>IF(B35&lt;&gt;"complete","",IF(OR(W35="",X35="",Y35="",Z35="",AA35="",AB35="",AD35="",AF35="",AG35=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="70" customHeight="1">
@@ -3841,8 +4231,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="40" t="str">
-        <x:f>IF('Independent Review'!B34="","",'Independent Review'!B34)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C36" s="40" t="str">
         <x:v>NEWS-guardian_api-8f21ed1fa60a</x:v>
@@ -3899,28 +4288,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W36" s="41" t="str">
-        <x:f>IF('Independent Review'!M34="","",'Independent Review'!M34)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X36" s="41" t="str">
-        <x:f>IF('Independent Review'!N34="","",'Independent Review'!N34)</x:f>
-      </x:c>
-      <x:c r="Y36" s="41" t="str"/>
-      <x:c r="Z36" s="41" t="str"/>
-      <x:c r="AA36" s="41" t="str"/>
-      <x:c r="AB36" s="41" t="str"/>
-      <x:c r="AC36" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y36" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z36" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA36" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB36" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC36" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD36" s="49" t="str">
-        <x:f>IF('Independent Review'!O34="","",'Independent Review'!O34)</x:f>
-      </x:c>
-      <x:c r="AE36" s="49" t="str"/>
+        <x:v>BBC’s Newsnight’s take on the reported acrimony between Boris Johnson and his advisers.</x:v>
+      </x:c>
+      <x:c r="AE36" s="49" t="str">
+        <x:v>The live blog directly covers senior Downing Street advisers, Boris Johnson and the operation of government. This is N1 government-performance coverage.</x:v>
+      </x:c>
       <x:c r="AF36" s="41" t="str">
-        <x:f>IF('Independent Review'!Q34="","",'Independent Review'!Q34)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG36" s="41" t="str">
-        <x:f>IF('Independent Review'!R34="","",'Independent Review'!R34)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH36" s="42" t="str">
         <x:f>IF(B36&lt;&gt;"complete","",IF(OR(W36="",X36="",Y36="",Z36="",AA36="",AB36="",AD36="",AF36="",AG36=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="70" customHeight="1">
@@ -3928,8 +4330,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="40" t="str">
-        <x:f>IF('Independent Review'!B35="","",'Independent Review'!B35)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C37" s="40" t="str">
         <x:v>NEWS-guardian_api-8f8e97810c4d</x:v>
@@ -3990,28 +4391,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W37" s="41" t="str">
-        <x:f>IF('Independent Review'!M35="","",'Independent Review'!M35)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X37" s="41" t="str">
-        <x:f>IF('Independent Review'!N35="","",'Independent Review'!N35)</x:f>
-      </x:c>
-      <x:c r="Y37" s="41" t="str"/>
-      <x:c r="Z37" s="41" t="str"/>
-      <x:c r="AA37" s="41" t="str"/>
-      <x:c r="AB37" s="41" t="str"/>
-      <x:c r="AC37" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y37" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z37" s="41" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="AA37" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB37" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC37" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD37" s="49" t="str">
-        <x:f>IF('Independent Review'!O35="","",'Independent Review'!O35)</x:f>
-      </x:c>
-      <x:c r="AE37" s="49" t="str"/>
+        <x:v>Traditional Boxing Day hunts across large parts of the UK have been cancelled due to coronavirus restrictions, with those going ahead elsewhere not parading through town centres prior to their yuletide meet this year for the first time in recent history.</x:v>
+      </x:c>
+      <x:c r="AE37" s="49" t="str">
+        <x:v>The article concerns hunting restrictions across Britain and a Peterborough council decision. It does not concern a Surrey council issue affecting a sampled area.</x:v>
+      </x:c>
       <x:c r="AF37" s="41" t="str">
-        <x:f>IF('Independent Review'!Q35="","",'Independent Review'!Q35)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG37" s="41" t="str">
-        <x:f>IF('Independent Review'!R35="","",'Independent Review'!R35)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH37" s="42" t="str">
         <x:f>IF(B37&lt;&gt;"complete","",IF(OR(W37="",X37="",Y37="",Z37="",AA37="",AB37="",AD37="",AF37="",AG37=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="70" customHeight="1">
@@ -4019,8 +4433,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="40" t="str">
-        <x:f>IF('Independent Review'!B36="","",'Independent Review'!B36)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C38" s="40" t="str">
         <x:v>NEWS-guardian_api-95d73413bd9b</x:v>
@@ -4081,28 +4494,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W38" s="41" t="str">
-        <x:f>IF('Independent Review'!M36="","",'Independent Review'!M36)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X38" s="41" t="str">
-        <x:f>IF('Independent Review'!N36="","",'Independent Review'!N36)</x:f>
-      </x:c>
-      <x:c r="Y38" s="41" t="str"/>
-      <x:c r="Z38" s="41" t="str"/>
-      <x:c r="AA38" s="41" t="str"/>
-      <x:c r="AB38" s="41" t="str"/>
-      <x:c r="AC38" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y38" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z38" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA38" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB38" s="41" t="str">
+        <x:v>human_label_adjudication</x:v>
+      </x:c>
+      <x:c r="AC38" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD38" s="49" t="str">
-        <x:f>IF('Independent Review'!O36="","",'Independent Review'!O36)</x:f>
-      </x:c>
-      <x:c r="AE38" s="49" t="str"/>
+        <x:v>Nigel Farage has redoubled his efforts to become irritant-in-chief to British ministers in the wake of Donald Trump’s election by suggesting their earlier criticisms of the president-elect could have meant he delayed speaking to Theresa May.</x:v>
+      </x:c>
+      <x:c r="AE38" s="49" t="str">
+        <x:v>The article concerns Nigel Farage, Theresa May, Boris Johnson and UK relations with the incoming US administration. It clearly meets N1, but it is not primarily evidence of UKIP/Reform growth under N3.</x:v>
+      </x:c>
       <x:c r="AF38" s="41" t="str">
-        <x:f>IF('Independent Review'!Q36="","",'Independent Review'!Q36)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG38" s="41" t="str">
-        <x:f>IF('Independent Review'!R36="","",'Independent Review'!R36)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH38" s="42" t="str">
         <x:f>IF(B38&lt;&gt;"complete","",IF(OR(W38="",X38="",Y38="",Z38="",AA38="",AB38="",AD38="",AF38="",AG38=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="70" customHeight="1">
@@ -4110,8 +4536,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="40" t="str">
-        <x:f>IF('Independent Review'!B37="","",'Independent Review'!B37)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C39" s="40" t="str">
         <x:v>NEWS-guardian_api-97b3a5489c02</x:v>
@@ -4170,28 +4595,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W39" s="41" t="str">
-        <x:f>IF('Independent Review'!M37="","",'Independent Review'!M37)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X39" s="41" t="str">
-        <x:f>IF('Independent Review'!N37="","",'Independent Review'!N37)</x:f>
-      </x:c>
-      <x:c r="Y39" s="41" t="str"/>
-      <x:c r="Z39" s="41" t="str"/>
-      <x:c r="AA39" s="41" t="str"/>
-      <x:c r="AB39" s="41" t="str"/>
-      <x:c r="AC39" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y39" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z39" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA39" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB39" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC39" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD39" s="49" t="str">
-        <x:f>IF('Independent Review'!O37="","",'Independent Review'!O37)</x:f>
-      </x:c>
-      <x:c r="AE39" s="49" t="str"/>
+        <x:v>(See 4.59pm.) Labour has written to Boris Johnson asking him to correct the record after Downing Street repeatedly refused to acknowledge that the prime minister was mistaken when he said the party had voted against an NHS pay deal.</x:v>
+      </x:c>
+      <x:c r="AE39" s="49" t="str">
+        <x:v>The live blog substantively discusses UK Covid testing, vaccination policy and an NHS pay dispute. These are NHS/public-service issues under N2.</x:v>
+      </x:c>
       <x:c r="AF39" s="41" t="str">
-        <x:f>IF('Independent Review'!Q37="","",'Independent Review'!Q37)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG39" s="41" t="str">
-        <x:f>IF('Independent Review'!R37="","",'Independent Review'!R37)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH39" s="42" t="str">
         <x:f>IF(B39&lt;&gt;"complete","",IF(OR(W39="",X39="",Y39="",Z39="",AA39="",AB39="",AD39="",AF39="",AG39=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="70" customHeight="1">
@@ -4199,8 +4637,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="40" t="str">
-        <x:f>IF('Independent Review'!B38="","",'Independent Review'!B38)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C40" s="40" t="str">
         <x:v>NEWS-guardian_api-9dea17fa1487</x:v>
@@ -4257,28 +4694,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W40" s="41" t="str">
-        <x:f>IF('Independent Review'!M38="","",'Independent Review'!M38)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X40" s="41" t="str">
-        <x:f>IF('Independent Review'!N38="","",'Independent Review'!N38)</x:f>
-      </x:c>
-      <x:c r="Y40" s="41" t="str"/>
-      <x:c r="Z40" s="41" t="str"/>
-      <x:c r="AA40" s="41" t="str"/>
-      <x:c r="AB40" s="41" t="str"/>
-      <x:c r="AC40" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y40" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z40" s="41" t="str">
+        <x:v>surrey_wide_rule_misapplied</x:v>
+      </x:c>
+      <x:c r="AA40" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB40" s="41" t="str">
+        <x:v>codebook_review</x:v>
+      </x:c>
+      <x:c r="AC40" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD40" s="49" t="str">
-        <x:f>IF('Independent Review'!O38="","",'Independent Review'!O38)</x:f>
-      </x:c>
-      <x:c r="AE40" s="49" t="str"/>
+        <x:v>Liverpool city region, York, North Yorkshire, Cambridgeshire, Norfolk, Essex, East Sussex, Surrey, Oxfordshire, Dorset and Devon are among other locations in tier 2.</x:v>
+      </x:c>
+      <x:c r="AE40" s="49" t="str">
+        <x:v>The article explains national Covid tier rules and lists Surrey among many tier-2 areas. It does not name a sampled division or town, concern a Surrey council decision, or provide Surrey-wide political coverage.</x:v>
+      </x:c>
       <x:c r="AF40" s="41" t="str">
-        <x:f>IF('Independent Review'!Q38="","",'Independent Review'!Q38)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG40" s="41" t="str">
-        <x:f>IF('Independent Review'!R38="","",'Independent Review'!R38)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH40" s="42" t="str">
         <x:f>IF(B40&lt;&gt;"complete","",IF(OR(W40="",X40="",Y40="",Z40="",AA40="",AB40="",AD40="",AF40="",AG40=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="70" customHeight="1">
@@ -4286,8 +4736,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B41" s="40" t="str">
-        <x:f>IF('Independent Review'!B39="","",'Independent Review'!B39)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C41" s="40" t="str">
         <x:v>NEWS-guardian_api-a3577fa415ba</x:v>
@@ -4348,28 +4797,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W41" s="41" t="str">
-        <x:f>IF('Independent Review'!M39="","",'Independent Review'!M39)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X41" s="41" t="str">
-        <x:f>IF('Independent Review'!N39="","",'Independent Review'!N39)</x:f>
-      </x:c>
-      <x:c r="Y41" s="41" t="str"/>
-      <x:c r="Z41" s="41" t="str"/>
-      <x:c r="AA41" s="41" t="str"/>
-      <x:c r="AB41" s="41" t="str"/>
-      <x:c r="AC41" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y41" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z41" s="41" t="str">
+        <x:v>national_policy_scope_too_broad</x:v>
+      </x:c>
+      <x:c r="AA41" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB41" s="41" t="str">
+        <x:v>human_label_adjudication</x:v>
+      </x:c>
+      <x:c r="AC41" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD41" s="49" t="str">
-        <x:f>IF('Independent Review'!O39="","",'Independent Review'!O39)</x:f>
-      </x:c>
-      <x:c r="AE41" s="49" t="str"/>
+        <x:v>We’ve launched a new blog at the link below – head there for the latest: Israel is set to ban passenger flights in attempt to prevent Covid variant imports, coming into effect from Monday 10pm for two weeks Greek health authorities have reported a jump in the number of cases of the coronavirus variant first spotted in the UK, with 32 infections detected.</x:v>
+      </x:c>
+      <x:c r="AE41" s="49" t="str">
+        <x:v>The article is principally an international Covid live blog led by Israel and Greece. UK figures and comments appear among many updates, but the article is not substantively focused on a specified UK national policy issue.</x:v>
+      </x:c>
       <x:c r="AF41" s="41" t="str">
-        <x:f>IF('Independent Review'!Q39="","",'Independent Review'!Q39)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG41" s="41" t="str">
-        <x:f>IF('Independent Review'!R39="","",'Independent Review'!R39)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH41" s="42" t="str">
         <x:f>IF(B41&lt;&gt;"complete","",IF(OR(W41="",X41="",Y41="",Z41="",AA41="",AB41="",AD41="",AF41="",AG41=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="70" customHeight="1">
@@ -4377,8 +4839,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="40" t="str">
-        <x:f>IF('Independent Review'!B40="","",'Independent Review'!B40)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C42" s="40" t="str">
         <x:v>NEWS-guardian_api-ab4a777c619a</x:v>
@@ -4439,28 +4900,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W42" s="41" t="str">
-        <x:f>IF('Independent Review'!M40="","",'Independent Review'!M40)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X42" s="41" t="str">
-        <x:f>IF('Independent Review'!N40="","",'Independent Review'!N40)</x:f>
-      </x:c>
-      <x:c r="Y42" s="41" t="str"/>
-      <x:c r="Z42" s="41" t="str"/>
-      <x:c r="AA42" s="41" t="str"/>
-      <x:c r="AB42" s="41" t="str"/>
-      <x:c r="AC42" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y42" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z42" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA42" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB42" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC42" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD42" s="49" t="str">
-        <x:f>IF('Independent Review'!O40="","",'Independent Review'!O40)</x:f>
-      </x:c>
-      <x:c r="AE42" s="49" t="str"/>
+        <x:v>It is far too easy to impersonate someone at a polling station and claim their vote (Voters in local elections will be required to show ID in anti-fraud trials, 28 December).</x:v>
+      </x:c>
+      <x:c r="AE42" s="49" t="str">
+        <x:v>The letters concern national voter identification and electoral registration. They contain no sampled Surrey place or council issue for the local arm.</x:v>
+      </x:c>
       <x:c r="AF42" s="41" t="str">
-        <x:f>IF('Independent Review'!Q40="","",'Independent Review'!Q40)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG42" s="41" t="str">
-        <x:f>IF('Independent Review'!R40="","",'Independent Review'!R40)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH42" s="42" t="str">
         <x:f>IF(B42&lt;&gt;"complete","",IF(OR(W42="",X42="",Y42="",Z42="",AA42="",AB42="",AD42="",AF42="",AG42=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="70" customHeight="1">
@@ -4468,8 +4942,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B43" s="40" t="str">
-        <x:f>IF('Independent Review'!B41="","",'Independent Review'!B41)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C43" s="40" t="str">
         <x:v>NEWS-guardian_api-b48d01a86b76</x:v>
@@ -4530,28 +5003,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W43" s="41" t="str">
-        <x:f>IF('Independent Review'!M41="","",'Independent Review'!M41)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X43" s="41" t="str">
-        <x:f>IF('Independent Review'!N41="","",'Independent Review'!N41)</x:f>
-      </x:c>
-      <x:c r="Y43" s="41" t="str"/>
-      <x:c r="Z43" s="41" t="str"/>
-      <x:c r="AA43" s="41" t="str"/>
-      <x:c r="AB43" s="41" t="str"/>
-      <x:c r="AC43" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y43" s="41" t="str">
+        <x:v>evidence_beyond_excerpt</x:v>
+      </x:c>
+      <x:c r="Z43" s="41" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="AA43" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB43" s="41" t="str">
+        <x:v>human_label_adjudication</x:v>
+      </x:c>
+      <x:c r="AC43" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD43" s="49" t="str">
-        <x:f>IF('Independent Review'!O41="","",'Independent Review'!O41)</x:f>
-      </x:c>
-      <x:c r="AE43" s="49" t="str"/>
+        <x:v>Surrey and Thames Valley police forces are considering claims of sexual wrongdoing by the former prince.</x:v>
+      </x:c>
+      <x:c r="AE43" s="49" t="str">
+        <x:v>The article concerns police investigations into Andrew Mountbatten-Windsor. Mention of Surrey Police is not a Surrey council decision or service and no effect on a sampled division is established.</x:v>
+      </x:c>
       <x:c r="AF43" s="41" t="str">
-        <x:f>IF('Independent Review'!Q41="","",'Independent Review'!Q41)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG43" s="41" t="str">
-        <x:f>IF('Independent Review'!R41="","",'Independent Review'!R41)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH43" s="42" t="str">
         <x:f>IF(B43&lt;&gt;"complete","",IF(OR(W43="",X43="",Y43="",Z43="",AA43="",AB43="",AD43="",AF43="",AG43=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="70" customHeight="1">
@@ -4559,8 +5045,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="40" t="str">
-        <x:f>IF('Independent Review'!B42="","",'Independent Review'!B42)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>needs_adjudication</x:v>
       </x:c>
       <x:c r="C44" s="40" t="str">
         <x:v>NEWS-guardian_api-b9d210492f43</x:v>
@@ -4619,25 +5104,37 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W44" s="41" t="str">
-        <x:f>IF('Independent Review'!M42="","",'Independent Review'!M42)</x:f>
+        <x:v>needs_second_review</x:v>
       </x:c>
       <x:c r="X44" s="41" t="str">
-        <x:f>IF('Independent Review'!N42="","",'Independent Review'!N42)</x:f>
-      </x:c>
-      <x:c r="Y44" s="41" t="str"/>
-      <x:c r="Z44" s="41" t="str"/>
-      <x:c r="AA44" s="41" t="str"/>
-      <x:c r="AB44" s="41" t="str"/>
-      <x:c r="AC44" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y44" s="41" t="str">
+        <x:v>missing_query_context</x:v>
+      </x:c>
+      <x:c r="Z44" s="41" t="str">
+        <x:v>codebook_boundary_unclear</x:v>
+      </x:c>
+      <x:c r="AA44" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB44" s="41" t="str">
+        <x:v>codebook_review</x:v>
+      </x:c>
+      <x:c r="AC44" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD44" s="49" t="str">
-        <x:f>IF('Independent Review'!O42="","",'Independent Review'!O42)</x:f>
-      </x:c>
-      <x:c r="AE44" s="49" t="str"/>
+        <x:v>Areas moving to tier 4 are Sussex, Oxfordshire, Suffolk, Norfolk and Cambridgeshire, parts of Essex not yet in the highest tier, Waverley in Surrey and Hampshire, with the exception of the New Forest.</x:v>
+      </x:c>
+      <x:c r="AE44" s="49" t="str">
+        <x:v>The article states that Waverley in Surrey moved to tier 4, which substantively affects areas containing sampled divisions. The current L3 wording, however, requires a Surrey council decision/service/issue; national Covid restrictions do not clearly satisfy that condition.</x:v>
+      </x:c>
       <x:c r="AF44" s="41" t="str">
-        <x:f>IF('Independent Review'!Q42="","",'Independent Review'!Q42)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG44" s="41" t="str">
-        <x:f>IF('Independent Review'!R42="","",'Independent Review'!R42)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH44" s="42" t="str">
         <x:f>IF(B44&lt;&gt;"complete","",IF(OR(W44="",X44="",Y44="",Z44="",AA44="",AB44="",AD44="",AF44="",AG44=""),"MISSING REQUIRED FIELD","OK"))</x:f>
@@ -4648,8 +5145,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B45" s="40" t="str">
-        <x:f>IF('Independent Review'!B43="","",'Independent Review'!B43)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C45" s="40" t="str">
         <x:v>NEWS-guardian_api-be5b11434a57</x:v>
@@ -4710,28 +5206,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W45" s="41" t="str">
-        <x:f>IF('Independent Review'!M43="","",'Independent Review'!M43)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X45" s="41" t="str">
-        <x:f>IF('Independent Review'!N43="","",'Independent Review'!N43)</x:f>
-      </x:c>
-      <x:c r="Y45" s="41" t="str"/>
-      <x:c r="Z45" s="41" t="str"/>
-      <x:c r="AA45" s="41" t="str"/>
-      <x:c r="AB45" s="41" t="str"/>
-      <x:c r="AC45" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y45" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z45" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA45" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB45" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC45" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD45" s="49" t="str">
-        <x:f>IF('Independent Review'!O43="","",'Independent Review'!O43)</x:f>
-      </x:c>
-      <x:c r="AE45" s="49" t="str"/>
+        <x:v>Homelessness campaigners have demanded an urgent reboot of the government’s “Everybody In” scheme in England to provide safe shelter for thousands of rough sleepers as the UK enters another lockdown, with winter temperatures expected to plummet.</x:v>
+      </x:c>
+      <x:c r="AE45" s="49" t="str">
+        <x:v>The article concerns national homelessness policy and the duties of English local authorities during lockdown. This is a substantive public-service and local-government issue under N2.</x:v>
+      </x:c>
       <x:c r="AF45" s="41" t="str">
-        <x:f>IF('Independent Review'!Q43="","",'Independent Review'!Q43)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG45" s="41" t="str">
-        <x:f>IF('Independent Review'!R43="","",'Independent Review'!R43)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH45" s="42" t="str">
         <x:f>IF(B45&lt;&gt;"complete","",IF(OR(W45="",X45="",Y45="",Z45="",AA45="",AB45="",AD45="",AF45="",AG45=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="70" customHeight="1">
@@ -4739,8 +5248,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B46" s="40" t="str">
-        <x:f>IF('Independent Review'!B44="","",'Independent Review'!B44)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C46" s="40" t="str">
         <x:v>NEWS-guardian_api-c726af230abd</x:v>
@@ -4801,28 +5309,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W46" s="41" t="str">
-        <x:f>IF('Independent Review'!M44="","",'Independent Review'!M44)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X46" s="41" t="str">
-        <x:f>IF('Independent Review'!N44="","",'Independent Review'!N44)</x:f>
-      </x:c>
-      <x:c r="Y46" s="41" t="str"/>
-      <x:c r="Z46" s="41" t="str"/>
-      <x:c r="AA46" s="41" t="str"/>
-      <x:c r="AB46" s="41" t="str"/>
-      <x:c r="AC46" s="41" t="str"/>
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="Y46" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z46" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA46" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB46" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC46" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD46" s="49" t="str">
-        <x:f>IF('Independent Review'!O44="","",'Independent Review'!O44)</x:f>
-      </x:c>
-      <x:c r="AE46" s="49" t="str"/>
+        <x:v>Dozens of children and young people with mental health problems are still being treated on wards containing adults with sometimes severe psychiatric problems despite ministers having supposedly outlawed the practice in 2010, the Guardian can reveal.</x:v>
+      </x:c>
+      <x:c r="AE46" s="49" t="str">
+        <x:v>The article concerns children being treated on adult NHS psychiatric wards and ministerial responsibility. It directly satisfies the NHS/public-services branch of N2.</x:v>
+      </x:c>
       <x:c r="AF46" s="41" t="str">
-        <x:f>IF('Independent Review'!Q44="","",'Independent Review'!Q44)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG46" s="41" t="str">
-        <x:f>IF('Independent Review'!R44="","",'Independent Review'!R44)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH46" s="42" t="str">
         <x:f>IF(B46&lt;&gt;"complete","",IF(OR(W46="",X46="",Y46="",Z46="",AA46="",AB46="",AD46="",AF46="",AG46=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="70" customHeight="1">
@@ -4830,8 +5351,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B47" s="40" t="str">
-        <x:f>IF('Independent Review'!B45="","",'Independent Review'!B45)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C47" s="40" t="str">
         <x:v>NEWS-guardian_api-cc8e272342e5</x:v>
@@ -4892,28 +5412,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W47" s="41" t="str">
-        <x:f>IF('Independent Review'!M45="","",'Independent Review'!M45)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X47" s="41" t="str">
-        <x:f>IF('Independent Review'!N45="","",'Independent Review'!N45)</x:f>
-      </x:c>
-      <x:c r="Y47" s="41" t="str"/>
-      <x:c r="Z47" s="41" t="str"/>
-      <x:c r="AA47" s="41" t="str"/>
-      <x:c r="AB47" s="41" t="str"/>
-      <x:c r="AC47" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y47" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z47" s="41" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="AA47" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB47" s="41" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="AC47" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD47" s="49" t="str">
-        <x:f>IF('Independent Review'!O45="","",'Independent Review'!O45)</x:f>
-      </x:c>
-      <x:c r="AE47" s="49" t="str"/>
+        <x:v>A brilliant interview as always from Zoe Williams (‘We thought the Rwanda scheme was the worst of it’: Enver Solomon on leading – and leaving – the Refugee Council, 24 November).</x:v>
+      </x:c>
+      <x:c r="AE47" s="49" t="str">
+        <x:v>The letter comments on national governments and the Labour party but contains no sampled Surrey place, candidate or council issue. National political content cannot satisfy a local L-rule.</x:v>
+      </x:c>
       <x:c r="AF47" s="41" t="str">
-        <x:f>IF('Independent Review'!Q45="","",'Independent Review'!Q45)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG47" s="41" t="str">
-        <x:f>IF('Independent Review'!R45="","",'Independent Review'!R45)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH47" s="42" t="str">
         <x:f>IF(B47&lt;&gt;"complete","",IF(OR(W47="",X47="",Y47="",Z47="",AA47="",AB47="",AD47="",AF47="",AG47=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="70" customHeight="1">
@@ -4921,8 +5454,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="40" t="str">
-        <x:f>IF('Independent Review'!B46="","",'Independent Review'!B46)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C48" s="40" t="str">
         <x:v>NEWS-guardian_api-d12e8db585f0</x:v>
@@ -4983,28 +5515,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W48" s="41" t="str">
-        <x:f>IF('Independent Review'!M46="","",'Independent Review'!M46)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X48" s="41" t="str">
-        <x:f>IF('Independent Review'!N46="","",'Independent Review'!N46)</x:f>
-      </x:c>
-      <x:c r="Y48" s="41" t="str"/>
-      <x:c r="Z48" s="41" t="str"/>
-      <x:c r="AA48" s="41" t="str"/>
-      <x:c r="AB48" s="41" t="str"/>
-      <x:c r="AC48" s="41" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y48" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z48" s="41" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="AA48" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB48" s="41" t="str">
+        <x:v>few_shot_example</x:v>
+      </x:c>
+      <x:c r="AC48" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="AD48" s="49" t="str">
-        <x:f>IF('Independent Review'!O46="","",'Independent Review'!O46)</x:f>
-      </x:c>
-      <x:c r="AE48" s="49" t="str"/>
+        <x:v>Polly Toynbee is correct to point out the foolishness of a massive local government reorganisation, given other priorities (Is No 10 seeking its own destruction?</x:v>
+      </x:c>
+      <x:c r="AE48" s="49" t="str">
+        <x:v>The letter discusses local-government reorganisation nationally. Guildford appears only in the writer's address, which is not substantive evidence of an effect on a sampled division.</x:v>
+      </x:c>
       <x:c r="AF48" s="41" t="str">
-        <x:f>IF('Independent Review'!Q46="","",'Independent Review'!Q46)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG48" s="41" t="str">
-        <x:f>IF('Independent Review'!R46="","",'Independent Review'!R46)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH48" s="42" t="str">
         <x:f>IF(B48&lt;&gt;"complete","",IF(OR(W48="",X48="",Y48="",Z48="",AA48="",AB48="",AD48="",AF48="",AG48=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="70" customHeight="1">
@@ -5012,8 +5557,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="40" t="str">
-        <x:f>IF('Independent Review'!B47="","",'Independent Review'!B47)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C49" s="40" t="str">
         <x:v>NEWS-guardian_api-de14fda465d9</x:v>
@@ -5072,28 +5616,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W49" s="41" t="str">
-        <x:f>IF('Independent Review'!M47="","",'Independent Review'!M47)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X49" s="41" t="str">
-        <x:f>IF('Independent Review'!N47="","",'Independent Review'!N47)</x:f>
-      </x:c>
-      <x:c r="Y49" s="41" t="str"/>
-      <x:c r="Z49" s="41" t="str"/>
-      <x:c r="AA49" s="41" t="str"/>
-      <x:c r="AB49" s="41" t="str"/>
-      <x:c r="AC49" s="41" t="str"/>
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="Y49" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z49" s="41" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="AA49" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB49" s="41" t="str">
+        <x:v>human_label_adjudication</x:v>
+      </x:c>
+      <x:c r="AC49" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD49" s="49" t="str">
-        <x:f>IF('Independent Review'!O47="","",'Independent Review'!O47)</x:f>
-      </x:c>
-      <x:c r="AE49" s="49" t="str"/>
+        <x:v>Co-edited by Fowler, it highlighted that 93 trust properties, including Clandon Park in Surrey and Hare Hill in Cheshire, were linked to wealth from plantations and the slave trade, while others, such as Bateman’s, Rudyard Kipling’s home in Sussex, were important to understanding Britain’s colonial history.</x:v>
+      </x:c>
+      <x:c r="AE49" s="49" t="str">
+        <x:v>The article is about a national controversy over National Trust colonial-history research. Clandon Park is one item in a list of 93 properties and is not the substantive subject of the report.</x:v>
+      </x:c>
       <x:c r="AF49" s="41" t="str">
-        <x:f>IF('Independent Review'!Q47="","",'Independent Review'!Q47)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG49" s="41" t="str">
-        <x:f>IF('Independent Review'!R47="","",'Independent Review'!R47)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH49" s="42" t="str">
         <x:f>IF(B49&lt;&gt;"complete","",IF(OR(W49="",X49="",Y49="",Z49="",AA49="",AB49="",AD49="",AF49="",AG49=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="70" customHeight="1">
@@ -5101,8 +5658,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="40" t="str">
-        <x:f>IF('Independent Review'!B48="","",'Independent Review'!B48)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C50" s="40" t="str">
         <x:v>NEWS-guardian_api-e2001566d58a</x:v>
@@ -5163,28 +5719,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W50" s="41" t="str">
-        <x:f>IF('Independent Review'!M48="","",'Independent Review'!M48)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X50" s="41" t="str">
-        <x:f>IF('Independent Review'!N48="","",'Independent Review'!N48)</x:f>
-      </x:c>
-      <x:c r="Y50" s="41" t="str"/>
-      <x:c r="Z50" s="41" t="str"/>
-      <x:c r="AA50" s="41" t="str"/>
-      <x:c r="AB50" s="41" t="str"/>
-      <x:c r="AC50" s="41" t="str"/>
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="Y50" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z50" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA50" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB50" s="41" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC50" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD50" s="49" t="str">
-        <x:f>IF('Independent Review'!O48="","",'Independent Review'!O48)</x:f>
-      </x:c>
-      <x:c r="AE50" s="49" t="str"/>
+        <x:v>David Cameron has arrived in the Gulf at the beginning of a low-key arms trip aimed at persuading regional powers upset by Britain's response to the Arab spring to buy more than 100 Eurofighter Typhoon fighter jets.</x:v>
+      </x:c>
+      <x:c r="AE50" s="49" t="str">
+        <x:v>The article reports the prime minister's arms-trade diplomacy, government policy and human-rights criticism. This is substantive UK government-performance coverage under N1.</x:v>
+      </x:c>
       <x:c r="AF50" s="41" t="str">
-        <x:f>IF('Independent Review'!Q48="","",'Independent Review'!Q48)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG50" s="41" t="str">
-        <x:f>IF('Independent Review'!R48="","",'Independent Review'!R48)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH50" s="42" t="str">
         <x:f>IF(B50&lt;&gt;"complete","",IF(OR(W50="",X50="",Y50="",Z50="",AA50="",AB50="",AD50="",AF50="",AG50=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="70" customHeight="1">
@@ -5192,8 +5761,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="40" t="str">
-        <x:f>IF('Independent Review'!B49="","",'Independent Review'!B49)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C51" s="40" t="str">
         <x:v>NEWS-guardian_api-e9ed22adbdb1</x:v>
@@ -5254,28 +5822,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W51" s="41" t="str">
-        <x:f>IF('Independent Review'!M49="","",'Independent Review'!M49)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X51" s="41" t="str">
-        <x:f>IF('Independent Review'!N49="","",'Independent Review'!N49)</x:f>
-      </x:c>
-      <x:c r="Y51" s="41" t="str"/>
-      <x:c r="Z51" s="41" t="str"/>
-      <x:c r="AA51" s="41" t="str"/>
-      <x:c r="AB51" s="41" t="str"/>
-      <x:c r="AC51" s="41" t="str"/>
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="Y51" s="41" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z51" s="41" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="AA51" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB51" s="41" t="str">
+        <x:v>few_shot_example</x:v>
+      </x:c>
+      <x:c r="AC51" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD51" s="49" t="str">
-        <x:f>IF('Independent Review'!O49="","",'Independent Review'!O49)</x:f>
-      </x:c>
-      <x:c r="AE51" s="49" t="str"/>
+        <x:v>“Did 2025 mark the end of British parliamentary democracy as we know it?” asks the headline on Andy Beckett’s article (25 December).</x:v>
+      </x:c>
+      <x:c r="AE51" s="49" t="str">
+        <x:v>The letters discuss national democracy, Labour and proportional representation. Farnham appears only in a writer's address and does not create substantive L1 relevance.</x:v>
+      </x:c>
       <x:c r="AF51" s="41" t="str">
-        <x:f>IF('Independent Review'!Q49="","",'Independent Review'!Q49)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG51" s="41" t="str">
-        <x:f>IF('Independent Review'!R49="","",'Independent Review'!R49)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH51" s="42" t="str">
         <x:f>IF(B51&lt;&gt;"complete","",IF(OR(W51="",X51="",Y51="",Z51="",AA51="",AB51="",AD51="",AF51="",AG51=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="70" customHeight="1">
@@ -5283,8 +5864,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="40" t="str">
-        <x:f>IF('Independent Review'!B50="","",'Independent Review'!B50)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C52" s="40" t="str">
         <x:v>NEWS-guardian_api-f0e1fbfa261a</x:v>
@@ -5343,28 +5923,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W52" s="41" t="str">
-        <x:f>IF('Independent Review'!M50="","",'Independent Review'!M50)</x:f>
+        <x:v>include</x:v>
       </x:c>
       <x:c r="X52" s="41" t="str">
-        <x:f>IF('Independent Review'!N50="","",'Independent Review'!N50)</x:f>
-      </x:c>
-      <x:c r="Y52" s="41" t="str"/>
-      <x:c r="Z52" s="41" t="str"/>
-      <x:c r="AA52" s="41" t="str"/>
-      <x:c r="AB52" s="41" t="str"/>
-      <x:c r="AC52" s="41" t="str"/>
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="Y52" s="41" t="str">
+        <x:v>evidence_beyond_excerpt</x:v>
+      </x:c>
+      <x:c r="Z52" s="41" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="AA52" s="41" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="AB52" s="41" t="str">
+        <x:v>input_fix</x:v>
+      </x:c>
+      <x:c r="AC52" s="41" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD52" s="49" t="str">
-        <x:f>IF('Independent Review'!O50="","",'Independent Review'!O50)</x:f>
-      </x:c>
-      <x:c r="AE52" s="49" t="str"/>
+        <x:v>Jessica Fuhl writes Assurances have been given that Epsom Hospital will not close under an NHS review covering Surrey and south west London, Epsom council has said.</x:v>
+      </x:c>
+      <x:c r="AE52" s="49" t="str">
+        <x:v>The healthcare live blog contains a substantive item about Epsom Hospital and an NHS review covering Surrey. The correct local basis is L1 place linkage; the NHS review is not itself a Surrey council decision under L3.</x:v>
+      </x:c>
       <x:c r="AF52" s="41" t="str">
-        <x:f>IF('Independent Review'!Q50="","",'Independent Review'!Q50)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG52" s="41" t="str">
-        <x:f>IF('Independent Review'!R50="","",'Independent Review'!R50)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH52" s="42" t="str">
         <x:f>IF(B52&lt;&gt;"complete","",IF(OR(W52="",X52="",Y52="",Z52="",AA52="",AB52="",AD52="",AF52="",AG52=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="70" customHeight="1">
@@ -5372,8 +5965,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B53" s="44" t="str">
-        <x:f>IF('Independent Review'!B51="","",'Independent Review'!B51)</x:f>
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C53" s="44" t="str">
         <x:v>NEWS-guardian_api-ffae95f17052</x:v>
@@ -5434,28 +6026,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="W53" s="45" t="str">
-        <x:f>IF('Independent Review'!M51="","",'Independent Review'!M51)</x:f>
+        <x:v>exclude</x:v>
       </x:c>
       <x:c r="X53" s="45" t="str">
-        <x:f>IF('Independent Review'!N51="","",'Independent Review'!N51)</x:f>
-      </x:c>
-      <x:c r="Y53" s="45" t="str"/>
-      <x:c r="Z53" s="45" t="str"/>
-      <x:c r="AA53" s="45" t="str"/>
-      <x:c r="AB53" s="45" t="str"/>
-      <x:c r="AC53" s="45" t="str"/>
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="Y53" s="45" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="Z53" s="45" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="AA53" s="45" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="AB53" s="45" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="AC53" s="45" t="str">
+        <x:v>no</x:v>
+      </x:c>
       <x:c r="AD53" s="50" t="str">
-        <x:f>IF('Independent Review'!O51="","",'Independent Review'!O51)</x:f>
-      </x:c>
-      <x:c r="AE53" s="50" t="str"/>
+        <x:v>In the week that many families went to the coast for the fresh sea air or the tang of fish and chips, visitors to one Lancashire resort inhaled a rather more unpleasant aroma.</x:v>
+      </x:c>
+      <x:c r="AE53" s="50" t="str">
+        <x:v>The landfill story concerns Fleetwood in Lancashire and the Environment Agency. It has no Surrey council or sampled-area linkage.</x:v>
+      </x:c>
       <x:c r="AF53" s="45" t="str">
-        <x:f>IF('Independent Review'!Q51="","",'Independent Review'!Q51)</x:f>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="AG53" s="45" t="str">
-        <x:f>IF('Independent Review'!R51="","",'Independent Review'!R51)</x:f>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="AH53" s="46" t="str">
         <x:f>IF(B53&lt;&gt;"complete","",IF(OR(W53="",X53="",Y53="",Z53="",AA53="",AB53="",AD53="",AF53="",AG53=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6947,11 +7552,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -6997,7 +7603,7 @@
       </x:c>
       <x:c r="B5" s="56" t="n">
         <x:f>COUNTIF('Review'!$B$6:$B$53,"complete")</x:f>
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D5" s="59"/>
       <x:c r="E5" s="59"/>
@@ -7009,7 +7615,7 @@
       </x:c>
       <x:c r="B6" s="56" t="n">
         <x:f>COUNTIF('Review'!$B$6:$B$53,"needs_adjudication")</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="59"/>
       <x:c r="E6" s="59"/>
@@ -7072,7 +7678,7 @@
       </x:c>
       <x:c r="B12" s="56" t="n">
         <x:f>COUNTIF('Review'!$AA$6:$AA$53,"yes")</x:f>
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7081,6 +7687,168 @@
       </x:c>
       <x:c r="B13" s="57" t="n">
         <x:f>COUNTIF('Review'!$AC$6:$AC$53,"yes")</x:f>
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="128" t="str">
+        <x:v>Draft reassessment</x:v>
+      </x:c>
+      <x:c r="B15" s="128" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="D15" s="128" t="str">
+        <x:v>Primary mechanism</x:v>
+      </x:c>
+      <x:c r="E15" s="128" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="G15" s="128" t="str">
+        <x:v>Recommended action</x:v>
+      </x:c>
+      <x:c r="H15" s="128" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="129" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="B16" s="130" t="n">
+        <x:f>COUNTIF('Review'!$W$6:$W$53,A16)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D16" s="129" t="str">
+        <x:v>missed_qualifying_evidence</x:v>
+      </x:c>
+      <x:c r="E16" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D16)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G16" s="129" t="str">
+        <x:v>prompt_clarification</x:v>
+      </x:c>
+      <x:c r="H16" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G16)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="129" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="B17" s="130" t="n">
+        <x:f>COUNTIF('Review'!$W$6:$W$53,A17)</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D17" s="129" t="str">
+        <x:v>wrong_arm_rule</x:v>
+      </x:c>
+      <x:c r="E17" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D17)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G17" s="129" t="str">
+        <x:v>decision_tree_change</x:v>
+      </x:c>
+      <x:c r="H17" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G17)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="129" t="str">
+        <x:v>needs_second_review</x:v>
+      </x:c>
+      <x:c r="B18" s="130" t="n">
+        <x:f>COUNTIF('Review'!$W$6:$W$53,A18)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="129" t="str">
+        <x:v>local_effect_not_established</x:v>
+      </x:c>
+      <x:c r="E18" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D18)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G18" s="129" t="str">
+        <x:v>few_shot_example</x:v>
+      </x:c>
+      <x:c r="H18" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G18)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="D19" s="129" t="str">
+        <x:v>incidental_place_overread</x:v>
+      </x:c>
+      <x:c r="E19" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D19)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G19" s="129" t="str">
+        <x:v>human_label_adjudication</x:v>
+      </x:c>
+      <x:c r="H19" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G19)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="D20" s="129" t="str">
+        <x:v>codebook_boundary_unclear</x:v>
+      </x:c>
+      <x:c r="E20" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D20)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="129" t="str">
+        <x:v>input_fix</x:v>
+      </x:c>
+      <x:c r="H20" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G20)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="D21" s="129" t="str">
+        <x:v>national_policy_scope_too_broad</x:v>
+      </x:c>
+      <x:c r="E21" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D21)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" s="129" t="str">
+        <x:v>codebook_review</x:v>
+      </x:c>
+      <x:c r="H21" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G21)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="D22" s="129" t="str">
+        <x:v>surrey_wide_rule_misapplied</x:v>
+      </x:c>
+      <x:c r="E22" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D22)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="129" t="str">
+        <x:v>multiple</x:v>
+      </x:c>
+      <x:c r="H22" s="130" t="n">
+        <x:f>COUNTIF('Review'!$AB$6:$AB$53,G22)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="D23" s="129" t="str">
+        <x:v>entity_or_namesake_confusion</x:v>
+      </x:c>
+      <x:c r="E23" s="130" t="n">
+        <x:f>COUNTIF('Review'!$Z$6:$Z$53,D23)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -7477,10 +8245,10 @@
         <x:v>The first year student at the University of Surrey died while returning from a sports trip to Italy.</x:v>
       </x:c>
       <x:c r="P4" s="90" t="str">
-        <x:v>The University of Surrey is central to the article, but the record has no sampled ward/division or originating query text. L1 therefore cannot yet be confirmed. The article does not meet L2, L3 or L4.</x:v>
+        <x:v>The university is substantively central to the article, but the record does not establish that its campus falls within one of the 17 sampled divisions. Confirm the sampled-area linkage before treating the Surrey name as sufficient L1 evidence.</x:v>
       </x:c>
       <x:c r="Q4" s="82" t="str">
-        <x:v>Codex-assisted development draft (not human blind review)</x:v>
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
       </x:c>
       <x:c r="R4" s="82" t="str">
         <x:v>2026-07-24</x:v>
@@ -7494,7 +8262,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C5" s="81" t="str">
         <x:v>NEWS-guardian_api-07bc83a03221</x:v>
@@ -7524,14 +8292,27 @@
       <x:c r="L5" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M5" s="82" t="str"/>
-      <x:c r="N5" s="82" t="str"/>
-      <x:c r="O5" s="90" t="str"/>
-      <x:c r="P5" s="90" t="str"/>
-      <x:c r="Q5" s="82" t="str"/>
-      <x:c r="R5" s="82" t="str"/>
+      <x:c r="M5" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N5" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O5" s="90" t="str">
+        <x:v>Keir Starmer has faced down immediate calls for his resignation after receiving the full backing of his cabinet and delivering an impassioned appeal to the PLP this evening that appears to have steadied the government’s ship, at least for now.</x:v>
+      </x:c>
+      <x:c r="P5" s="90" t="str">
+        <x:v>The article is UK national leadership coverage and would satisfy N1 in the national arm, but this record is fixed to the local arm and supplies no Surrey L1-L4 link.</x:v>
+      </x:c>
+      <x:c r="Q5" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R5" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S5" s="83" t="str">
         <x:f>IF(B5&lt;&gt;"complete","",IF(OR(M5="",N5="",O5="",Q5="",R5=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
@@ -7539,7 +8320,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C6" s="81" t="str">
         <x:v>NEWS-guardian_api-0a2b7642ed1f</x:v>
@@ -7569,14 +8350,27 @@
       <x:c r="L6" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M6" s="82" t="str"/>
-      <x:c r="N6" s="82" t="str"/>
-      <x:c r="O6" s="90" t="str"/>
-      <x:c r="P6" s="90" t="str"/>
-      <x:c r="Q6" s="82" t="str"/>
-      <x:c r="R6" s="82" t="str"/>
+      <x:c r="M6" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N6" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O6" s="90" t="str">
+        <x:v>It has been an election buildup dominated by the rise of Reform UK and the Greens, and the contrasting woes of Labour and the Tories.</x:v>
+      </x:c>
+      <x:c r="P6" s="90" t="str">
+        <x:v>The article concerns English local-government party performance nationally. It may satisfy N1 in a national search, but it does not satisfy any local L-rule for this local-arm record.</x:v>
+      </x:c>
+      <x:c r="Q6" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R6" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S6" s="83" t="str">
         <x:f>IF(B6&lt;&gt;"complete","",IF(OR(M6="",N6="",O6="",Q6="",R6=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="70" customHeight="1">
@@ -7584,7 +8378,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C7" s="81" t="str">
         <x:v>NEWS-guardian_api-0a8a98eec2fa</x:v>
@@ -7614,14 +8408,27 @@
       <x:c r="L7" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M7" s="82" t="str"/>
-      <x:c r="N7" s="82" t="str"/>
-      <x:c r="O7" s="90" t="str"/>
-      <x:c r="P7" s="90" t="str"/>
-      <x:c r="Q7" s="82" t="str"/>
-      <x:c r="R7" s="82" t="str"/>
+      <x:c r="M7" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N7" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O7" s="90" t="str">
+        <x:v>Almost 90% of English councils overspent on their budgets for teaching children with special needs last year, and the underfunding is set to continue into 2021, according to figures seen by the Observer.</x:v>
+      </x:c>
+      <x:c r="P7" s="90" t="str">
+        <x:v>The article concerns SEND funding across English councils. A Surrey council quotation is one example in a national comparison and does not establish an effect on a sampled Surrey division.</x:v>
+      </x:c>
+      <x:c r="Q7" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R7" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S7" s="83" t="str">
         <x:f>IF(B7&lt;&gt;"complete","",IF(OR(M7="",N7="",O7="",Q7="",R7=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="70" customHeight="1">
@@ -7629,7 +8436,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C8" s="81" t="str">
         <x:v>NEWS-guardian_api-0e7b3e16141a</x:v>
@@ -7659,14 +8466,27 @@
       <x:c r="L8" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M8" s="82" t="str"/>
-      <x:c r="N8" s="82" t="str"/>
-      <x:c r="O8" s="90" t="str"/>
-      <x:c r="P8" s="90" t="str"/>
-      <x:c r="Q8" s="82" t="str"/>
-      <x:c r="R8" s="82" t="str"/>
+      <x:c r="M8" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N8" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O8" s="90" t="str">
+        <x:v>Ministers have dropped plans to delay 30 local elections this May after receiving legal advice that doing so might be unlawful.</x:v>
+      </x:c>
+      <x:c r="P8" s="90" t="str">
+        <x:v>The live blog concerns national decisions about English local elections. It contains no sampled Surrey place or Surrey-specific council effect, so a general local-government story cannot satisfy local L3.</x:v>
+      </x:c>
+      <x:c r="Q8" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R8" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S8" s="83" t="str">
         <x:f>IF(B8&lt;&gt;"complete","",IF(OR(M8="",N8="",O8="",Q8="",R8=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
@@ -7674,7 +8494,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C9" s="81" t="str">
         <x:v>NEWS-guardian_api-0f4380a6f846</x:v>
@@ -7704,14 +8524,27 @@
       <x:c r="L9" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M9" s="82" t="str"/>
-      <x:c r="N9" s="82" t="str"/>
-      <x:c r="O9" s="90" t="str"/>
-      <x:c r="P9" s="90" t="str"/>
-      <x:c r="Q9" s="82" t="str"/>
-      <x:c r="R9" s="82" t="str"/>
+      <x:c r="M9" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N9" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O9" s="90" t="str">
+        <x:v>Nigel Farage must know but doesn’t seem to care that history is written by the winners (Nigel Farage quits as Reform UK leader in step back from party politics, 8 March) as he worries about what our children might learn today.</x:v>
+      </x:c>
+      <x:c r="P9" s="90" t="str">
+        <x:v>The letter directly discusses Nigel Farage, Reform UK leadership and party politics. That is sufficient national-party evidence under N1 even though most of the letter discusses historical education.</x:v>
+      </x:c>
+      <x:c r="Q9" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R9" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S9" s="83" t="str">
         <x:f>IF(B9&lt;&gt;"complete","",IF(OR(M9="",N9="",O9="",Q9="",R9=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -7719,7 +8552,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C10" s="81" t="str">
         <x:v>NEWS-guardian_api-1593f58b94d2</x:v>
@@ -7749,14 +8582,27 @@
       <x:c r="L10" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M10" s="82" t="str"/>
-      <x:c r="N10" s="82" t="str"/>
-      <x:c r="O10" s="90" t="str"/>
-      <x:c r="P10" s="90" t="str"/>
-      <x:c r="Q10" s="82" t="str"/>
-      <x:c r="R10" s="82" t="str"/>
+      <x:c r="M10" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N10" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O10" s="90" t="str">
+        <x:v>The sports foundation at the heart of the Millwall FC compulsory purchase battle has been making false claims of having a £2m funding agreement from Sport England during the ongoing CPO process, the Guardian can reveal.</x:v>
+      </x:c>
+      <x:c r="P10" s="90" t="str">
+        <x:v>The story is about Millwall, Lewisham council and a company called Surrey Canal Sports Foundation. Surrey Canal is a name connected to south London, not evidence of a Surrey council issue or sampled Surrey place.</x:v>
+      </x:c>
+      <x:c r="Q10" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R10" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S10" s="83" t="str">
         <x:f>IF(B10&lt;&gt;"complete","",IF(OR(M10="",N10="",O10="",Q10="",R10=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70" customHeight="1">
@@ -7764,7 +8610,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C11" s="81" t="str">
         <x:v>NEWS-guardian_api-165b44f90fe0</x:v>
@@ -7794,14 +8640,27 @@
       <x:c r="L11" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M11" s="82" t="str"/>
-      <x:c r="N11" s="82" t="str"/>
-      <x:c r="O11" s="90" t="str"/>
-      <x:c r="P11" s="90" t="str"/>
-      <x:c r="Q11" s="82" t="str"/>
-      <x:c r="R11" s="82" t="str"/>
+      <x:c r="M11" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N11" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O11" s="90" t="str">
+        <x:v>The business of the shortest parliament since 1974 is nearly done.</x:v>
+      </x:c>
+      <x:c r="P11" s="90" t="str">
+        <x:v>The editorial is about the UK general election and Brexit. Its retrospective Surrey council example is a passing illustration and is not Surrey-wide political coverage for the sampled local arm.</x:v>
+      </x:c>
+      <x:c r="Q11" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R11" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S11" s="83" t="str">
         <x:f>IF(B11&lt;&gt;"complete","",IF(OR(M11="",N11="",O11="",Q11="",R11=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="70" customHeight="1">
@@ -7809,7 +8668,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C12" s="81" t="str">
         <x:v>NEWS-guardian_api-1d67c0c9dc56</x:v>
@@ -7839,14 +8698,27 @@
       <x:c r="L12" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M12" s="82" t="str"/>
-      <x:c r="N12" s="82" t="str"/>
-      <x:c r="O12" s="90" t="str"/>
-      <x:c r="P12" s="90" t="str"/>
-      <x:c r="Q12" s="82" t="str"/>
-      <x:c r="R12" s="82" t="str"/>
+      <x:c r="M12" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N12" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O12" s="90" t="str">
+        <x:v>When Gary Collins arrived at work in Stoke Newington police station, east London, in January last year he was told a teenage boy had been stabbed to death.</x:v>
+      </x:c>
+      <x:c r="P12" s="90" t="str">
+        <x:v>The article substantively examines a Metropolitan Police identification service and its use in criminal investigations. Policing is a national public-service issue within the N2 public-services category.</x:v>
+      </x:c>
+      <x:c r="Q12" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R12" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S12" s="83" t="str">
         <x:f>IF(B12&lt;&gt;"complete","",IF(OR(M12="",N12="",O12="",Q12="",R12=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="70" customHeight="1">
@@ -7854,7 +8726,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C13" s="81" t="str">
         <x:v>NEWS-guardian_api-26998343d44f</x:v>
@@ -7884,14 +8756,27 @@
       <x:c r="L13" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M13" s="82" t="str"/>
-      <x:c r="N13" s="82" t="str"/>
-      <x:c r="O13" s="90" t="str"/>
-      <x:c r="P13" s="90" t="str"/>
-      <x:c r="Q13" s="82" t="str"/>
-      <x:c r="R13" s="82" t="str"/>
+      <x:c r="M13" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N13" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O13" s="90" t="str">
+        <x:v>Today, the Observer New Review publishes a vivid account of Robert Reich's new documentary Inequality for All.</x:v>
+      </x:c>
+      <x:c r="P13" s="90" t="str">
+        <x:v>The article explicitly concerns stagnant wages, rising living costs and economic inequality. These are substantive cost-of-living issues under N2.</x:v>
+      </x:c>
+      <x:c r="Q13" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R13" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S13" s="83" t="str">
         <x:f>IF(B13&lt;&gt;"complete","",IF(OR(M13="",N13="",O13="",Q13="",R13=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="70" customHeight="1">
@@ -7899,7 +8784,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C14" s="81" t="str">
         <x:v>NEWS-guardian_api-299f68788499</x:v>
@@ -7929,14 +8814,27 @@
       <x:c r="L14" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M14" s="82" t="str"/>
-      <x:c r="N14" s="82" t="str"/>
-      <x:c r="O14" s="90" t="str"/>
-      <x:c r="P14" s="90" t="str"/>
-      <x:c r="Q14" s="82" t="str"/>
-      <x:c r="R14" s="82" t="str"/>
+      <x:c r="M14" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N14" s="82" t="str">
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="O14" s="90" t="str">
+        <x:v>In the south of England East Surrey hospital in Redhill stopped visits to 10 of its wards on Tuesday, a decision which had not been taken lightly, Surrey and Sussex Healthcare NHS trust said.</x:v>
+      </x:c>
+      <x:c r="P14" s="90" t="str">
+        <x:v>The article gives a substantive local example at East Surrey Hospital in Redhill. The correct basis is L1 place linkage; the NHS trust decision is not a Surrey council decision and should not be coded as L3.</x:v>
+      </x:c>
+      <x:c r="Q14" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R14" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S14" s="83" t="str">
         <x:f>IF(B14&lt;&gt;"complete","",IF(OR(M14="",N14="",O14="",Q14="",R14=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="70" customHeight="1">
@@ -7944,7 +8842,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C15" s="81" t="str">
         <x:v>NEWS-guardian_api-34e77f9bede6</x:v>
@@ -7974,14 +8872,27 @@
       <x:c r="L15" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M15" s="82" t="str"/>
-      <x:c r="N15" s="82" t="str"/>
-      <x:c r="O15" s="90" t="str"/>
-      <x:c r="P15" s="90" t="str"/>
-      <x:c r="Q15" s="82" t="str"/>
-      <x:c r="R15" s="82" t="str"/>
+      <x:c r="M15" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N15" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O15" s="90" t="str">
+        <x:v>Having campaigned against devolution in Wales, in 1999 he was elected to the Welsh Assembly on a platform of opposition to any further devolution, and won Monmouth for the Conservatives in 2005.</x:v>
+      </x:c>
+      <x:c r="P15" s="90" t="str">
+        <x:v>The full article is a political profile of a Conservative MP and discusses his electoral and parliamentary positions. The decisive N1 material was outside the short v1 excerpt.</x:v>
+      </x:c>
+      <x:c r="Q15" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R15" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S15" s="83" t="str">
         <x:f>IF(B15&lt;&gt;"complete","",IF(OR(M15="",N15="",O15="",Q15="",R15=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="70" customHeight="1">
@@ -7989,7 +8900,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C16" s="81" t="str">
         <x:v>NEWS-guardian_api-3a9be3f68624</x:v>
@@ -8019,14 +8930,27 @@
       <x:c r="L16" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M16" s="82" t="str"/>
-      <x:c r="N16" s="82" t="str"/>
-      <x:c r="O16" s="90" t="str"/>
-      <x:c r="P16" s="90" t="str"/>
-      <x:c r="Q16" s="82" t="str"/>
-      <x:c r="R16" s="82" t="str"/>
+      <x:c r="M16" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N16" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O16" s="90" t="str">
+        <x:v>In April 2018, a woman told the newspaper how she was struggling to sell the retirement flat her late parents had bought in 1997 and that she had been forced to cut the price from £185,000 to £140,000, well below the £260,000 average for a normal flat in the same Surrey village.</x:v>
+      </x:c>
+      <x:c r="P16" s="90" t="str">
+        <x:v>The article's main case concerns a retirement flat in Solihull. The unnamed Surrey village appears only in a comparison with a different case and does not create substantive sampled-area relevance.</x:v>
+      </x:c>
+      <x:c r="Q16" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R16" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S16" s="83" t="str">
         <x:f>IF(B16&lt;&gt;"complete","",IF(OR(M16="",N16="",O16="",Q16="",R16=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="70" customHeight="1">
@@ -8034,7 +8958,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C17" s="81" t="str">
         <x:v>NEWS-guardian_api-4b66c98ae734</x:v>
@@ -8064,14 +8988,27 @@
       <x:c r="L17" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M17" s="82" t="str"/>
-      <x:c r="N17" s="82" t="str"/>
-      <x:c r="O17" s="90" t="str"/>
-      <x:c r="P17" s="90" t="str"/>
-      <x:c r="Q17" s="82" t="str"/>
-      <x:c r="R17" s="82" t="str"/>
+      <x:c r="M17" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N17" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O17" s="90" t="str">
+        <x:v>The shop windows are decked out in their festive finery, there are carols on the stereos and the tills are ringing.</x:v>
+      </x:c>
+      <x:c r="P17" s="90" t="str">
+        <x:v>The article concerns parking charges in Clevedon imposed by North Somerset council. A non-Surrey council issue cannot satisfy local L3.</x:v>
+      </x:c>
+      <x:c r="Q17" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R17" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S17" s="83" t="str">
         <x:f>IF(B17&lt;&gt;"complete","",IF(OR(M17="",N17="",O17="",Q17="",R17=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="70" customHeight="1">
@@ -8079,7 +9016,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C18" s="81" t="str">
         <x:v>NEWS-guardian_api-4f0bd20943f7</x:v>
@@ -8109,14 +9046,27 @@
       <x:c r="L18" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M18" s="82" t="str"/>
-      <x:c r="N18" s="82" t="str"/>
-      <x:c r="O18" s="90" t="str"/>
-      <x:c r="P18" s="90" t="str"/>
-      <x:c r="Q18" s="82" t="str"/>
-      <x:c r="R18" s="82" t="str"/>
+      <x:c r="M18" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N18" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O18" s="90" t="str">
+        <x:v>A revolt against urban liberalism and multiculturalism, and their supposed imposition on the rest of the population, was a big element of the Brexit and Donald Trump campaigns.</x:v>
+      </x:c>
+      <x:c r="P18" s="90" t="str">
+        <x:v>The analysis concerns Brexit, Donald Trump and the political division between urban and rural voters. It is substantive national political coverage under N1.</x:v>
+      </x:c>
+      <x:c r="Q18" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R18" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S18" s="83" t="str">
         <x:f>IF(B18&lt;&gt;"complete","",IF(OR(M18="",N18="",O18="",Q18="",R18=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="70" customHeight="1">
@@ -8124,7 +9074,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>needs_adjudication</x:v>
       </x:c>
       <x:c r="C19" s="81" t="str">
         <x:v>NEWS-guardian_api-4fc41ad01b24</x:v>
@@ -8154,12 +9104,24 @@
       <x:c r="L19" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M19" s="82" t="str"/>
-      <x:c r="N19" s="82" t="str"/>
-      <x:c r="O19" s="90" t="str"/>
-      <x:c r="P19" s="90" t="str"/>
-      <x:c r="Q19" s="82" t="str"/>
-      <x:c r="R19" s="82" t="str"/>
+      <x:c r="M19" s="82" t="str">
+        <x:v>needs_second_review</x:v>
+      </x:c>
+      <x:c r="N19" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O19" s="90" t="str">
+        <x:v>Liz Neil is account co-ordinator, programmes and projects at British Council Liz has many years experience working on international education programmes for schools, colleges and universities, including eTwinning and Comenius.</x:v>
+      </x:c>
+      <x:c r="P19" s="90" t="str">
+        <x:v>The article concerns global awareness teaching rather than a clearly defined UK political decision, funding question or public-service performance issue. Adjudication should clarify whether general educational practice falls within N2 public services.</x:v>
+      </x:c>
+      <x:c r="Q19" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R19" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S19" s="83" t="str">
         <x:f>IF(B19&lt;&gt;"complete","",IF(OR(M19="",N19="",O19="",Q19="",R19=""),"MISSING REQUIRED FIELD","OK"))</x:f>
       </x:c>
@@ -8169,7 +9131,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C20" s="81" t="str">
         <x:v>NEWS-guardian_api-5155ba13661a</x:v>
@@ -8199,14 +9161,27 @@
       <x:c r="L20" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M20" s="82" t="str"/>
-      <x:c r="N20" s="82" t="str"/>
-      <x:c r="O20" s="90" t="str"/>
-      <x:c r="P20" s="90" t="str"/>
-      <x:c r="Q20" s="82" t="str"/>
-      <x:c r="R20" s="82" t="str"/>
+      <x:c r="M20" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N20" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O20" s="90" t="str">
+        <x:v>A woman is taking legal action against an NHS trust over the “diabolical” and discriminatory treatment of her profoundly deaf husband, who died of cancer in May last year.</x:v>
+      </x:c>
+      <x:c r="P20" s="90" t="str">
+        <x:v>The article concerns alleged discriminatory treatment by an NHS trust and therefore directly addresses NHS service quality under N2.</x:v>
+      </x:c>
+      <x:c r="Q20" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R20" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S20" s="83" t="str">
         <x:f>IF(B20&lt;&gt;"complete","",IF(OR(M20="",N20="",O20="",Q20="",R20=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="70" customHeight="1">
@@ -8214,7 +9189,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C21" s="81" t="str">
         <x:v>NEWS-guardian_api-568af3a4ccd4</x:v>
@@ -8244,14 +9219,27 @@
       <x:c r="L21" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M21" s="82" t="str"/>
-      <x:c r="N21" s="82" t="str"/>
-      <x:c r="O21" s="90" t="str"/>
-      <x:c r="P21" s="90" t="str"/>
-      <x:c r="Q21" s="82" t="str"/>
-      <x:c r="R21" s="82" t="str"/>
+      <x:c r="M21" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N21" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O21" s="90" t="str">
+        <x:v>Ohio is where the warring halves of America meet.</x:v>
+      </x:c>
+      <x:c r="P21" s="90" t="str">
+        <x:v>The article is about the United States presidential election. N1 is limited to UK national politics, and the L2 candidate code used by the model is invalid for a national-arm record.</x:v>
+      </x:c>
+      <x:c r="Q21" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R21" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S21" s="83" t="str">
         <x:f>IF(B21&lt;&gt;"complete","",IF(OR(M21="",N21="",O21="",Q21="",R21=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="70" customHeight="1">
@@ -8259,7 +9247,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C22" s="81" t="str">
         <x:v>NEWS-guardian_api-649bfee8381e</x:v>
@@ -8289,14 +9277,27 @@
       <x:c r="L22" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M22" s="82" t="str"/>
-      <x:c r="N22" s="82" t="str"/>
-      <x:c r="O22" s="90" t="str"/>
-      <x:c r="P22" s="90" t="str"/>
-      <x:c r="Q22" s="82" t="str"/>
-      <x:c r="R22" s="82" t="str"/>
+      <x:c r="M22" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N22" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O22" s="90" t="str">
+        <x:v>Ministers are to postpone elections for new mayors in four parts of England, prompting accusations from opposition parties that Downing Street is “cancelling democracy”.</x:v>
+      </x:c>
+      <x:c r="P22" s="90" t="str">
+        <x:v>The article concerns mayoral elections in Essex, East Anglia, Hampshire and Sussex. Coverage spanning several English regions is not Surrey-wide political coverage under L4.</x:v>
+      </x:c>
+      <x:c r="Q22" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R22" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S22" s="83" t="str">
         <x:f>IF(B22&lt;&gt;"complete","",IF(OR(M22="",N22="",O22="",Q22="",R22=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="70" customHeight="1">
@@ -8304,7 +9305,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C23" s="81" t="str">
         <x:v>NEWS-guardian_api-64ea38ced8bd</x:v>
@@ -8334,14 +9335,27 @@
       <x:c r="L23" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M23" s="82" t="str"/>
-      <x:c r="N23" s="82" t="str"/>
-      <x:c r="O23" s="90" t="str"/>
-      <x:c r="P23" s="90" t="str"/>
-      <x:c r="Q23" s="82" t="str"/>
-      <x:c r="R23" s="82" t="str"/>
+      <x:c r="M23" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N23" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O23" s="90" t="str">
+        <x:v>The speech was made in the playground of Nonsuch high school for girls in Surrey.</x:v>
+      </x:c>
+      <x:c r="P23" s="90" t="str">
+        <x:v>The article is substantively about Nonsuch High School, but the school is associated with the Nonsuch area rather than any of the 17 sampled divisions in this study. A generic Surrey description is insufficient for sampled-area L1.</x:v>
+      </x:c>
+      <x:c r="Q23" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R23" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S23" s="83" t="str">
         <x:f>IF(B23&lt;&gt;"complete","",IF(OR(M23="",N23="",O23="",Q23="",R23=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="70" customHeight="1">
@@ -8349,7 +9363,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C24" s="81" t="str">
         <x:v>NEWS-guardian_api-6549611cf8a4</x:v>
@@ -8379,14 +9393,27 @@
       <x:c r="L24" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M24" s="82" t="str"/>
-      <x:c r="N24" s="82" t="str"/>
-      <x:c r="O24" s="90" t="str"/>
-      <x:c r="P24" s="90" t="str"/>
-      <x:c r="Q24" s="82" t="str"/>
-      <x:c r="R24" s="82" t="str"/>
+      <x:c r="M24" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N24" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O24" s="90" t="str">
+        <x:v>Ask Barbara Keeley what keeps her awake at night and Labour’s shadow cabinet member for mental health and social care will tell you it’s the stories of people in “heartrending” situations whose care is being cut.</x:v>
+      </x:c>
+      <x:c r="P24" s="90" t="str">
+        <x:v>The article is a national social-care funding interview. It could satisfy N2 in the national arm, but it contains no sampled Surrey L1-L4 link for this local-arm record.</x:v>
+      </x:c>
+      <x:c r="Q24" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R24" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S24" s="83" t="str">
         <x:f>IF(B24&lt;&gt;"complete","",IF(OR(M24="",N24="",O24="",Q24="",R24=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="70" customHeight="1">
@@ -8394,7 +9421,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C25" s="81" t="str">
         <x:v>NEWS-guardian_api-6d0b3b8aedc2</x:v>
@@ -8424,14 +9451,27 @@
       <x:c r="L25" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M25" s="82" t="str"/>
-      <x:c r="N25" s="82" t="str"/>
-      <x:c r="O25" s="90" t="str"/>
-      <x:c r="P25" s="90" t="str"/>
-      <x:c r="Q25" s="82" t="str"/>
-      <x:c r="R25" s="82" t="str"/>
+      <x:c r="M25" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N25" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O25" s="90" t="str">
+        <x:v>Millwall Football Club have admitted for the first time that they may be forced to leave their south London home and relocate to Kent should the seizure of their land go ahead.</x:v>
+      </x:c>
+      <x:c r="P25" s="90" t="str">
+        <x:v>The compulsory-purchase dispute concerns Lewisham council and Millwall in south London. It is not a Surrey council decision and cannot satisfy local L3.</x:v>
+      </x:c>
+      <x:c r="Q25" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R25" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S25" s="83" t="str">
         <x:f>IF(B25&lt;&gt;"complete","",IF(OR(M25="",N25="",O25="",Q25="",R25=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="70" customHeight="1">
@@ -8439,7 +9479,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C26" s="81" t="str">
         <x:v>NEWS-guardian_api-6d2d7efbb858</x:v>
@@ -8469,14 +9509,27 @@
       <x:c r="L26" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M26" s="82" t="str"/>
-      <x:c r="N26" s="82" t="str"/>
-      <x:c r="O26" s="90" t="str"/>
-      <x:c r="P26" s="90" t="str"/>
-      <x:c r="Q26" s="82" t="str"/>
-      <x:c r="R26" s="82" t="str"/>
+      <x:c r="M26" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N26" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O26" s="90" t="str">
+        <x:v>Tory supporters of equal marriage are making an eleventh hour plea to fellow Conservative MPs to vote in favour of reform by invoking the record of Margaret Thatcher, who supported the legalisation of homosexuality in the 1960s.</x:v>
+      </x:c>
+      <x:c r="P26" s="90" t="str">
+        <x:v>The article concerns national parliamentary politics and equal marriage. It could meet N1 in the national arm, but it contains no local Surrey linkage for this local-arm record.</x:v>
+      </x:c>
+      <x:c r="Q26" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R26" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S26" s="83" t="str">
         <x:f>IF(B26&lt;&gt;"complete","",IF(OR(M26="",N26="",O26="",Q26="",R26=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="70" customHeight="1">
@@ -8484,7 +9537,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C27" s="81" t="str">
         <x:v>NEWS-guardian_api-775f95b2aee7</x:v>
@@ -8514,14 +9567,27 @@
       <x:c r="L27" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M27" s="82" t="str"/>
-      <x:c r="N27" s="82" t="str"/>
-      <x:c r="O27" s="90" t="str"/>
-      <x:c r="P27" s="90" t="str"/>
-      <x:c r="Q27" s="82" t="str"/>
-      <x:c r="R27" s="82" t="str"/>
+      <x:c r="M27" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N27" s="82" t="str">
+        <x:v>N3</x:v>
+      </x:c>
+      <x:c r="O27" s="90" t="str">
+        <x:v>Michael says this poses a question for the government: “With Reform UK continuing to rise in the polls, and political attacks on the BBC increasing, will the government decide it needs to defend and protect the corporation’s independence in this increasingly hostile environment?” The risk of Labour leaning into a populist anti-BBC sentiment is unlikely: it would be seismic, he tells me, for the government to scrap the licence fee.</x:v>
+      </x:c>
+      <x:c r="P27" s="90" t="str">
+        <x:v>The full briefing explicitly links Reform UK's rise in the polls to political pressure on the BBC and government choices. This is direct Reform growth evidence under N3.</x:v>
+      </x:c>
+      <x:c r="Q27" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R27" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S27" s="83" t="str">
         <x:f>IF(B27&lt;&gt;"complete","",IF(OR(M27="",N27="",O27="",Q27="",R27=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="70" customHeight="1">
@@ -8529,7 +9595,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C28" s="81" t="str">
         <x:v>NEWS-guardian_api-7cf057334d25</x:v>
@@ -8559,14 +9625,27 @@
       <x:c r="L28" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M28" s="82" t="str"/>
-      <x:c r="N28" s="82" t="str"/>
-      <x:c r="O28" s="90" t="str"/>
-      <x:c r="P28" s="90" t="str"/>
-      <x:c r="Q28" s="82" t="str"/>
-      <x:c r="R28" s="82" t="str"/>
+      <x:c r="M28" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N28" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O28" s="90" t="str">
+        <x:v>When and how will I be able to get a Covid vaccine?</x:v>
+      </x:c>
+      <x:c r="P28" s="90" t="str">
+        <x:v>The article explains the UK government's Covid vaccination programme, priority groups and NHS delivery. It directly satisfies the NHS/public-services branch of N2.</x:v>
+      </x:c>
+      <x:c r="Q28" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R28" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S28" s="83" t="str">
         <x:f>IF(B28&lt;&gt;"complete","",IF(OR(M28="",N28="",O28="",Q28="",R28=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="70" customHeight="1">
@@ -8574,7 +9653,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C29" s="81" t="str">
         <x:v>NEWS-guardian_api-87c983cdc10f</x:v>
@@ -8604,14 +9683,27 @@
       <x:c r="L29" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M29" s="82" t="str"/>
-      <x:c r="N29" s="82" t="str"/>
-      <x:c r="O29" s="90" t="str"/>
-      <x:c r="P29" s="90" t="str"/>
-      <x:c r="Q29" s="82" t="str"/>
-      <x:c r="R29" s="82" t="str"/>
+      <x:c r="M29" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N29" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O29" s="90" t="str">
+        <x:v>Now somebody else will become Boris Johnson’s best known adviser.</x:v>
+      </x:c>
+      <x:c r="P29" s="90" t="str">
+        <x:v>The article analyses Dominic Cummings's departure and Boris Johnson's Downing Street operation. This is substantive government-performance coverage under N1.</x:v>
+      </x:c>
+      <x:c r="Q29" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R29" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S29" s="83" t="str">
         <x:f>IF(B29&lt;&gt;"complete","",IF(OR(M29="",N29="",O29="",Q29="",R29=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="70" customHeight="1">
@@ -8619,7 +9711,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C30" s="81" t="str">
         <x:v>NEWS-guardian_api-88e751d96451</x:v>
@@ -8649,14 +9741,27 @@
       <x:c r="L30" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M30" s="82" t="str"/>
-      <x:c r="N30" s="82" t="str"/>
-      <x:c r="O30" s="90" t="str"/>
-      <x:c r="P30" s="90" t="str"/>
-      <x:c r="Q30" s="82" t="str"/>
-      <x:c r="R30" s="82" t="str"/>
+      <x:c r="M30" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N30" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O30" s="90" t="str">
+        <x:v>The impact of the Brexit vote on higher education is too early to call.</x:v>
+      </x:c>
+      <x:c r="P30" s="90" t="str">
+        <x:v>The article examines the effect of the Brexit vote on UK universities and European students. Brexit and its domestic political consequences fall within UK national politics under N1.</x:v>
+      </x:c>
+      <x:c r="Q30" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R30" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S30" s="83" t="str">
         <x:f>IF(B30&lt;&gt;"complete","",IF(OR(M30="",N30="",O30="",Q30="",R30=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="70" customHeight="1">
@@ -8664,7 +9769,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C31" s="81" t="str">
         <x:v>NEWS-guardian_api-8a849cd56bab</x:v>
@@ -8694,14 +9799,27 @@
       <x:c r="L31" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M31" s="82" t="str"/>
-      <x:c r="N31" s="82" t="str"/>
-      <x:c r="O31" s="90" t="str"/>
-      <x:c r="P31" s="90" t="str"/>
-      <x:c r="Q31" s="82" t="str"/>
-      <x:c r="R31" s="82" t="str"/>
+      <x:c r="M31" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N31" s="82" t="str">
+        <x:v>N3</x:v>
+      </x:c>
+      <x:c r="O31" s="90" t="str">
+        <x:v>Nigel Farage and his allies have relaunched their political party, encouraging people to walk past their local war memorial on Remembrance Sunday in a low-key anti-lockdown protest that marks a fresh attempt to restore its political relevance.</x:v>
+      </x:c>
+      <x:c r="P31" s="90" t="str">
+        <x:v>The live blog contains a substantive UK entry on Nigel Farage relaunching his party and attempting to restore its political relevance. That entry supplies N3 new-party evidence even though the blog also covers international Covid news.</x:v>
+      </x:c>
+      <x:c r="Q31" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R31" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S31" s="83" t="str">
         <x:f>IF(B31&lt;&gt;"complete","",IF(OR(M31="",N31="",O31="",Q31="",R31=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="70" customHeight="1">
@@ -8709,7 +9827,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C32" s="81" t="str">
         <x:v>NEWS-guardian_api-8c28af0f119c</x:v>
@@ -8739,14 +9857,27 @@
       <x:c r="L32" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M32" s="82" t="str"/>
-      <x:c r="N32" s="82" t="str"/>
-      <x:c r="O32" s="90" t="str"/>
-      <x:c r="P32" s="90" t="str"/>
-      <x:c r="Q32" s="82" t="str"/>
-      <x:c r="R32" s="82" t="str"/>
+      <x:c r="M32" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N32" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O32" s="90" t="str">
+        <x:v>Kemi Badenoch has been accused of weaponising violence against women and girls and using “dangerous” and “deeply inaccurate” claims in her response to the government’s plan to tackle the issue.</x:v>
+      </x:c>
+      <x:c r="P32" s="90" t="str">
+        <x:v>The live blog is UK national party and government coverage. It contains no substantive sampled Surrey linkage and therefore fails the local-arm L1-L4 test.</x:v>
+      </x:c>
+      <x:c r="Q32" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R32" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S32" s="83" t="str">
         <x:f>IF(B32&lt;&gt;"complete","",IF(OR(M32="",N32="",O32="",Q32="",R32=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="70" customHeight="1">
@@ -8754,7 +9885,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C33" s="81" t="str">
         <x:v>NEWS-guardian_api-8e547ee6efe6</x:v>
@@ -8784,14 +9915,27 @@
       <x:c r="L33" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M33" s="82" t="str"/>
-      <x:c r="N33" s="82" t="str"/>
-      <x:c r="O33" s="90" t="str"/>
-      <x:c r="P33" s="90" t="str"/>
-      <x:c r="Q33" s="82" t="str"/>
-      <x:c r="R33" s="82" t="str"/>
+      <x:c r="M33" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N33" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O33" s="90" t="str">
+        <x:v>Nigel Farage has unveiled the first part of Reform UK’s frontbench team, saying it shows that the party is no longer reliant entirely on him – while also warning that he will not tolerate any dissent from his colleagues.</x:v>
+      </x:c>
+      <x:c r="P33" s="90" t="str">
+        <x:v>The live blog contains strong national Reform UK coverage, but the record is local-arm. A historical passing reference to an unnamed Surrey councillor does not satisfy L1-L4.</x:v>
+      </x:c>
+      <x:c r="Q33" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R33" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S33" s="83" t="str">
         <x:f>IF(B33&lt;&gt;"complete","",IF(OR(M33="",N33="",O33="",Q33="",R33=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="70" customHeight="1">
@@ -8799,7 +9943,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C34" s="81" t="str">
         <x:v>NEWS-guardian_api-8f21ed1fa60a</x:v>
@@ -8827,14 +9971,27 @@
       <x:c r="L34" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M34" s="82" t="str"/>
-      <x:c r="N34" s="82" t="str"/>
-      <x:c r="O34" s="90" t="str"/>
-      <x:c r="P34" s="90" t="str"/>
-      <x:c r="Q34" s="82" t="str"/>
-      <x:c r="R34" s="82" t="str"/>
+      <x:c r="M34" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N34" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O34" s="90" t="str">
+        <x:v>BBC’s Newsnight’s take on the reported acrimony between Boris Johnson and his advisers.</x:v>
+      </x:c>
+      <x:c r="P34" s="90" t="str">
+        <x:v>The live blog directly covers senior Downing Street advisers, Boris Johnson and the operation of government. This is N1 government-performance coverage.</x:v>
+      </x:c>
+      <x:c r="Q34" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R34" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S34" s="83" t="str">
         <x:f>IF(B34&lt;&gt;"complete","",IF(OR(M34="",N34="",O34="",Q34="",R34=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="70" customHeight="1">
@@ -8842,7 +9999,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C35" s="81" t="str">
         <x:v>NEWS-guardian_api-8f8e97810c4d</x:v>
@@ -8872,14 +10029,27 @@
       <x:c r="L35" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M35" s="82" t="str"/>
-      <x:c r="N35" s="82" t="str"/>
-      <x:c r="O35" s="90" t="str"/>
-      <x:c r="P35" s="90" t="str"/>
-      <x:c r="Q35" s="82" t="str"/>
-      <x:c r="R35" s="82" t="str"/>
+      <x:c r="M35" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N35" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O35" s="90" t="str">
+        <x:v>Traditional Boxing Day hunts across large parts of the UK have been cancelled due to coronavirus restrictions, with those going ahead elsewhere not parading through town centres prior to their yuletide meet this year for the first time in recent history.</x:v>
+      </x:c>
+      <x:c r="P35" s="90" t="str">
+        <x:v>The article concerns hunting restrictions across Britain and a Peterborough council decision. It does not concern a Surrey council issue affecting a sampled area.</x:v>
+      </x:c>
+      <x:c r="Q35" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R35" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S35" s="83" t="str">
         <x:f>IF(B35&lt;&gt;"complete","",IF(OR(M35="",N35="",O35="",Q35="",R35=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="70" customHeight="1">
@@ -8887,7 +10057,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C36" s="81" t="str">
         <x:v>NEWS-guardian_api-95d73413bd9b</x:v>
@@ -8917,14 +10087,27 @@
       <x:c r="L36" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M36" s="82" t="str"/>
-      <x:c r="N36" s="82" t="str"/>
-      <x:c r="O36" s="90" t="str"/>
-      <x:c r="P36" s="90" t="str"/>
-      <x:c r="Q36" s="82" t="str"/>
-      <x:c r="R36" s="82" t="str"/>
+      <x:c r="M36" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N36" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O36" s="90" t="str">
+        <x:v>Nigel Farage has redoubled his efforts to become irritant-in-chief to British ministers in the wake of Donald Trump’s election by suggesting their earlier criticisms of the president-elect could have meant he delayed speaking to Theresa May.</x:v>
+      </x:c>
+      <x:c r="P36" s="90" t="str">
+        <x:v>The article concerns Nigel Farage, Theresa May, Boris Johnson and UK relations with the incoming US administration. It clearly meets N1, but it is not primarily evidence of UKIP/Reform growth under N3.</x:v>
+      </x:c>
+      <x:c r="Q36" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R36" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S36" s="83" t="str">
         <x:f>IF(B36&lt;&gt;"complete","",IF(OR(M36="",N36="",O36="",Q36="",R36=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="70" customHeight="1">
@@ -8932,7 +10115,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C37" s="81" t="str">
         <x:v>NEWS-guardian_api-97b3a5489c02</x:v>
@@ -8962,14 +10145,27 @@
       <x:c r="L37" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M37" s="82" t="str"/>
-      <x:c r="N37" s="82" t="str"/>
-      <x:c r="O37" s="90" t="str"/>
-      <x:c r="P37" s="90" t="str"/>
-      <x:c r="Q37" s="82" t="str"/>
-      <x:c r="R37" s="82" t="str"/>
+      <x:c r="M37" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N37" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O37" s="90" t="str">
+        <x:v>(See 4.59pm.) Labour has written to Boris Johnson asking him to correct the record after Downing Street repeatedly refused to acknowledge that the prime minister was mistaken when he said the party had voted against an NHS pay deal.</x:v>
+      </x:c>
+      <x:c r="P37" s="90" t="str">
+        <x:v>The live blog substantively discusses UK Covid testing, vaccination policy and an NHS pay dispute. These are NHS/public-service issues under N2.</x:v>
+      </x:c>
+      <x:c r="Q37" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R37" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S37" s="83" t="str">
         <x:f>IF(B37&lt;&gt;"complete","",IF(OR(M37="",N37="",O37="",Q37="",R37=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="70" customHeight="1">
@@ -8977,7 +10173,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C38" s="81" t="str">
         <x:v>NEWS-guardian_api-9dea17fa1487</x:v>
@@ -9005,14 +10201,27 @@
       <x:c r="L38" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M38" s="82" t="str"/>
-      <x:c r="N38" s="82" t="str"/>
-      <x:c r="O38" s="90" t="str"/>
-      <x:c r="P38" s="90" t="str"/>
-      <x:c r="Q38" s="82" t="str"/>
-      <x:c r="R38" s="82" t="str"/>
+      <x:c r="M38" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N38" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O38" s="90" t="str">
+        <x:v>Liverpool city region, York, North Yorkshire, Cambridgeshire, Norfolk, Essex, East Sussex, Surrey, Oxfordshire, Dorset and Devon are among other locations in tier 2.</x:v>
+      </x:c>
+      <x:c r="P38" s="90" t="str">
+        <x:v>The article explains national Covid tier rules and lists Surrey among many tier-2 areas. It does not name a sampled division or town, concern a Surrey council decision, or provide Surrey-wide political coverage.</x:v>
+      </x:c>
+      <x:c r="Q38" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R38" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S38" s="83" t="str">
         <x:f>IF(B38&lt;&gt;"complete","",IF(OR(M38="",N38="",O38="",Q38="",R38=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="70" customHeight="1">
@@ -9020,7 +10229,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C39" s="81" t="str">
         <x:v>NEWS-guardian_api-a3577fa415ba</x:v>
@@ -9050,14 +10259,27 @@
       <x:c r="L39" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M39" s="82" t="str"/>
-      <x:c r="N39" s="82" t="str"/>
-      <x:c r="O39" s="90" t="str"/>
-      <x:c r="P39" s="90" t="str"/>
-      <x:c r="Q39" s="82" t="str"/>
-      <x:c r="R39" s="82" t="str"/>
+      <x:c r="M39" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N39" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O39" s="90" t="str">
+        <x:v>We’ve launched a new blog at the link below – head there for the latest: Israel is set to ban passenger flights in attempt to prevent Covid variant imports, coming into effect from Monday 10pm for two weeks Greek health authorities have reported a jump in the number of cases of the coronavirus variant first spotted in the UK, with 32 infections detected.</x:v>
+      </x:c>
+      <x:c r="P39" s="90" t="str">
+        <x:v>The article is principally an international Covid live blog led by Israel and Greece. UK figures and comments appear among many updates, but the article is not substantively focused on a specified UK national policy issue.</x:v>
+      </x:c>
+      <x:c r="Q39" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R39" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S39" s="83" t="str">
         <x:f>IF(B39&lt;&gt;"complete","",IF(OR(M39="",N39="",O39="",Q39="",R39=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="70" customHeight="1">
@@ -9065,7 +10287,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C40" s="81" t="str">
         <x:v>NEWS-guardian_api-ab4a777c619a</x:v>
@@ -9095,14 +10317,27 @@
       <x:c r="L40" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M40" s="82" t="str"/>
-      <x:c r="N40" s="82" t="str"/>
-      <x:c r="O40" s="90" t="str"/>
-      <x:c r="P40" s="90" t="str"/>
-      <x:c r="Q40" s="82" t="str"/>
-      <x:c r="R40" s="82" t="str"/>
+      <x:c r="M40" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N40" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O40" s="90" t="str">
+        <x:v>It is far too easy to impersonate someone at a polling station and claim their vote (Voters in local elections will be required to show ID in anti-fraud trials, 28 December).</x:v>
+      </x:c>
+      <x:c r="P40" s="90" t="str">
+        <x:v>The letters concern national voter identification and electoral registration. They contain no sampled Surrey place or council issue for the local arm.</x:v>
+      </x:c>
+      <x:c r="Q40" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R40" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S40" s="83" t="str">
         <x:f>IF(B40&lt;&gt;"complete","",IF(OR(M40="",N40="",O40="",Q40="",R40=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="70" customHeight="1">
@@ -9110,7 +10345,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C41" s="81" t="str">
         <x:v>NEWS-guardian_api-b48d01a86b76</x:v>
@@ -9140,14 +10375,27 @@
       <x:c r="L41" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M41" s="82" t="str"/>
-      <x:c r="N41" s="82" t="str"/>
-      <x:c r="O41" s="90" t="str"/>
-      <x:c r="P41" s="90" t="str"/>
-      <x:c r="Q41" s="82" t="str"/>
-      <x:c r="R41" s="82" t="str"/>
+      <x:c r="M41" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N41" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O41" s="90" t="str">
+        <x:v>Surrey and Thames Valley police forces are considering claims of sexual wrongdoing by the former prince.</x:v>
+      </x:c>
+      <x:c r="P41" s="90" t="str">
+        <x:v>The article concerns police investigations into Andrew Mountbatten-Windsor. Mention of Surrey Police is not a Surrey council decision or service and no effect on a sampled division is established.</x:v>
+      </x:c>
+      <x:c r="Q41" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R41" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S41" s="83" t="str">
         <x:f>IF(B41&lt;&gt;"complete","",IF(OR(M41="",N41="",O41="",Q41="",R41=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="70" customHeight="1">
@@ -9155,7 +10403,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>needs_adjudication</x:v>
       </x:c>
       <x:c r="C42" s="81" t="str">
         <x:v>NEWS-guardian_api-b9d210492f43</x:v>
@@ -9185,12 +10433,24 @@
       <x:c r="L42" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M42" s="82" t="str"/>
-      <x:c r="N42" s="82" t="str"/>
-      <x:c r="O42" s="90" t="str"/>
-      <x:c r="P42" s="90" t="str"/>
-      <x:c r="Q42" s="82" t="str"/>
-      <x:c r="R42" s="82" t="str"/>
+      <x:c r="M42" s="82" t="str">
+        <x:v>needs_second_review</x:v>
+      </x:c>
+      <x:c r="N42" s="82" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="O42" s="90" t="str">
+        <x:v>Areas moving to tier 4 are Sussex, Oxfordshire, Suffolk, Norfolk and Cambridgeshire, parts of Essex not yet in the highest tier, Waverley in Surrey and Hampshire, with the exception of the New Forest.</x:v>
+      </x:c>
+      <x:c r="P42" s="90" t="str">
+        <x:v>The article states that Waverley in Surrey moved to tier 4, which substantively affects areas containing sampled divisions. The current L3 wording, however, requires a Surrey council decision/service/issue; national Covid restrictions do not clearly satisfy that condition.</x:v>
+      </x:c>
+      <x:c r="Q42" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R42" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S42" s="83" t="str">
         <x:f>IF(B42&lt;&gt;"complete","",IF(OR(M42="",N42="",O42="",Q42="",R42=""),"MISSING REQUIRED FIELD","OK"))</x:f>
       </x:c>
@@ -9200,7 +10460,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C43" s="81" t="str">
         <x:v>NEWS-guardian_api-be5b11434a57</x:v>
@@ -9230,14 +10490,27 @@
       <x:c r="L43" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M43" s="82" t="str"/>
-      <x:c r="N43" s="82" t="str"/>
-      <x:c r="O43" s="90" t="str"/>
-      <x:c r="P43" s="90" t="str"/>
-      <x:c r="Q43" s="82" t="str"/>
-      <x:c r="R43" s="82" t="str"/>
+      <x:c r="M43" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N43" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O43" s="90" t="str">
+        <x:v>Homelessness campaigners have demanded an urgent reboot of the government’s “Everybody In” scheme in England to provide safe shelter for thousands of rough sleepers as the UK enters another lockdown, with winter temperatures expected to plummet.</x:v>
+      </x:c>
+      <x:c r="P43" s="90" t="str">
+        <x:v>The article concerns national homelessness policy and the duties of English local authorities during lockdown. This is a substantive public-service and local-government issue under N2.</x:v>
+      </x:c>
+      <x:c r="Q43" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R43" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S43" s="83" t="str">
         <x:f>IF(B43&lt;&gt;"complete","",IF(OR(M43="",N43="",O43="",Q43="",R43=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="70" customHeight="1">
@@ -9245,7 +10518,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C44" s="81" t="str">
         <x:v>NEWS-guardian_api-c726af230abd</x:v>
@@ -9275,14 +10548,27 @@
       <x:c r="L44" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M44" s="82" t="str"/>
-      <x:c r="N44" s="82" t="str"/>
-      <x:c r="O44" s="90" t="str"/>
-      <x:c r="P44" s="90" t="str"/>
-      <x:c r="Q44" s="82" t="str"/>
-      <x:c r="R44" s="82" t="str"/>
+      <x:c r="M44" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N44" s="82" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="O44" s="90" t="str">
+        <x:v>Dozens of children and young people with mental health problems are still being treated on wards containing adults with sometimes severe psychiatric problems despite ministers having supposedly outlawed the practice in 2010, the Guardian can reveal.</x:v>
+      </x:c>
+      <x:c r="P44" s="90" t="str">
+        <x:v>The article concerns children being treated on adult NHS psychiatric wards and ministerial responsibility. It directly satisfies the NHS/public-services branch of N2.</x:v>
+      </x:c>
+      <x:c r="Q44" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R44" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S44" s="83" t="str">
         <x:f>IF(B44&lt;&gt;"complete","",IF(OR(M44="",N44="",O44="",Q44="",R44=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="70" customHeight="1">
@@ -9290,7 +10576,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C45" s="81" t="str">
         <x:v>NEWS-guardian_api-cc8e272342e5</x:v>
@@ -9320,14 +10606,27 @@
       <x:c r="L45" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M45" s="82" t="str"/>
-      <x:c r="N45" s="82" t="str"/>
-      <x:c r="O45" s="90" t="str"/>
-      <x:c r="P45" s="90" t="str"/>
-      <x:c r="Q45" s="82" t="str"/>
-      <x:c r="R45" s="82" t="str"/>
+      <x:c r="M45" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N45" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O45" s="90" t="str">
+        <x:v>A brilliant interview as always from Zoe Williams (‘We thought the Rwanda scheme was the worst of it’: Enver Solomon on leading – and leaving – the Refugee Council, 24 November).</x:v>
+      </x:c>
+      <x:c r="P45" s="90" t="str">
+        <x:v>The letter comments on national governments and the Labour party but contains no sampled Surrey place, candidate or council issue. National political content cannot satisfy a local L-rule.</x:v>
+      </x:c>
+      <x:c r="Q45" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R45" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S45" s="83" t="str">
         <x:f>IF(B45&lt;&gt;"complete","",IF(OR(M45="",N45="",O45="",Q45="",R45=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="70" customHeight="1">
@@ -9335,7 +10634,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C46" s="81" t="str">
         <x:v>NEWS-guardian_api-d12e8db585f0</x:v>
@@ -9365,14 +10664,27 @@
       <x:c r="L46" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M46" s="82" t="str"/>
-      <x:c r="N46" s="82" t="str"/>
-      <x:c r="O46" s="90" t="str"/>
-      <x:c r="P46" s="90" t="str"/>
-      <x:c r="Q46" s="82" t="str"/>
-      <x:c r="R46" s="82" t="str"/>
+      <x:c r="M46" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N46" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O46" s="90" t="str">
+        <x:v>Polly Toynbee is correct to point out the foolishness of a massive local government reorganisation, given other priorities (Is No 10 seeking its own destruction?</x:v>
+      </x:c>
+      <x:c r="P46" s="90" t="str">
+        <x:v>The letter discusses local-government reorganisation nationally. Guildford appears only in the writer's address, which is not substantive evidence of an effect on a sampled division.</x:v>
+      </x:c>
+      <x:c r="Q46" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R46" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S46" s="83" t="str">
         <x:f>IF(B46&lt;&gt;"complete","",IF(OR(M46="",N46="",O46="",Q46="",R46=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="70" customHeight="1">
@@ -9380,7 +10692,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C47" s="81" t="str">
         <x:v>NEWS-guardian_api-de14fda465d9</x:v>
@@ -9410,14 +10722,27 @@
       <x:c r="L47" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M47" s="82" t="str"/>
-      <x:c r="N47" s="82" t="str"/>
-      <x:c r="O47" s="90" t="str"/>
-      <x:c r="P47" s="90" t="str"/>
-      <x:c r="Q47" s="82" t="str"/>
-      <x:c r="R47" s="82" t="str"/>
+      <x:c r="M47" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N47" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O47" s="90" t="str">
+        <x:v>Co-edited by Fowler, it highlighted that 93 trust properties, including Clandon Park in Surrey and Hare Hill in Cheshire, were linked to wealth from plantations and the slave trade, while others, such as Bateman’s, Rudyard Kipling’s home in Sussex, were important to understanding Britain’s colonial history.</x:v>
+      </x:c>
+      <x:c r="P47" s="90" t="str">
+        <x:v>The article is about a national controversy over National Trust colonial-history research. Clandon Park is one item in a list of 93 properties and is not the substantive subject of the report.</x:v>
+      </x:c>
+      <x:c r="Q47" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R47" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S47" s="83" t="str">
         <x:f>IF(B47&lt;&gt;"complete","",IF(OR(M47="",N47="",O47="",Q47="",R47=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="70" customHeight="1">
@@ -9425,7 +10750,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C48" s="81" t="str">
         <x:v>NEWS-guardian_api-e2001566d58a</x:v>
@@ -9455,14 +10780,27 @@
       <x:c r="L48" s="81" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="M48" s="82" t="str"/>
-      <x:c r="N48" s="82" t="str"/>
-      <x:c r="O48" s="90" t="str"/>
-      <x:c r="P48" s="90" t="str"/>
-      <x:c r="Q48" s="82" t="str"/>
-      <x:c r="R48" s="82" t="str"/>
+      <x:c r="M48" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N48" s="82" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="O48" s="90" t="str">
+        <x:v>David Cameron has arrived in the Gulf at the beginning of a low-key arms trip aimed at persuading regional powers upset by Britain's response to the Arab spring to buy more than 100 Eurofighter Typhoon fighter jets.</x:v>
+      </x:c>
+      <x:c r="P48" s="90" t="str">
+        <x:v>The article reports the prime minister's arms-trade diplomacy, government policy and human-rights criticism. This is substantive UK government-performance coverage under N1.</x:v>
+      </x:c>
+      <x:c r="Q48" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R48" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S48" s="83" t="str">
         <x:f>IF(B48&lt;&gt;"complete","",IF(OR(M48="",N48="",O48="",Q48="",R48=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="70" customHeight="1">
@@ -9470,7 +10808,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C49" s="81" t="str">
         <x:v>NEWS-guardian_api-e9ed22adbdb1</x:v>
@@ -9500,14 +10838,27 @@
       <x:c r="L49" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M49" s="82" t="str"/>
-      <x:c r="N49" s="82" t="str"/>
-      <x:c r="O49" s="90" t="str"/>
-      <x:c r="P49" s="90" t="str"/>
-      <x:c r="Q49" s="82" t="str"/>
-      <x:c r="R49" s="82" t="str"/>
+      <x:c r="M49" s="82" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N49" s="82" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O49" s="90" t="str">
+        <x:v>“Did 2025 mark the end of British parliamentary democracy as we know it?” asks the headline on Andy Beckett’s article (25 December).</x:v>
+      </x:c>
+      <x:c r="P49" s="90" t="str">
+        <x:v>The letters discuss national democracy, Labour and proportional representation. Farnham appears only in a writer's address and does not create substantive L1 relevance.</x:v>
+      </x:c>
+      <x:c r="Q49" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R49" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S49" s="83" t="str">
         <x:f>IF(B49&lt;&gt;"complete","",IF(OR(M49="",N49="",O49="",Q49="",R49=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="70" customHeight="1">
@@ -9515,7 +10866,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="81" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C50" s="81" t="str">
         <x:v>NEWS-guardian_api-f0e1fbfa261a</x:v>
@@ -9545,14 +10896,27 @@
       <x:c r="L50" s="81" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M50" s="82" t="str"/>
-      <x:c r="N50" s="82" t="str"/>
-      <x:c r="O50" s="90" t="str"/>
-      <x:c r="P50" s="90" t="str"/>
-      <x:c r="Q50" s="82" t="str"/>
-      <x:c r="R50" s="82" t="str"/>
+      <x:c r="M50" s="82" t="str">
+        <x:v>include</x:v>
+      </x:c>
+      <x:c r="N50" s="82" t="str">
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="O50" s="90" t="str">
+        <x:v>Jessica Fuhl writes Assurances have been given that Epsom Hospital will not close under an NHS review covering Surrey and south west London, Epsom council has said.</x:v>
+      </x:c>
+      <x:c r="P50" s="90" t="str">
+        <x:v>The healthcare live blog contains a substantive item about Epsom Hospital and an NHS review covering Surrey. The correct local basis is L1 place linkage; the NHS review is not itself a Surrey council decision under L3.</x:v>
+      </x:c>
+      <x:c r="Q50" s="82" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R50" s="82" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S50" s="83" t="str">
         <x:f>IF(B50&lt;&gt;"complete","",IF(OR(M50="",N50="",O50="",Q50="",R50=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="70" customHeight="1">
@@ -9560,7 +10924,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="85" t="str">
-        <x:v>not_started</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="C51" s="85" t="str">
         <x:v>NEWS-guardian_api-ffae95f17052</x:v>
@@ -9590,14 +10954,27 @@
       <x:c r="L51" s="85" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M51" s="86" t="str"/>
-      <x:c r="N51" s="86" t="str"/>
-      <x:c r="O51" s="91" t="str"/>
-      <x:c r="P51" s="91" t="str"/>
-      <x:c r="Q51" s="86" t="str"/>
-      <x:c r="R51" s="86" t="str"/>
+      <x:c r="M51" s="86" t="str">
+        <x:v>exclude</x:v>
+      </x:c>
+      <x:c r="N51" s="86" t="str">
+        <x:v>exclusion_boundary</x:v>
+      </x:c>
+      <x:c r="O51" s="91" t="str">
+        <x:v>In the week that many families went to the coast for the fresh sea air or the tang of fish and chips, visitors to one Lancashire resort inhaled a rather more unpleasant aroma.</x:v>
+      </x:c>
+      <x:c r="P51" s="91" t="str">
+        <x:v>The landfill story concerns Fleetwood in Lancashire and the Environment Agency. It has no Surrey council or sampled-area linkage.</x:v>
+      </x:c>
+      <x:c r="Q51" s="86" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="R51" s="86" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="S51" s="87" t="str">
         <x:f>IF(B51&lt;&gt;"complete","",IF(OR(M51="",N51="",O51="",Q51="",R51=""),"MISSING REQUIRED FIELD","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9804,16 +11181,30 @@
       <x:c r="I6" s="117" t="str"/>
       <x:c r="J6" s="117" t="str"/>
       <x:c r="K6" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L6" s="118" t="str"/>
-      <x:c r="M6" s="118" t="str"/>
+        <x:v>needs_adjudication</x:v>
+      </x:c>
+      <x:c r="L6" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M6" s="118" t="str">
+        <x:v>University of Surrey</x:v>
+      </x:c>
       <x:c r="N6" s="118" t="str"/>
-      <x:c r="O6" s="118" t="str"/>
-      <x:c r="P6" s="118" t="str"/>
-      <x:c r="Q6" s="118" t="str"/>
-      <x:c r="R6" s="118" t="str"/>
-      <x:c r="S6" s="118" t="str"/>
+      <x:c r="O6" s="118" t="str">
+        <x:v>The first year student at the University of Surrey died while returning from a sports trip to Italy.</x:v>
+      </x:c>
+      <x:c r="P6" s="118" t="str">
+        <x:v>unresolved_missing_context</x:v>
+      </x:c>
+      <x:c r="Q6" s="118" t="str">
+        <x:v>The institution is Surrey-specific, but no sampled division is established by the stored query or article.</x:v>
+      </x:c>
+      <x:c r="R6" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S6" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T6" s="119" t="str">
         <x:f>IF(K6&lt;&gt;"complete","",IF(OR(L6="",P6="",O6="",R6="",S6=""),"CHECK","OK"))</x:f>
       </x:c>
@@ -9842,18 +11233,31 @@
       <x:c r="I7" s="117" t="str"/>
       <x:c r="J7" s="117" t="str"/>
       <x:c r="K7" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L7" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L7" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M7" s="118" t="str"/>
       <x:c r="N7" s="118" t="str"/>
-      <x:c r="O7" s="118" t="str"/>
-      <x:c r="P7" s="118" t="str"/>
-      <x:c r="Q7" s="118" t="str"/>
-      <x:c r="R7" s="118" t="str"/>
-      <x:c r="S7" s="118" t="str"/>
+      <x:c r="O7" s="118" t="str">
+        <x:v>Keir Starmer has faced down immediate calls for his resignation after receiving the full backing of his cabinet and delivering an impassioned appeal to the PLP this evening that appears to have steadied the government’s ship, at least for now.</x:v>
+      </x:c>
+      <x:c r="P7" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q7" s="118" t="str">
+        <x:v>No sampled Surrey place, candidate, councillor, council issue or county-wide Surrey political coverage is identified.</x:v>
+      </x:c>
+      <x:c r="R7" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S7" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T7" s="119" t="str">
         <x:f>IF(K7&lt;&gt;"complete","",IF(OR(L7="",P7="",O7="",R7="",S7=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -9880,18 +11284,31 @@
       <x:c r="I8" s="117" t="str"/>
       <x:c r="J8" s="117" t="str"/>
       <x:c r="K8" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L8" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L8" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M8" s="118" t="str"/>
       <x:c r="N8" s="118" t="str"/>
-      <x:c r="O8" s="118" t="str"/>
-      <x:c r="P8" s="118" t="str"/>
-      <x:c r="Q8" s="118" t="str"/>
-      <x:c r="R8" s="118" t="str"/>
-      <x:c r="S8" s="118" t="str"/>
+      <x:c r="O8" s="118" t="str">
+        <x:v>It has been an election buildup dominated by the rise of Reform UK and the Greens, and the contrasting woes of Labour and the Tories.</x:v>
+      </x:c>
+      <x:c r="P8" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q8" s="118" t="str">
+        <x:v>The article contains no substantive link to a sampled Surrey area.</x:v>
+      </x:c>
+      <x:c r="R8" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S8" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T8" s="119" t="str">
         <x:f>IF(K8&lt;&gt;"complete","",IF(OR(L8="",P8="",O8="",R8="",S8=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -9922,18 +11339,33 @@
         <x:v>Surrey council cabinet member Julie Iles said: “We are proposing changes that provide the right level of support, and help young people to gain independence where possible and transition to adulthood successfully.</x:v>
       </x:c>
       <x:c r="K9" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L9" s="118" t="str"/>
-      <x:c r="M9" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L9" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M9" s="118" t="str">
+        <x:v>Surrey council</x:v>
+      </x:c>
       <x:c r="N9" s="118" t="str"/>
-      <x:c r="O9" s="118" t="str"/>
-      <x:c r="P9" s="118" t="str"/>
-      <x:c r="Q9" s="118" t="str"/>
-      <x:c r="R9" s="118" t="str"/>
-      <x:c r="S9" s="118" t="str"/>
+      <x:c r="O9" s="118" t="str">
+        <x:v>Surrey council cabinet member Julie Iles said: “We are proposing changes that provide the right level of support, and help young people to gain independence where possible and transition to adulthood successfully.</x:v>
+      </x:c>
+      <x:c r="P9" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q9" s="118" t="str">
+        <x:v>The Surrey quotation is incidental to an England-wide funding story and is not linked to a sampled division.</x:v>
+      </x:c>
+      <x:c r="R9" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S9" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T9" s="119" t="str">
         <x:f>IF(K9&lt;&gt;"complete","",IF(OR(L9="",P9="",O9="",R9="",S9=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -9960,18 +11392,31 @@
       <x:c r="I10" s="117" t="str"/>
       <x:c r="J10" s="117" t="str"/>
       <x:c r="K10" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L10" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L10" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M10" s="118" t="str"/>
       <x:c r="N10" s="118" t="str"/>
-      <x:c r="O10" s="118" t="str"/>
-      <x:c r="P10" s="118" t="str"/>
-      <x:c r="Q10" s="118" t="str"/>
-      <x:c r="R10" s="118" t="str"/>
-      <x:c r="S10" s="118" t="str"/>
+      <x:c r="O10" s="118" t="str">
+        <x:v>Ministers have dropped plans to delay 30 local elections this May after receiving legal advice that doing so might be unlawful.</x:v>
+      </x:c>
+      <x:c r="P10" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q10" s="118" t="str">
+        <x:v>No sampled Surrey linkage is stated.</x:v>
+      </x:c>
+      <x:c r="R10" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S10" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T10" s="119" t="str">
         <x:f>IF(K10&lt;&gt;"complete","",IF(OR(L10="",P10="",O10="",R10="",S10=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -9998,18 +11443,33 @@
       <x:c r="I11" s="117" t="str"/>
       <x:c r="J11" s="117" t="str"/>
       <x:c r="K11" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L11" s="118" t="str"/>
-      <x:c r="M11" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L11" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M11" s="118" t="str">
+        <x:v>Surrey Canal Sports Foundation</x:v>
+      </x:c>
       <x:c r="N11" s="118" t="str"/>
-      <x:c r="O11" s="118" t="str"/>
-      <x:c r="P11" s="118" t="str"/>
-      <x:c r="Q11" s="118" t="str"/>
-      <x:c r="R11" s="118" t="str"/>
-      <x:c r="S11" s="118" t="str"/>
+      <x:c r="O11" s="118" t="str">
+        <x:v>The sports foundation at the heart of the Millwall FC compulsory purchase battle has been making false claims of having a £2m funding agreement from Sport England during the ongoing CPO process, the Guardian can reveal.</x:v>
+      </x:c>
+      <x:c r="P11" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q11" s="118" t="str">
+        <x:v>The word Surrey occurs inside an organisation/place name associated with Lewisham and does not denote the study area.</x:v>
+      </x:c>
+      <x:c r="R11" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S11" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T11" s="119" t="str">
         <x:f>IF(K11&lt;&gt;"complete","",IF(OR(L11="",P11="",O11="",R11="",S11=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -10040,18 +11500,33 @@
         <x:v>Mr Corbyn did it in February when he read out leaked text exchanges between the leader of Surrey council and officials in the Department for Communities and Local Government, exposing a sweetheart deal over spending to avert a local referendum.</x:v>
       </x:c>
       <x:c r="K12" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L12" s="118" t="str"/>
-      <x:c r="M12" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L12" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M12" s="118" t="str">
+        <x:v>Surrey council</x:v>
+      </x:c>
       <x:c r="N12" s="118" t="str"/>
-      <x:c r="O12" s="118" t="str"/>
-      <x:c r="P12" s="118" t="str"/>
-      <x:c r="Q12" s="118" t="str"/>
-      <x:c r="R12" s="118" t="str"/>
-      <x:c r="S12" s="118" t="str"/>
+      <x:c r="O12" s="118" t="str">
+        <x:v>Mr Corbyn did it in February when he read out leaked text exchanges between the leader of Surrey council and officials in the Department for Communities and Local Government, exposing a sweetheart deal over spending to avert a local referendum.</x:v>
+      </x:c>
+      <x:c r="P12" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q12" s="118" t="str">
+        <x:v>The Surrey council reference is a historical example rather than the subject of the article.</x:v>
+      </x:c>
+      <x:c r="R12" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S12" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T12" s="119" t="str">
         <x:f>IF(K12&lt;&gt;"complete","",IF(OR(L12="",P12="",O12="",R12="",S12=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -10082,18 +11557,35 @@
         <x:v>In the south of England East Surrey hospital in Redhill stopped visits to 10 of its wards on Tuesday, a decision which had not been taken lightly, Surrey and Sussex Healthcare NHS trust said.</x:v>
       </x:c>
       <x:c r="K13" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L13" s="118" t="str"/>
-      <x:c r="M13" s="118" t="str"/>
-      <x:c r="N13" s="118" t="str"/>
-      <x:c r="O13" s="118" t="str"/>
-      <x:c r="P13" s="118" t="str"/>
-      <x:c r="Q13" s="118" t="str"/>
-      <x:c r="R13" s="118" t="str"/>
-      <x:c r="S13" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L13" s="118" t="str">
+        <x:v>L1_place</x:v>
+      </x:c>
+      <x:c r="M13" s="118" t="str">
+        <x:v>Redhill</x:v>
+      </x:c>
+      <x:c r="N13" s="118" t="str">
+        <x:v>Redhill East</x:v>
+      </x:c>
+      <x:c r="O13" s="118" t="str">
+        <x:v>In the south of England East Surrey hospital in Redhill stopped visits to 10 of its wards on Tuesday, a decision which had not been taken lightly, Surrey and Sussex Healthcare NHS trust said.</x:v>
+      </x:c>
+      <x:c r="P13" s="118" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Q13" s="118" t="str">
+        <x:v>Redhill is a town represented in the sampled Redhill East division; the hospital example is substantive rather than a byline or dateline.</x:v>
+      </x:c>
+      <x:c r="R13" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S13" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T13" s="119" t="str">
         <x:f>IF(K13&lt;&gt;"complete","",IF(OR(L13="",P13="",O13="",R13="",S13=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -10120,18 +11612,33 @@
       <x:c r="I14" s="117" t="str"/>
       <x:c r="J14" s="117" t="str"/>
       <x:c r="K14" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L14" s="118" t="str"/>
-      <x:c r="M14" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L14" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M14" s="118" t="str">
+        <x:v>unspecified Surrey village</x:v>
+      </x:c>
       <x:c r="N14" s="118" t="str"/>
-      <x:c r="O14" s="118" t="str"/>
-      <x:c r="P14" s="118" t="str"/>
-      <x:c r="Q14" s="118" t="str"/>
-      <x:c r="R14" s="118" t="str"/>
-      <x:c r="S14" s="118" t="str"/>
+      <x:c r="O14" s="118" t="str">
+        <x:v>In April 2018, a woman told the newspaper how she was struggling to sell the retirement flat her late parents had bought in 1997 and that she had been forced to cut the price from £185,000 to £140,000, well below the £260,000 average for a normal flat in the same Surrey village.</x:v>
+      </x:c>
+      <x:c r="P14" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q14" s="118" t="str">
+        <x:v>The Surrey reference belongs to a separate illustrative case and provides no sampled-division linkage.</x:v>
+      </x:c>
+      <x:c r="R14" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S14" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T14" s="119" t="str">
         <x:f>IF(K14&lt;&gt;"complete","",IF(OR(L14="",P14="",O14="",R14="",S14=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -10158,18 +11665,33 @@
       <x:c r="I15" s="117" t="str"/>
       <x:c r="J15" s="117" t="str"/>
       <x:c r="K15" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L15" s="118" t="str"/>
-      <x:c r="M15" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L15" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M15" s="118" t="str">
+        <x:v>Clevedon</x:v>
+      </x:c>
       <x:c r="N15" s="118" t="str"/>
-      <x:c r="O15" s="118" t="str"/>
-      <x:c r="P15" s="118" t="str"/>
-      <x:c r="Q15" s="118" t="str"/>
-      <x:c r="R15" s="118" t="str"/>
-      <x:c r="S15" s="118" t="str"/>
+      <x:c r="O15" s="118" t="str">
+        <x:v>The shop windows are decked out in their festive finery, there are carols on the stereos and the tills are ringing.</x:v>
+      </x:c>
+      <x:c r="P15" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q15" s="118" t="str">
+        <x:v>The affected location and authority are in North Somerset, not Surrey.</x:v>
+      </x:c>
+      <x:c r="R15" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S15" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T15" s="119" t="str">
         <x:f>IF(K15&lt;&gt;"complete","",IF(OR(L15="",P15="",O15="",R15="",S15=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -10196,18 +11718,33 @@
       <x:c r="I16" s="117" t="str"/>
       <x:c r="J16" s="117" t="str"/>
       <x:c r="K16" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L16" s="118" t="str"/>
-      <x:c r="M16" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L16" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M16" s="118" t="str">
+        <x:v>Essex; Norfolk; Suffolk; Hampshire; Sussex</x:v>
+      </x:c>
       <x:c r="N16" s="118" t="str"/>
-      <x:c r="O16" s="118" t="str"/>
-      <x:c r="P16" s="118" t="str"/>
-      <x:c r="Q16" s="118" t="str"/>
-      <x:c r="R16" s="118" t="str"/>
-      <x:c r="S16" s="118" t="str"/>
+      <x:c r="O16" s="118" t="str">
+        <x:v>Ministers are to postpone elections for new mayors in four parts of England, prompting accusations from opposition parties that Downing Street is “cancelling democracy”.</x:v>
+      </x:c>
+      <x:c r="P16" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q16" s="118" t="str">
+        <x:v>None of the named mayoralties establishes a sampled Surrey link.</x:v>
+      </x:c>
+      <x:c r="R16" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S16" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T16" s="119" t="str">
         <x:f>IF(K16&lt;&gt;"complete","",IF(OR(L16="",P16="",O16="",R16="",S16=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -10234,18 +11771,33 @@
       <x:c r="I17" s="117" t="str"/>
       <x:c r="J17" s="117" t="str"/>
       <x:c r="K17" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L17" s="118" t="str"/>
-      <x:c r="M17" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L17" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M17" s="118" t="str">
+        <x:v>Nonsuch High School</x:v>
+      </x:c>
       <x:c r="N17" s="118" t="str"/>
-      <x:c r="O17" s="118" t="str"/>
-      <x:c r="P17" s="118" t="str"/>
-      <x:c r="Q17" s="118" t="str"/>
-      <x:c r="R17" s="118" t="str"/>
-      <x:c r="S17" s="118" t="str"/>
+      <x:c r="O17" s="118" t="str">
+        <x:v>The speech was made in the playground of Nonsuch high school for girls in Surrey.</x:v>
+      </x:c>
+      <x:c r="P17" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q17" s="118" t="str">
+        <x:v>The project data identifies a separate Nonsuch area, but Nonsuch is not one of the 17 sampled divisions.</x:v>
+      </x:c>
+      <x:c r="R17" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S17" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T17" s="119" t="str">
         <x:f>IF(K17&lt;&gt;"complete","",IF(OR(L17="",P17="",O17="",R17="",S17=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -10272,18 +11824,31 @@
       <x:c r="I18" s="117" t="str"/>
       <x:c r="J18" s="117" t="str"/>
       <x:c r="K18" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L18" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L18" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M18" s="118" t="str"/>
       <x:c r="N18" s="118" t="str"/>
-      <x:c r="O18" s="118" t="str"/>
-      <x:c r="P18" s="118" t="str"/>
-      <x:c r="Q18" s="118" t="str"/>
-      <x:c r="R18" s="118" t="str"/>
-      <x:c r="S18" s="118" t="str"/>
+      <x:c r="O18" s="118" t="str">
+        <x:v>Ask Barbara Keeley what keeps her awake at night and Labour’s shadow cabinet member for mental health and social care will tell you it’s the stories of people in “heartrending” situations whose care is being cut.</x:v>
+      </x:c>
+      <x:c r="P18" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q18" s="118" t="str">
+        <x:v>No sampled Surrey location or Surrey-specific council effect is identified.</x:v>
+      </x:c>
+      <x:c r="R18" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S18" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T18" s="119" t="str">
         <x:f>IF(K18&lt;&gt;"complete","",IF(OR(L18="",P18="",O18="",R18="",S18=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -10310,18 +11875,33 @@
       <x:c r="I19" s="117" t="str"/>
       <x:c r="J19" s="117" t="str"/>
       <x:c r="K19" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L19" s="118" t="str"/>
-      <x:c r="M19" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L19" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M19" s="118" t="str">
+        <x:v>Lewisham</x:v>
+      </x:c>
       <x:c r="N19" s="118" t="str"/>
-      <x:c r="O19" s="118" t="str"/>
-      <x:c r="P19" s="118" t="str"/>
-      <x:c r="Q19" s="118" t="str"/>
-      <x:c r="R19" s="118" t="str"/>
-      <x:c r="S19" s="118" t="str"/>
+      <x:c r="O19" s="118" t="str">
+        <x:v>Millwall Football Club have admitted for the first time that they may be forced to leave their south London home and relocate to Kent should the seizure of their land go ahead.</x:v>
+      </x:c>
+      <x:c r="P19" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q19" s="118" t="str">
+        <x:v>The relevant council and affected area are outside Surrey.</x:v>
+      </x:c>
+      <x:c r="R19" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S19" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T19" s="119" t="str">
         <x:f>IF(K19&lt;&gt;"complete","",IF(OR(L19="",P19="",O19="",R19="",S19=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -10348,18 +11928,31 @@
       <x:c r="I20" s="117" t="str"/>
       <x:c r="J20" s="117" t="str"/>
       <x:c r="K20" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L20" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L20" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M20" s="118" t="str"/>
       <x:c r="N20" s="118" t="str"/>
-      <x:c r="O20" s="118" t="str"/>
-      <x:c r="P20" s="118" t="str"/>
-      <x:c r="Q20" s="118" t="str"/>
-      <x:c r="R20" s="118" t="str"/>
-      <x:c r="S20" s="118" t="str"/>
+      <x:c r="O20" s="118" t="str">
+        <x:v>Tory supporters of equal marriage are making an eleventh hour plea to fellow Conservative MPs to vote in favour of reform by invoking the record of Margaret Thatcher, who supported the legalisation of homosexuality in the 1960s.</x:v>
+      </x:c>
+      <x:c r="P20" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q20" s="118" t="str">
+        <x:v>No sampled Surrey link is present.</x:v>
+      </x:c>
+      <x:c r="R20" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S20" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T20" s="119" t="str">
         <x:f>IF(K20&lt;&gt;"complete","",IF(OR(L20="",P20="",O20="",R20="",S20=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -10386,18 +11979,31 @@
       <x:c r="I21" s="117" t="str"/>
       <x:c r="J21" s="117" t="str"/>
       <x:c r="K21" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L21" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L21" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M21" s="118" t="str"/>
       <x:c r="N21" s="118" t="str"/>
-      <x:c r="O21" s="118" t="str"/>
-      <x:c r="P21" s="118" t="str"/>
-      <x:c r="Q21" s="118" t="str"/>
-      <x:c r="R21" s="118" t="str"/>
-      <x:c r="S21" s="118" t="str"/>
+      <x:c r="O21" s="118" t="str">
+        <x:v>Kemi Badenoch has been accused of weaponising violence against women and girls and using “dangerous” and “deeply inaccurate” claims in her response to the government’s plan to tackle the issue.</x:v>
+      </x:c>
+      <x:c r="P21" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q21" s="118" t="str">
+        <x:v>No sampled Surrey place or issue is established.</x:v>
+      </x:c>
+      <x:c r="R21" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S21" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T21" s="119" t="str">
         <x:f>IF(K21&lt;&gt;"complete","",IF(OR(L21="",P21="",O21="",R21="",S21=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -10428,18 +12034,33 @@
         <x:v>On C4News tonight, Gary Gibbon tells the story - based on my biography - of how in 2004, while a Ukip MEP, Farage secretly met a senior Cons MP &amp;amp; a Surrey councillor, seeking their help to defect &amp;amp; get picked for a safe Tory seat.</x:v>
       </x:c>
       <x:c r="K22" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L22" s="118" t="str"/>
-      <x:c r="M22" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L22" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M22" s="118" t="str">
+        <x:v>unnamed Surrey councillor</x:v>
+      </x:c>
       <x:c r="N22" s="118" t="str"/>
-      <x:c r="O22" s="118" t="str"/>
-      <x:c r="P22" s="118" t="str"/>
-      <x:c r="Q22" s="118" t="str"/>
-      <x:c r="R22" s="118" t="str"/>
-      <x:c r="S22" s="118" t="str"/>
+      <x:c r="O22" s="118" t="str">
+        <x:v>On C4News tonight, Gary Gibbon tells the story - based on my biography - of how in 2004, while a Ukip MEP, Farage secretly met a senior Cons MP &amp;amp; a Surrey councillor, seeking their help to defect &amp;amp; get picked for a safe Tory seat.</x:v>
+      </x:c>
+      <x:c r="P22" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q22" s="118" t="str">
+        <x:v>The Surrey councillor reference is historical and incidental to national Reform coverage.</x:v>
+      </x:c>
+      <x:c r="R22" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S22" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T22" s="119" t="str">
         <x:f>IF(K22&lt;&gt;"complete","",IF(OR(L22="",P22="",O22="",R22="",S22=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -10466,18 +12087,33 @@
       <x:c r="I23" s="117" t="str"/>
       <x:c r="J23" s="117" t="str"/>
       <x:c r="K23" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L23" s="118" t="str"/>
-      <x:c r="M23" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L23" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M23" s="118" t="str">
+        <x:v>Peterborough</x:v>
+      </x:c>
       <x:c r="N23" s="118" t="str"/>
-      <x:c r="O23" s="118" t="str"/>
-      <x:c r="P23" s="118" t="str"/>
-      <x:c r="Q23" s="118" t="str"/>
-      <x:c r="R23" s="118" t="str"/>
-      <x:c r="S23" s="118" t="str"/>
+      <x:c r="O23" s="118" t="str">
+        <x:v>Traditional Boxing Day hunts across large parts of the UK have been cancelled due to coronavirus restrictions, with those going ahead elsewhere not parading through town centres prior to their yuletide meet this year for the first time in recent history.</x:v>
+      </x:c>
+      <x:c r="P23" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q23" s="118" t="str">
+        <x:v>The only named council decision is outside Surrey.</x:v>
+      </x:c>
+      <x:c r="R23" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S23" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T23" s="119" t="str">
         <x:f>IF(K23&lt;&gt;"complete","",IF(OR(L23="",P23="",O23="",R23="",S23=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -10504,18 +12140,33 @@
       <x:c r="I24" s="117" t="str"/>
       <x:c r="J24" s="117" t="str"/>
       <x:c r="K24" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L24" s="118" t="str"/>
-      <x:c r="M24" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L24" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M24" s="118" t="str">
+        <x:v>Surrey</x:v>
+      </x:c>
       <x:c r="N24" s="118" t="str"/>
-      <x:c r="O24" s="118" t="str"/>
-      <x:c r="P24" s="118" t="str"/>
-      <x:c r="Q24" s="118" t="str"/>
-      <x:c r="R24" s="118" t="str"/>
-      <x:c r="S24" s="118" t="str"/>
+      <x:c r="O24" s="118" t="str">
+        <x:v>Liverpool city region, York, North Yorkshire, Cambridgeshire, Norfolk, Essex, East Sussex, Surrey, Oxfordshire, Dorset and Devon are among other locations in tier 2.</x:v>
+      </x:c>
+      <x:c r="P24" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q24" s="118" t="str">
+        <x:v>Surrey appears in a national list of affected areas without a sampled-division link.</x:v>
+      </x:c>
+      <x:c r="R24" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S24" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T24" s="119" t="str">
         <x:f>IF(K24&lt;&gt;"complete","",IF(OR(L24="",P24="",O24="",R24="",S24=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -10542,18 +12193,31 @@
       <x:c r="I25" s="117" t="str"/>
       <x:c r="J25" s="117" t="str"/>
       <x:c r="K25" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L25" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L25" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M25" s="118" t="str"/>
       <x:c r="N25" s="118" t="str"/>
-      <x:c r="O25" s="118" t="str"/>
-      <x:c r="P25" s="118" t="str"/>
-      <x:c r="Q25" s="118" t="str"/>
-      <x:c r="R25" s="118" t="str"/>
-      <x:c r="S25" s="118" t="str"/>
+      <x:c r="O25" s="118" t="str">
+        <x:v>It is far too easy to impersonate someone at a polling station and claim their vote (Voters in local elections will be required to show ID in anti-fraud trials, 28 December).</x:v>
+      </x:c>
+      <x:c r="P25" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q25" s="118" t="str">
+        <x:v>No sampled Surrey linkage is present.</x:v>
+      </x:c>
+      <x:c r="R25" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S25" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T25" s="119" t="str">
         <x:f>IF(K25&lt;&gt;"complete","",IF(OR(L25="",P25="",O25="",R25="",S25=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -10580,18 +12244,33 @@
       <x:c r="I26" s="117" t="str"/>
       <x:c r="J26" s="117" t="str"/>
       <x:c r="K26" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L26" s="118" t="str"/>
-      <x:c r="M26" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L26" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M26" s="118" t="str">
+        <x:v>Surrey Police</x:v>
+      </x:c>
       <x:c r="N26" s="118" t="str"/>
-      <x:c r="O26" s="118" t="str"/>
-      <x:c r="P26" s="118" t="str"/>
-      <x:c r="Q26" s="118" t="str"/>
-      <x:c r="R26" s="118" t="str"/>
-      <x:c r="S26" s="118" t="str"/>
+      <x:c r="O26" s="118" t="str">
+        <x:v>Surrey and Thames Valley police forces are considering claims of sexual wrongdoing by the former prince.</x:v>
+      </x:c>
+      <x:c r="P26" s="118" t="str">
+        <x:v>unresolved_missing_context</x:v>
+      </x:c>
+      <x:c r="Q26" s="118" t="str">
+        <x:v>The Surrey force is substantively mentioned, but policing is not the council linkage required by L3 and no sampled area is named.</x:v>
+      </x:c>
+      <x:c r="R26" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S26" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T26" s="119" t="str">
         <x:f>IF(K26&lt;&gt;"complete","",IF(OR(L26="",P26="",O26="",R26="",S26=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -10618,16 +12297,30 @@
       <x:c r="I27" s="117" t="str"/>
       <x:c r="J27" s="117" t="str"/>
       <x:c r="K27" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L27" s="118" t="str"/>
-      <x:c r="M27" s="118" t="str"/>
+        <x:v>needs_adjudication</x:v>
+      </x:c>
+      <x:c r="L27" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M27" s="118" t="str">
+        <x:v>Waverley</x:v>
+      </x:c>
       <x:c r="N27" s="118" t="str"/>
-      <x:c r="O27" s="118" t="str"/>
-      <x:c r="P27" s="118" t="str"/>
-      <x:c r="Q27" s="118" t="str"/>
-      <x:c r="R27" s="118" t="str"/>
-      <x:c r="S27" s="118" t="str"/>
+      <x:c r="O27" s="118" t="str">
+        <x:v>Areas moving to tier 4 are Sussex, Oxfordshire, Suffolk, Norfolk and Cambridgeshire, parts of Essex not yet in the highest tier, Waverley in Surrey and Hampshire, with the exception of the New Forest.</x:v>
+      </x:c>
+      <x:c r="P27" s="118" t="str">
+        <x:v>unresolved_missing_context</x:v>
+      </x:c>
+      <x:c r="Q27" s="118" t="str">
+        <x:v>Waverley contains sampled areas, but the article does not identify a specific sampled division and the governing decision is national rather than a Surrey council decision.</x:v>
+      </x:c>
+      <x:c r="R27" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S27" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T27" s="119" t="str">
         <x:f>IF(K27&lt;&gt;"complete","",IF(OR(L27="",P27="",O27="",R27="",S27=""),"CHECK","OK"))</x:f>
       </x:c>
@@ -10656,18 +12349,31 @@
       <x:c r="I28" s="117" t="str"/>
       <x:c r="J28" s="117" t="str"/>
       <x:c r="K28" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L28" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L28" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
       <x:c r="M28" s="118" t="str"/>
       <x:c r="N28" s="118" t="str"/>
-      <x:c r="O28" s="118" t="str"/>
-      <x:c r="P28" s="118" t="str"/>
-      <x:c r="Q28" s="118" t="str"/>
-      <x:c r="R28" s="118" t="str"/>
-      <x:c r="S28" s="118" t="str"/>
+      <x:c r="O28" s="118" t="str">
+        <x:v>A brilliant interview as always from Zoe Williams (‘We thought the Rwanda scheme was the worst of it’: Enver Solomon on leading – and leaving – the Refugee Council, 24 November).</x:v>
+      </x:c>
+      <x:c r="P28" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q28" s="118" t="str">
+        <x:v>No sampled Surrey link is present.</x:v>
+      </x:c>
+      <x:c r="R28" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S28" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T28" s="119" t="str">
         <x:f>IF(K28&lt;&gt;"complete","",IF(OR(L28="",P28="",O28="",R28="",S28=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -10698,18 +12404,33 @@
         <x:v>Bernard Quoroll Guildford, Surrey • Why Labour is wasting energy on an unnecessary reform of local government is, as Polly Toynbee points out, puzzling.</x:v>
       </x:c>
       <x:c r="K29" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L29" s="118" t="str"/>
-      <x:c r="M29" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L29" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M29" s="118" t="str">
+        <x:v>Guildford</x:v>
+      </x:c>
       <x:c r="N29" s="118" t="str"/>
-      <x:c r="O29" s="118" t="str"/>
-      <x:c r="P29" s="118" t="str"/>
-      <x:c r="Q29" s="118" t="str"/>
-      <x:c r="R29" s="118" t="str"/>
-      <x:c r="S29" s="118" t="str"/>
+      <x:c r="O29" s="118" t="str">
+        <x:v>Bernard Quoroll Guildford, Surrey • Why Labour is wasting energy on an unnecessary reform of local government is, as Polly Toynbee points out, puzzling.</x:v>
+      </x:c>
+      <x:c r="P29" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q29" s="118" t="str">
+        <x:v>Guildford is an author-location line rather than the subject or affected area of the letter.</x:v>
+      </x:c>
+      <x:c r="R29" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S29" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T29" s="119" t="str">
         <x:f>IF(K29&lt;&gt;"complete","",IF(OR(L29="",P29="",O29="",R29="",S29=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -10736,18 +12457,33 @@
       <x:c r="I30" s="117" t="str"/>
       <x:c r="J30" s="117" t="str"/>
       <x:c r="K30" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L30" s="118" t="str"/>
-      <x:c r="M30" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L30" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M30" s="118" t="str">
+        <x:v>Clandon Park</x:v>
+      </x:c>
       <x:c r="N30" s="118" t="str"/>
-      <x:c r="O30" s="118" t="str"/>
-      <x:c r="P30" s="118" t="str"/>
-      <x:c r="Q30" s="118" t="str"/>
-      <x:c r="R30" s="118" t="str"/>
-      <x:c r="S30" s="118" t="str"/>
+      <x:c r="O30" s="118" t="str">
+        <x:v>Co-edited by Fowler, it highlighted that 93 trust properties, including Clandon Park in Surrey and Hare Hill in Cheshire, were linked to wealth from plantations and the slave trade, while others, such as Bateman’s, Rudyard Kipling’s home in Sussex, were important to understanding Britain’s colonial history.</x:v>
+      </x:c>
+      <x:c r="P30" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q30" s="118" t="str">
+        <x:v>The Surrey property is a passing example within a national list and does not establish sampled-area relevance.</x:v>
+      </x:c>
+      <x:c r="R30" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S30" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T30" s="119" t="str">
         <x:f>IF(K30&lt;&gt;"complete","",IF(OR(L30="",P30="",O30="",R30="",S30=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -10778,18 +12514,33 @@
         <x:v>Tom Quinn Farnham, Surrey • Have an opinion on anything you’ve read in the Guardian today?</x:v>
       </x:c>
       <x:c r="K31" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L31" s="118" t="str"/>
-      <x:c r="M31" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L31" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M31" s="118" t="str">
+        <x:v>Farnham</x:v>
+      </x:c>
       <x:c r="N31" s="118" t="str"/>
-      <x:c r="O31" s="118" t="str"/>
-      <x:c r="P31" s="118" t="str"/>
-      <x:c r="Q31" s="118" t="str"/>
-      <x:c r="R31" s="118" t="str"/>
-      <x:c r="S31" s="118" t="str"/>
+      <x:c r="O31" s="118" t="str">
+        <x:v>Tom Quinn Farnham, Surrey • Have an opinion on anything you’ve read in the Guardian today?</x:v>
+      </x:c>
+      <x:c r="P31" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q31" s="118" t="str">
+        <x:v>Farnham is an author-location line rather than the subject of the letter.</x:v>
+      </x:c>
+      <x:c r="R31" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S31" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T31" s="119" t="str">
         <x:f>IF(K31&lt;&gt;"complete","",IF(OR(L31="",P31="",O31="",R31="",S31=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -10816,18 +12567,35 @@
       <x:c r="I32" s="117" t="str"/>
       <x:c r="J32" s="117" t="str"/>
       <x:c r="K32" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L32" s="118" t="str"/>
-      <x:c r="M32" s="118" t="str"/>
-      <x:c r="N32" s="118" t="str"/>
-      <x:c r="O32" s="118" t="str"/>
-      <x:c r="P32" s="118" t="str"/>
-      <x:c r="Q32" s="118" t="str"/>
-      <x:c r="R32" s="118" t="str"/>
-      <x:c r="S32" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L32" s="118" t="str">
+        <x:v>L1_place</x:v>
+      </x:c>
+      <x:c r="M32" s="118" t="str">
+        <x:v>Epsom</x:v>
+      </x:c>
+      <x:c r="N32" s="118" t="str">
+        <x:v>Epsom Town &amp; Downs</x:v>
+      </x:c>
+      <x:c r="O32" s="118" t="str">
+        <x:v>Jessica Fuhl writes Assurances have been given that Epsom Hospital will not close under an NHS review covering Surrey and south west London, Epsom council has said.</x:v>
+      </x:c>
+      <x:c r="P32" s="118" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Q32" s="118" t="str">
+        <x:v>The Epsom Hospital item directly concerns the sampled town and is not merely an address or passing list item.</x:v>
+      </x:c>
+      <x:c r="R32" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S32" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T32" s="119" t="str">
         <x:f>IF(K32&lt;&gt;"complete","",IF(OR(L32="",P32="",O32="",R32="",S32=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -10854,18 +12622,33 @@
       <x:c r="I33" s="117" t="str"/>
       <x:c r="J33" s="117" t="str"/>
       <x:c r="K33" s="118" t="str">
-        <x:v>not_started</x:v>
-      </x:c>
-      <x:c r="L33" s="118" t="str"/>
-      <x:c r="M33" s="118" t="str"/>
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="L33" s="118" t="str">
+        <x:v>no_link</x:v>
+      </x:c>
+      <x:c r="M33" s="118" t="str">
+        <x:v>Fleetwood</x:v>
+      </x:c>
       <x:c r="N33" s="118" t="str"/>
-      <x:c r="O33" s="118" t="str"/>
-      <x:c r="P33" s="118" t="str"/>
-      <x:c r="Q33" s="118" t="str"/>
-      <x:c r="R33" s="118" t="str"/>
-      <x:c r="S33" s="118" t="str"/>
+      <x:c r="O33" s="118" t="str">
+        <x:v>In the week that many families went to the coast for the fresh sea air or the tang of fish and chips, visitors to one Lancashire resort inhaled a rather more unpleasant aroma.</x:v>
+      </x:c>
+      <x:c r="P33" s="118" t="str">
+        <x:v>rejected_incidental</x:v>
+      </x:c>
+      <x:c r="Q33" s="118" t="str">
+        <x:v>The affected location is in Lancashire, outside the Surrey study area.</x:v>
+      </x:c>
+      <x:c r="R33" s="118" t="str">
+        <x:v>AI-assisted development draft (researcher verification required)</x:v>
+      </x:c>
+      <x:c r="S33" s="118" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
       <x:c r="T33" s="119" t="str">
         <x:f>IF(K33&lt;&gt;"complete","",IF(OR(L33="",P33="",O33="",R33="",S33=""),"CHECK","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
